--- a/theory/FEM matriisit.xlsx
+++ b/theory/FEM matriisit.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_Ohjelmointi\2_Rust\vefem\theory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B152728-5DA7-4027-A2A9-5B44D21E48A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F58154E-8FF7-4C85-A919-D1E2E8ED6AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{27180542-B0D2-4BFE-946B-7857B24C93C8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{27180542-B0D2-4BFE-946B-7857B24C93C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Ilman vapautuksia" sheetId="1" r:id="rId1"/>
     <sheet name="Vapautuksilla" sheetId="2" r:id="rId2"/>
     <sheet name="Jousituet" sheetId="4" r:id="rId3"/>
     <sheet name="Lukkovoimat" sheetId="3" r:id="rId4"/>
-    <sheet name="Tuki kierretty" sheetId="5" r:id="rId5"/>
+    <sheet name="Tuki kierretty x" sheetId="5" r:id="rId5"/>
+    <sheet name="Tuki kierretty y" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -73,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="125">
   <si>
     <t>°</t>
   </si>
@@ -510,6 +511,9 @@
   </si>
   <si>
     <t>KIERRETYT</t>
+  </si>
+  <si>
+    <t>Siirtymä tuen lokaalin Y-akselin suuntaan</t>
   </si>
 </sst>
 </file>
@@ -1233,7 +1237,64 @@
     <cellStyle name="Neutraali" xfId="1" builtinId="28"/>
     <cellStyle name="Normaali" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="31">
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
     <dxf>
       <font>
         <color auto="1"/>
@@ -1937,12 +1998,12 @@
     <xdr:from>
       <xdr:col>27</xdr:col>
       <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>485775</xdr:colOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
@@ -1958,9 +2019,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17421225" y="3771900"/>
-          <a:ext cx="0" cy="695325"/>
+        <a:xfrm flipH="1">
+          <a:off x="17907000" y="4248150"/>
+          <a:ext cx="447675" cy="219075"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1988,64 +2049,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>466725</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="15" name="Suora yhdysviiva 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{602C6171-DFE5-A416-433C-9F6A486F87D9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="17402175" y="2085975"/>
-          <a:ext cx="3267075" cy="1704975"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
@@ -2061,9 +2072,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17973675" y="3467100"/>
-          <a:ext cx="0" cy="695325"/>
+        <a:xfrm flipH="1">
+          <a:off x="18459450" y="3905250"/>
+          <a:ext cx="457200" cy="257175"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2093,12 +2104,12 @@
     <xdr:from>
       <xdr:col>29</xdr:col>
       <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>352425</xdr:colOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
@@ -2114,9 +2125,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="18516600" y="3200400"/>
-          <a:ext cx="0" cy="695325"/>
+        <a:xfrm flipH="1">
+          <a:off x="19002375" y="3657600"/>
+          <a:ext cx="447675" cy="238125"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2145,15 +2156,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2167,9 +2178,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19078575" y="2914650"/>
-          <a:ext cx="0" cy="695325"/>
+        <a:xfrm flipH="1">
+          <a:off x="19573875" y="3371850"/>
+          <a:ext cx="390525" cy="209550"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2199,12 +2210,12 @@
     <xdr:from>
       <xdr:col>31</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
+      <xdr:colOff>581025</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
@@ -2220,9 +2231,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19602450" y="2638425"/>
-          <a:ext cx="0" cy="695325"/>
+        <a:xfrm flipH="1">
+          <a:off x="20088225" y="3124200"/>
+          <a:ext cx="361950" cy="209550"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2252,12 +2263,12 @@
     <xdr:from>
       <xdr:col>32</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
+      <xdr:colOff>485775</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -2273,9 +2284,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20088225" y="2390775"/>
-          <a:ext cx="0" cy="695325"/>
+        <a:xfrm flipH="1">
+          <a:off x="20574000" y="2867025"/>
+          <a:ext cx="390525" cy="219075"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2305,12 +2316,12 @@
     <xdr:from>
       <xdr:col>33</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:colOff>457200</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
@@ -2326,9 +2337,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20640675" y="2066925"/>
-          <a:ext cx="0" cy="695325"/>
+        <a:xfrm flipH="1">
+          <a:off x="21126450" y="2495550"/>
+          <a:ext cx="419100" cy="266700"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2680,34 +2691,133 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>481285</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>141633</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>271864</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>112644</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Kuva 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFE474AA-C4CB-437A-816E-E8BE835D5A83}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4196035" y="294033"/>
+          <a:ext cx="1657479" cy="2295111"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="27" name="Suora nuoliyhdysviiva 26">
+        <xdr:cNvPr id="3" name="Suora yhdysviiva 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A45677F-260D-27C6-1A5C-BCFAE0E06BDC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85D37805-E29A-411A-99BF-28DAF46174A1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="19878675" y="3209925"/>
-          <a:ext cx="800100" cy="438150"/>
+        <a:xfrm flipV="1">
+          <a:off x="17868900" y="2952750"/>
+          <a:ext cx="3267075" cy="1704975"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Suora nuoliyhdysviiva 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E60F86F-D213-49BC-8229-DC6AF7AE82CB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17849850" y="3962400"/>
+          <a:ext cx="400050" cy="504825"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2731,6 +2841,604 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="Suora yhdysviiva 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B20BF5B7-A5F1-43F1-A73A-5D5EB42C5839}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="17802225" y="2266950"/>
+          <a:ext cx="3267075" cy="1704975"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="Suora nuoliyhdysviiva 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D055F5F4-E4B2-4C72-BC6F-29A9705FE712}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21059775" y="2266950"/>
+          <a:ext cx="323850" cy="514350"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>323851</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>28576</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Vapaamuotoinen: Muoto 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63F3C0F9-C64E-44D9-BF30-E70DD1B24A67}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5810539">
+          <a:off x="21250276" y="2914649"/>
+          <a:ext cx="257175" cy="314325"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="csX0" fmla="*/ 0 w 257175"/>
+            <a:gd name="csY0" fmla="*/ 0 h 314325"/>
+            <a:gd name="csX1" fmla="*/ 47625 w 257175"/>
+            <a:gd name="csY1" fmla="*/ 314325 h 314325"/>
+            <a:gd name="csX2" fmla="*/ 257175 w 257175"/>
+            <a:gd name="csY2" fmla="*/ 85725 h 314325"/>
+            <a:gd name="csX3" fmla="*/ 0 w 257175"/>
+            <a:gd name="csY3" fmla="*/ 0 h 314325"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="0">
+              <a:pos x="csX0" y="csY0"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX1" y="csY1"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX2" y="csY2"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX3" y="csY3"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="257175" h="314325">
+              <a:moveTo>
+                <a:pt x="0" y="0"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="47625" y="314325"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="257175" y="85725"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="0"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-FI" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Ellipsi 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55E3DDB5-02C1-4D7E-A52B-8730F6E78C00}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21326475" y="3143250"/>
+          <a:ext cx="123825" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-FI" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Ellipsi 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B786A94D-EECF-46C7-B03E-8165B039BC9F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21107400" y="2933700"/>
+          <a:ext cx="123825" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-FI" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="20" name="Suora nuoliyhdysviiva 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75F57A5E-A9CE-10D8-42F4-769D3826771E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18411825" y="3657600"/>
+          <a:ext cx="400050" cy="504825"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="21" name="Suora nuoliyhdysviiva 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9828089E-19DF-CE78-3C4F-538B3E561BB0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19002375" y="3333750"/>
+          <a:ext cx="400050" cy="504825"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="22" name="Suora nuoliyhdysviiva 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44DAB53D-9096-83C8-67D2-B02B8913FB52}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19621500" y="2990850"/>
+          <a:ext cx="400050" cy="504825"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="23" name="Suora nuoliyhdysviiva 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B7E9C36-C0BA-EEFD-267C-299A8D885B1D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20278725" y="2667000"/>
+          <a:ext cx="400050" cy="504825"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="Suorakulmio 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82B26A39-1C42-A6D2-FCF6-EA643B4B33F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18002250" y="4648200"/>
+          <a:ext cx="409575" cy="352425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-FI" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -11599,20 +12307,20 @@
     <mergeCell ref="AT84:AT85"/>
   </mergeCells>
   <conditionalFormatting sqref="AK43:AV54">
-    <cfRule type="expression" dxfId="22" priority="2">
+    <cfRule type="expression" dxfId="30" priority="2">
       <formula>ABS(AK43)&lt;0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ43:AZ54">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>ABS(AZ43)&lt;0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR166:BR168">
-    <cfRule type="cellIs" dxfId="20" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="4" operator="equal">
       <formula>"VIRHE!"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="5" operator="equal">
       <formula>"OK!"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20852,30 +21560,30 @@
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="AK66:AV73">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>ABS(AK66)&lt;0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK6:AX60">
-    <cfRule type="expression" dxfId="17" priority="2">
+    <cfRule type="expression" dxfId="25" priority="2">
       <formula>ABS(AK6)&lt;0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK90:AX103">
-    <cfRule type="expression" dxfId="16" priority="3">
+    <cfRule type="expression" dxfId="24" priority="3">
       <formula>ABS(AK90)&lt;0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB46:BB59">
-    <cfRule type="expression" dxfId="15" priority="4">
+    <cfRule type="expression" dxfId="23" priority="4">
       <formula>ABS(BB46)&lt;0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR172:BR174">
-    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="6" operator="equal">
       <formula>"VIRHE!"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="7" operator="equal">
       <formula>"OK!"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -31081,25 +31789,25 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="AK6:AX39 AK40:AN40 AP40:AW40 AK41:AX60 AL67:AN69 AP67:AX69 AL71:AN75 AP71:AX75">
-    <cfRule type="expression" dxfId="12" priority="2">
+    <cfRule type="expression" dxfId="20" priority="2">
       <formula>ABS(AK6)&lt;0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK90:AX106">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>ABS(AK90)&lt;0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB46:BB59">
-    <cfRule type="expression" dxfId="10" priority="5">
+    <cfRule type="expression" dxfId="18" priority="5">
       <formula>ABS(BB46)&lt;0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR172:BR174">
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="6" operator="equal">
       <formula>"VIRHE!"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="7" operator="equal">
       <formula>"OK!"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -32557,9 +33265,6 @@
       </c>
       <c r="Y24" s="154"/>
       <c r="Z24" s="156"/>
-      <c r="AH24" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ24" s="4"/>
       <c r="AK24" s="4"/>
       <c r="AL24" s="4"/>
@@ -36413,6 +37118,5199 @@
     </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
+  <conditionalFormatting sqref="M22:R27">
+    <cfRule type="expression" dxfId="15" priority="6">
+      <formula>ABS(M22)&lt;0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V22:V28 V31:V36">
+    <cfRule type="expression" dxfId="14" priority="5">
+      <formula>ABS(V22)&lt;0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BR166:BR168">
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
+      <formula>"VIRHE!"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="8" operator="equal">
+      <formula>"OK!"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M31:R36">
+    <cfRule type="expression" dxfId="11" priority="4">
+      <formula>ABS(M31)&lt;0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M39:R44">
+    <cfRule type="expression" dxfId="10" priority="3">
+      <formula>ABS(M39)&lt;0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M13:R18">
+    <cfRule type="expression" dxfId="9" priority="2">
+      <formula>ABS(M13)&lt;0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T13:Y18">
+    <cfRule type="expression" dxfId="8" priority="1">
+      <formula>ABS(T13)&lt;0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79D91F00-706C-4D97-B56A-53C9CBC5D9B4}">
+  <dimension ref="B1:CW227"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="4" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.140625" style="1"/>
+    <col min="19" max="19" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.140625" style="1"/>
+    <col min="21" max="21" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.140625" style="1"/>
+    <col min="29" max="29" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="35" width="9.140625" style="1"/>
+    <col min="36" max="36" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="43" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="48" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="9.140625" style="1"/>
+    <col min="50" max="53" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="62" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="63" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="23"/>
+      <c r="F3" s="24"/>
+      <c r="L3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y3" s="24"/>
+    </row>
+    <row r="4" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="35">
+        <v>45</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L4" s="9"/>
+      <c r="M4" s="78">
+        <v>1</v>
+      </c>
+      <c r="N4" s="78">
+        <v>2</v>
+      </c>
+      <c r="O4" s="78">
+        <v>3</v>
+      </c>
+      <c r="P4" s="78">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="78">
+        <v>5</v>
+      </c>
+      <c r="R4" s="78">
+        <v>6</v>
+      </c>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="25"/>
+      <c r="AZ4" s="2"/>
+    </row>
+    <row r="5" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B5" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="25">
+        <f>COS(RADIANS(E4))</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="5">
+        <f>SIN(RADIANS(E4))</f>
+        <v>0.70710678118654746</v>
+      </c>
+      <c r="L5" s="78">
+        <v>1</v>
+      </c>
+      <c r="M5" s="11">
+        <f t="shared" ref="M5:R10" si="0">B20</f>
+        <v>262664.06250000006</v>
+      </c>
+      <c r="N5" s="11">
+        <f t="shared" si="0"/>
+        <v>262335.9375</v>
+      </c>
+      <c r="O5" s="11">
+        <f t="shared" si="0"/>
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="P5" s="11">
+        <f t="shared" si="0"/>
+        <v>-262664.06250000006</v>
+      </c>
+      <c r="Q5" s="11">
+        <f t="shared" si="0"/>
+        <v>-262335.9375</v>
+      </c>
+      <c r="R5" s="11">
+        <f t="shared" si="0"/>
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="S5" s="7">
+        <f>I20</f>
+        <v>14142.13562373095</v>
+      </c>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="25"/>
+      <c r="AW5" s="4"/>
+      <c r="BA5" s="4"/>
+      <c r="BB5" s="4"/>
+      <c r="BC5" s="4"/>
+      <c r="BD5" s="4"/>
+      <c r="BE5" s="4"/>
+      <c r="BF5" s="4"/>
+      <c r="BG5" s="4"/>
+      <c r="BH5" s="4"/>
+      <c r="BI5" s="4"/>
+      <c r="BJ5" s="4"/>
+      <c r="BK5" s="4"/>
+      <c r="BL5" s="4"/>
+      <c r="BM5" s="4"/>
+    </row>
+    <row r="6" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="5">
+        <v>4000</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="78">
+        <v>2</v>
+      </c>
+      <c r="M6" s="11">
+        <f t="shared" si="0"/>
+        <v>262335.9375</v>
+      </c>
+      <c r="N6" s="11">
+        <f t="shared" si="0"/>
+        <v>262664.06249999994</v>
+      </c>
+      <c r="O6" s="11">
+        <f t="shared" si="0"/>
+        <v>464038.82515367185</v>
+      </c>
+      <c r="P6" s="11">
+        <f t="shared" si="0"/>
+        <v>-262335.9375</v>
+      </c>
+      <c r="Q6" s="11">
+        <f t="shared" si="0"/>
+        <v>-262664.06249999994</v>
+      </c>
+      <c r="R6" s="11">
+        <f t="shared" si="0"/>
+        <v>464038.82515367185</v>
+      </c>
+      <c r="S6" s="7">
+        <f>I21</f>
+        <v>-14142.135623730952</v>
+      </c>
+      <c r="T6" s="4"/>
+      <c r="U6" s="146"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+      <c r="X6" s="4"/>
+      <c r="Y6" s="25"/>
+      <c r="AW6" s="4"/>
+      <c r="AX6" s="3"/>
+      <c r="AZ6" s="4"/>
+      <c r="BA6" s="4"/>
+      <c r="BB6" s="4"/>
+      <c r="BC6" s="4"/>
+      <c r="BD6" s="4"/>
+      <c r="BE6" s="4"/>
+      <c r="BF6" s="4"/>
+      <c r="BG6" s="4"/>
+      <c r="BH6" s="4"/>
+      <c r="BI6" s="4"/>
+      <c r="BJ6" s="4"/>
+      <c r="BK6" s="4"/>
+      <c r="BL6" s="4"/>
+      <c r="BM6" s="4"/>
+    </row>
+    <row r="7" spans="2:66" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="13">
+        <f>100*100</f>
+        <v>10000</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L7" s="78">
+        <v>3</v>
+      </c>
+      <c r="M7" s="11">
+        <f t="shared" si="0"/>
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="N7" s="11">
+        <f t="shared" si="0"/>
+        <v>464038.82515367185</v>
+      </c>
+      <c r="O7" s="11">
+        <f t="shared" si="0"/>
+        <v>1750000000</v>
+      </c>
+      <c r="P7" s="11">
+        <f t="shared" si="0"/>
+        <v>464038.82515367179</v>
+      </c>
+      <c r="Q7" s="11">
+        <f t="shared" si="0"/>
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="R7" s="11">
+        <f t="shared" si="0"/>
+        <v>875000000</v>
+      </c>
+      <c r="S7" s="7">
+        <f>I22</f>
+        <v>-13333333.333333334</v>
+      </c>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="155"/>
+      <c r="W7" s="4"/>
+      <c r="X7" s="4"/>
+      <c r="Y7" s="27"/>
+      <c r="AW7" s="4"/>
+      <c r="AX7" s="3"/>
+      <c r="AZ7" s="4"/>
+      <c r="BA7" s="4"/>
+      <c r="BB7" s="4"/>
+      <c r="BC7" s="4"/>
+      <c r="BD7" s="4"/>
+      <c r="BE7" s="4"/>
+      <c r="BF7" s="4"/>
+      <c r="BG7" s="4"/>
+      <c r="BH7" s="4"/>
+      <c r="BI7" s="4"/>
+      <c r="BJ7" s="4"/>
+      <c r="BK7" s="4"/>
+      <c r="BL7" s="4"/>
+      <c r="BM7" s="4"/>
+    </row>
+    <row r="8" spans="2:66" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="B8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="13">
+        <f>100*100^3/12</f>
+        <v>8333333.333333333</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L8" s="78">
+        <v>4</v>
+      </c>
+      <c r="M8" s="11">
+        <f t="shared" si="0"/>
+        <v>-262664.06250000006</v>
+      </c>
+      <c r="N8" s="11">
+        <f t="shared" si="0"/>
+        <v>-262335.9375</v>
+      </c>
+      <c r="O8" s="11">
+        <f t="shared" si="0"/>
+        <v>464038.82515367179</v>
+      </c>
+      <c r="P8" s="11">
+        <f t="shared" si="0"/>
+        <v>262664.06250000006</v>
+      </c>
+      <c r="Q8" s="11">
+        <f t="shared" si="0"/>
+        <v>262335.9375</v>
+      </c>
+      <c r="R8" s="11">
+        <f t="shared" si="0"/>
+        <v>464038.82515367179</v>
+      </c>
+      <c r="S8" s="7">
+        <f>I23</f>
+        <v>14142.13562373095</v>
+      </c>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+      <c r="X8" s="4"/>
+      <c r="Y8" s="27"/>
+      <c r="AW8" s="4"/>
+      <c r="AX8" s="3"/>
+      <c r="AZ8" s="4"/>
+      <c r="BA8" s="4"/>
+      <c r="BB8" s="4"/>
+      <c r="BC8" s="4"/>
+      <c r="BD8" s="4"/>
+      <c r="BE8" s="4"/>
+      <c r="BF8" s="4"/>
+      <c r="BG8" s="4"/>
+      <c r="BH8" s="4"/>
+      <c r="BI8" s="4"/>
+      <c r="BJ8" s="4"/>
+      <c r="BK8" s="4"/>
+      <c r="BL8" s="4"/>
+      <c r="BM8" s="4"/>
+    </row>
+    <row r="9" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="13">
+        <f>210*10^3</f>
+        <v>210000</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="78">
+        <v>5</v>
+      </c>
+      <c r="M9" s="11">
+        <f t="shared" si="0"/>
+        <v>-262335.9375</v>
+      </c>
+      <c r="N9" s="11">
+        <f t="shared" si="0"/>
+        <v>-262664.06249999994</v>
+      </c>
+      <c r="O9" s="11">
+        <f t="shared" si="0"/>
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="P9" s="11">
+        <f t="shared" si="0"/>
+        <v>262335.9375</v>
+      </c>
+      <c r="Q9" s="11">
+        <f t="shared" si="0"/>
+        <v>262664.06249999994</v>
+      </c>
+      <c r="R9" s="11">
+        <f t="shared" si="0"/>
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="S9" s="7">
+        <f>I24</f>
+        <v>-14142.135623730952</v>
+      </c>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="27"/>
+      <c r="AW9" s="4"/>
+      <c r="AX9" s="3"/>
+      <c r="AZ9" s="4"/>
+      <c r="BA9" s="4"/>
+      <c r="BB9" s="4"/>
+      <c r="BC9" s="4"/>
+      <c r="BD9" s="16"/>
+      <c r="BE9" s="16"/>
+      <c r="BF9" s="16"/>
+      <c r="BG9" s="4"/>
+      <c r="BH9" s="4"/>
+      <c r="BI9" s="4"/>
+      <c r="BJ9" s="16"/>
+      <c r="BK9" s="16"/>
+      <c r="BL9" s="16"/>
+      <c r="BM9" s="16"/>
+      <c r="BN9" s="3"/>
+    </row>
+    <row r="10" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="36">
+        <f>E9*E7</f>
+        <v>2100000000</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L10" s="78">
+        <v>6</v>
+      </c>
+      <c r="M10" s="11">
+        <f t="shared" si="0"/>
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="N10" s="11">
+        <f t="shared" si="0"/>
+        <v>464038.82515367185</v>
+      </c>
+      <c r="O10" s="11">
+        <f t="shared" si="0"/>
+        <v>875000000</v>
+      </c>
+      <c r="P10" s="11">
+        <f t="shared" si="0"/>
+        <v>464038.82515367179</v>
+      </c>
+      <c r="Q10" s="11">
+        <f t="shared" si="0"/>
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="R10" s="11">
+        <f t="shared" si="0"/>
+        <v>1750000000</v>
+      </c>
+      <c r="S10" s="7">
+        <f>I25</f>
+        <v>13333333.333333334</v>
+      </c>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+      <c r="X10" s="4"/>
+      <c r="Y10" s="3"/>
+      <c r="AW10" s="4"/>
+      <c r="AX10" s="3"/>
+      <c r="AZ10" s="4"/>
+      <c r="BA10" s="4"/>
+      <c r="BB10" s="4"/>
+      <c r="BC10" s="4"/>
+      <c r="BD10" s="16"/>
+      <c r="BE10" s="16"/>
+      <c r="BF10" s="16"/>
+      <c r="BG10" s="4"/>
+      <c r="BH10" s="4"/>
+      <c r="BI10" s="4"/>
+      <c r="BJ10" s="16"/>
+      <c r="BK10" s="16"/>
+      <c r="BL10" s="16"/>
+      <c r="BM10" s="16"/>
+    </row>
+    <row r="11" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="36">
+        <f>E9*E8</f>
+        <v>1750000000000</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+      <c r="X11" s="4"/>
+      <c r="Y11" s="3"/>
+      <c r="AW11" s="4"/>
+      <c r="AX11" s="3"/>
+      <c r="AZ11" s="4"/>
+      <c r="BA11" s="4"/>
+      <c r="BB11" s="4"/>
+      <c r="BC11" s="4"/>
+      <c r="BD11" s="16"/>
+      <c r="BE11" s="16"/>
+      <c r="BF11" s="16"/>
+      <c r="BG11" s="4"/>
+      <c r="BH11" s="4"/>
+      <c r="BI11" s="4"/>
+      <c r="BJ11" s="16"/>
+      <c r="BK11" s="16"/>
+      <c r="BL11" s="16"/>
+      <c r="BM11" s="16"/>
+    </row>
+    <row r="12" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="L12" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="O12" s="162">
+        <v>0</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q12" s="162">
+        <v>90</v>
+      </c>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
+      <c r="X12" s="4"/>
+      <c r="AW12" s="4"/>
+      <c r="AZ12" s="4"/>
+      <c r="BA12" s="4"/>
+      <c r="BB12" s="4"/>
+      <c r="BC12" s="4"/>
+      <c r="BD12" s="4"/>
+      <c r="BE12" s="4"/>
+      <c r="BF12" s="4"/>
+      <c r="BG12" s="4"/>
+      <c r="BH12" s="4"/>
+      <c r="BI12" s="4"/>
+      <c r="BJ12" s="4"/>
+      <c r="BK12" s="4"/>
+      <c r="BL12" s="4"/>
+      <c r="BM12" s="16"/>
+    </row>
+    <row r="13" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L13" s="78">
+        <v>1</v>
+      </c>
+      <c r="M13" s="11">
+        <f>COS(RADIANS(O12))</f>
+        <v>1</v>
+      </c>
+      <c r="N13" s="11">
+        <f>SIN(RADIANS(O12))</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="11">
+        <v>0</v>
+      </c>
+      <c r="P13" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>0</v>
+      </c>
+      <c r="R13" s="11">
+        <v>0</v>
+      </c>
+      <c r="S13" s="4"/>
+      <c r="T13" s="11" cm="1">
+        <f t="array" ref="T13:Y18">TRANSPOSE(M13:R18)</f>
+        <v>1</v>
+      </c>
+      <c r="U13" s="11">
+        <v>0</v>
+      </c>
+      <c r="V13" s="11">
+        <v>0</v>
+      </c>
+      <c r="W13" s="11">
+        <v>0</v>
+      </c>
+      <c r="X13" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AW13" s="4"/>
+      <c r="AZ13" s="4"/>
+      <c r="BA13" s="4"/>
+      <c r="BB13" s="4"/>
+      <c r="BC13" s="4"/>
+      <c r="BD13" s="4"/>
+      <c r="BE13" s="4"/>
+      <c r="BF13" s="4"/>
+      <c r="BG13" s="4"/>
+      <c r="BH13" s="4"/>
+      <c r="BI13" s="4"/>
+      <c r="BJ13" s="4"/>
+      <c r="BK13" s="4"/>
+      <c r="BL13" s="4"/>
+      <c r="BM13" s="4"/>
+    </row>
+    <row r="14" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="14">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L14" s="78">
+        <v>2</v>
+      </c>
+      <c r="M14" s="11">
+        <f>-SIN(RADIANS(O12))</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="11">
+        <f>COS(RADIANS(O12))</f>
+        <v>1</v>
+      </c>
+      <c r="O14" s="11">
+        <v>0</v>
+      </c>
+      <c r="P14" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>0</v>
+      </c>
+      <c r="R14" s="11">
+        <v>0</v>
+      </c>
+      <c r="S14" s="4"/>
+      <c r="T14" s="11">
+        <v>0</v>
+      </c>
+      <c r="U14" s="11">
+        <v>1</v>
+      </c>
+      <c r="V14" s="11">
+        <v>0</v>
+      </c>
+      <c r="W14" s="11">
+        <v>0</v>
+      </c>
+      <c r="X14" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AW14" s="4"/>
+      <c r="AZ14" s="4"/>
+      <c r="BA14" s="4"/>
+      <c r="BB14" s="4"/>
+      <c r="BC14" s="4"/>
+      <c r="BD14" s="4"/>
+      <c r="BE14" s="4"/>
+      <c r="BF14" s="4"/>
+      <c r="BG14" s="4"/>
+      <c r="BH14" s="4"/>
+      <c r="BI14" s="4"/>
+      <c r="BJ14" s="4"/>
+      <c r="BK14" s="4"/>
+      <c r="BL14" s="4"/>
+      <c r="BM14" s="4"/>
+    </row>
+    <row r="15" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="14">
+        <v>10</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L15" s="78">
+        <v>3</v>
+      </c>
+      <c r="M15" s="11">
+        <v>0</v>
+      </c>
+      <c r="N15" s="11">
+        <v>0</v>
+      </c>
+      <c r="O15" s="11">
+        <v>1</v>
+      </c>
+      <c r="P15" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="11">
+        <v>0</v>
+      </c>
+      <c r="R15" s="11">
+        <v>0</v>
+      </c>
+      <c r="S15" s="4"/>
+      <c r="T15" s="11">
+        <v>0</v>
+      </c>
+      <c r="U15" s="11">
+        <v>0</v>
+      </c>
+      <c r="V15" s="11">
+        <v>1</v>
+      </c>
+      <c r="W15" s="11">
+        <v>0</v>
+      </c>
+      <c r="X15" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="11">
+        <v>0</v>
+      </c>
+      <c r="AW15" s="4"/>
+      <c r="AX15" s="12"/>
+      <c r="AZ15" s="4"/>
+      <c r="BA15" s="4"/>
+      <c r="BB15" s="4"/>
+      <c r="BC15" s="4"/>
+      <c r="BD15" s="16"/>
+      <c r="BE15" s="16"/>
+      <c r="BF15" s="16"/>
+      <c r="BG15" s="4"/>
+      <c r="BH15" s="4"/>
+      <c r="BI15" s="4"/>
+      <c r="BJ15" s="16"/>
+      <c r="BK15" s="16"/>
+      <c r="BL15" s="16"/>
+      <c r="BM15" s="16"/>
+      <c r="BN15" s="16"/>
+    </row>
+    <row r="16" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="E16" s="3"/>
+      <c r="L16" s="78">
+        <v>4</v>
+      </c>
+      <c r="M16" s="11">
+        <v>0</v>
+      </c>
+      <c r="N16" s="11">
+        <v>0</v>
+      </c>
+      <c r="O16" s="11">
+        <v>0</v>
+      </c>
+      <c r="P16" s="11">
+        <f>COS(RADIANS(Q12))</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="Q16" s="11">
+        <f>SIN(RADIANS(Q12))</f>
+        <v>1</v>
+      </c>
+      <c r="R16" s="11">
+        <v>0</v>
+      </c>
+      <c r="T16" s="11">
+        <v>0</v>
+      </c>
+      <c r="U16" s="11">
+        <v>0</v>
+      </c>
+      <c r="V16" s="11">
+        <v>0</v>
+      </c>
+      <c r="W16" s="11">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="X16" s="11">
+        <v>-1</v>
+      </c>
+      <c r="Y16" s="11">
+        <v>0</v>
+      </c>
+      <c r="AW16" s="4"/>
+      <c r="AX16" s="12"/>
+      <c r="AZ16" s="4"/>
+      <c r="BA16" s="4"/>
+      <c r="BB16" s="4"/>
+      <c r="BC16" s="4"/>
+      <c r="BD16" s="16"/>
+      <c r="BE16" s="16"/>
+      <c r="BF16" s="16"/>
+      <c r="BG16" s="4"/>
+      <c r="BH16" s="4"/>
+      <c r="BI16" s="4"/>
+      <c r="BJ16" s="16"/>
+      <c r="BK16" s="16"/>
+      <c r="BL16" s="16"/>
+      <c r="BM16" s="16"/>
+      <c r="BN16" s="12"/>
+    </row>
+    <row r="17" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="L17" s="78">
+        <v>5</v>
+      </c>
+      <c r="M17" s="11">
+        <v>0</v>
+      </c>
+      <c r="N17" s="11">
+        <v>0</v>
+      </c>
+      <c r="O17" s="11">
+        <v>0</v>
+      </c>
+      <c r="P17" s="11">
+        <f>-SIN(RADIANS(Q12))</f>
+        <v>-1</v>
+      </c>
+      <c r="Q17" s="11">
+        <f>COS(RADIANS(Q12))</f>
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="R17" s="11">
+        <v>0</v>
+      </c>
+      <c r="T17" s="11">
+        <v>0</v>
+      </c>
+      <c r="U17" s="11">
+        <v>0</v>
+      </c>
+      <c r="V17" s="11">
+        <v>0</v>
+      </c>
+      <c r="W17" s="11">
+        <v>1</v>
+      </c>
+      <c r="X17" s="11">
+        <v>6.1257422745431001E-17</v>
+      </c>
+      <c r="Y17" s="11">
+        <v>0</v>
+      </c>
+      <c r="AW17" s="4"/>
+      <c r="AX17" s="12"/>
+      <c r="AZ17" s="4"/>
+      <c r="BA17" s="4"/>
+      <c r="BB17" s="4"/>
+      <c r="BC17" s="4"/>
+      <c r="BD17" s="16"/>
+      <c r="BE17" s="16"/>
+      <c r="BF17" s="16"/>
+      <c r="BG17" s="4"/>
+      <c r="BH17" s="4"/>
+      <c r="BI17" s="4"/>
+      <c r="BJ17" s="16"/>
+      <c r="BK17" s="16"/>
+      <c r="BL17" s="16"/>
+      <c r="BM17" s="16"/>
+      <c r="BN17" s="12"/>
+    </row>
+    <row r="18" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="L18" s="78">
+        <v>6</v>
+      </c>
+      <c r="M18" s="11">
+        <v>0</v>
+      </c>
+      <c r="N18" s="11">
+        <v>0</v>
+      </c>
+      <c r="O18" s="11">
+        <v>0</v>
+      </c>
+      <c r="P18" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="11">
+        <v>0</v>
+      </c>
+      <c r="R18" s="11">
+        <v>1</v>
+      </c>
+      <c r="T18" s="11">
+        <v>0</v>
+      </c>
+      <c r="U18" s="11">
+        <v>0</v>
+      </c>
+      <c r="V18" s="11">
+        <v>0</v>
+      </c>
+      <c r="W18" s="11">
+        <v>0</v>
+      </c>
+      <c r="X18" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="11">
+        <v>1</v>
+      </c>
+      <c r="AM18" s="4"/>
+      <c r="AN18" s="4"/>
+      <c r="AO18" s="4"/>
+      <c r="AP18" s="4"/>
+      <c r="AQ18" s="4"/>
+      <c r="AR18" s="4"/>
+      <c r="AS18" s="4"/>
+      <c r="AT18" s="4"/>
+      <c r="AU18" s="4"/>
+      <c r="AV18" s="4"/>
+      <c r="AW18" s="4"/>
+      <c r="AX18" s="4"/>
+      <c r="AZ18" s="4"/>
+      <c r="BA18" s="4"/>
+      <c r="BB18" s="4"/>
+      <c r="BC18" s="4"/>
+      <c r="BD18" s="16"/>
+      <c r="BE18" s="16"/>
+      <c r="BF18" s="4"/>
+      <c r="BG18" s="16"/>
+      <c r="BH18" s="4"/>
+      <c r="BI18" s="4"/>
+      <c r="BJ18" s="4"/>
+      <c r="BK18" s="16"/>
+      <c r="BL18" s="16"/>
+      <c r="BM18" s="4"/>
+      <c r="BN18" s="16"/>
+    </row>
+    <row r="19" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC19" s="2"/>
+      <c r="AM19" s="4"/>
+      <c r="AN19" s="7"/>
+      <c r="AO19" s="4"/>
+      <c r="AP19" s="4"/>
+      <c r="AQ19" s="4"/>
+      <c r="AR19" s="4"/>
+      <c r="AS19" s="4"/>
+      <c r="AT19" s="4"/>
+      <c r="AU19" s="7"/>
+      <c r="AV19" s="4"/>
+      <c r="AW19" s="4"/>
+      <c r="AX19" s="4"/>
+      <c r="AZ19" s="4"/>
+      <c r="BA19" s="4"/>
+      <c r="BB19" s="4"/>
+      <c r="BC19" s="4"/>
+      <c r="BD19" s="16"/>
+      <c r="BE19" s="16"/>
+      <c r="BF19" s="4"/>
+      <c r="BG19" s="16"/>
+      <c r="BH19" s="4"/>
+      <c r="BI19" s="4"/>
+      <c r="BJ19" s="4"/>
+      <c r="BK19" s="16"/>
+      <c r="BL19" s="16"/>
+      <c r="BM19" s="4"/>
+      <c r="BN19" s="16"/>
+    </row>
+    <row r="20" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B20" s="37">
+        <f t="shared" ref="B20:G25" si="1">$B36*B$45+$C36*B$46+$D36*B$47+$E36*B$48+$F36*B$49+$G36*B$50</f>
+        <v>262664.06250000006</v>
+      </c>
+      <c r="C20" s="37">
+        <f t="shared" si="1"/>
+        <v>262335.9375</v>
+      </c>
+      <c r="D20" s="37">
+        <f t="shared" si="1"/>
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="E20" s="37">
+        <f t="shared" si="1"/>
+        <v>-262664.06250000006</v>
+      </c>
+      <c r="F20" s="37">
+        <f t="shared" si="1"/>
+        <v>-262335.9375</v>
+      </c>
+      <c r="G20" s="37">
+        <f t="shared" si="1"/>
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="I20" s="151">
+        <f>B54*I28+C54*I29+D54*I30+E54*I31+F54*I32+G54*I33</f>
+        <v>14142.13562373095</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S20" s="4"/>
+      <c r="T20" s="4"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="4"/>
+      <c r="X20" s="4"/>
+      <c r="Y20" s="3"/>
+      <c r="AJ20" s="2"/>
+    </row>
+    <row r="21" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B21" s="37">
+        <f t="shared" si="1"/>
+        <v>262335.9375</v>
+      </c>
+      <c r="C21" s="37">
+        <f t="shared" si="1"/>
+        <v>262664.06249999994</v>
+      </c>
+      <c r="D21" s="37">
+        <f t="shared" si="1"/>
+        <v>464038.82515367185</v>
+      </c>
+      <c r="E21" s="37">
+        <f t="shared" si="1"/>
+        <v>-262335.9375</v>
+      </c>
+      <c r="F21" s="37">
+        <f t="shared" si="1"/>
+        <v>-262664.06249999994</v>
+      </c>
+      <c r="G21" s="37">
+        <f t="shared" si="1"/>
+        <v>464038.82515367185</v>
+      </c>
+      <c r="I21" s="151">
+        <f>B55*I28+C55*I29+D55*I30+E55*I31+F55*I32+G55*I33</f>
+        <v>-14142.135623730952</v>
+      </c>
+      <c r="L21" s="9"/>
+      <c r="M21" s="78">
+        <v>1</v>
+      </c>
+      <c r="N21" s="78">
+        <v>2</v>
+      </c>
+      <c r="O21" s="78">
+        <v>3</v>
+      </c>
+      <c r="P21" s="78">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="78">
+        <v>5</v>
+      </c>
+      <c r="R21" s="78">
+        <v>6</v>
+      </c>
+      <c r="S21" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="T21" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="U21" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="V21" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="X21" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y21" s="80"/>
+      <c r="Z21" s="80" t="s">
+        <v>88</v>
+      </c>
+      <c r="AK21" s="4"/>
+      <c r="AL21" s="4"/>
+      <c r="AM21" s="4"/>
+      <c r="AN21" s="4"/>
+      <c r="AO21" s="4"/>
+      <c r="AP21" s="4"/>
+      <c r="AQ21" s="4"/>
+      <c r="AR21" s="4"/>
+      <c r="AS21" s="4"/>
+      <c r="AT21" s="4"/>
+      <c r="AU21" s="4"/>
+      <c r="AV21" s="4"/>
+      <c r="AW21" s="4"/>
+    </row>
+    <row r="22" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B22" s="37">
+        <f t="shared" si="1"/>
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="C22" s="37">
+        <f t="shared" si="1"/>
+        <v>464038.82515367185</v>
+      </c>
+      <c r="D22" s="37">
+        <f t="shared" si="1"/>
+        <v>1750000000</v>
+      </c>
+      <c r="E22" s="37">
+        <f t="shared" si="1"/>
+        <v>464038.82515367179</v>
+      </c>
+      <c r="F22" s="37">
+        <f t="shared" si="1"/>
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="G22" s="37">
+        <f>-1*$B38*G$45+$C38*G$46+$D38*G$47+$E38*G$48+$F38*G$49+$G38*G$50</f>
+        <v>875000000</v>
+      </c>
+      <c r="I22" s="151">
+        <f>B56*I28+C56*I29+D56*I30+E56*I31+F56*I32+G56*I33</f>
+        <v>-13333333.333333334</v>
+      </c>
+      <c r="L22" s="78">
+        <v>1</v>
+      </c>
+      <c r="M22" s="11">
+        <f>(M5+BA6+AK22)</f>
+        <v>262664.06250000006</v>
+      </c>
+      <c r="N22" s="11">
+        <f>(N5+BB6+AL22)</f>
+        <v>262335.9375</v>
+      </c>
+      <c r="O22" s="11">
+        <f>O5+BC6+AM22</f>
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="P22" s="11">
+        <f>P5+BD6+AN22</f>
+        <v>-262664.06250000006</v>
+      </c>
+      <c r="Q22" s="11">
+        <f>Q5+BE6+AO22</f>
+        <v>-262335.9375</v>
+      </c>
+      <c r="R22" s="11">
+        <f>R5+BF6+AP22</f>
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="T22" s="4">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <f>S5</f>
+        <v>14142.13562373095</v>
+      </c>
+      <c r="W22" s="144" t="s">
+        <v>52</v>
+      </c>
+      <c r="X22" s="153" cm="1">
+        <f t="array" ref="X22:X24">T22:T24</f>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="4"/>
+      <c r="Z22" s="4"/>
+      <c r="AJ22" s="4"/>
+      <c r="AK22" s="4"/>
+      <c r="AL22" s="4"/>
+      <c r="AM22" s="4"/>
+      <c r="AN22" s="4"/>
+      <c r="AO22" s="4"/>
+      <c r="AP22" s="4"/>
+      <c r="AQ22" s="4"/>
+      <c r="AR22" s="4"/>
+      <c r="AS22" s="4"/>
+      <c r="AT22" s="4"/>
+      <c r="AU22" s="4"/>
+      <c r="AV22" s="4"/>
+      <c r="AW22" s="4"/>
+    </row>
+    <row r="23" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B23" s="37">
+        <f t="shared" si="1"/>
+        <v>-262664.06250000006</v>
+      </c>
+      <c r="C23" s="37">
+        <f t="shared" si="1"/>
+        <v>-262335.9375</v>
+      </c>
+      <c r="D23" s="37">
+        <f t="shared" si="1"/>
+        <v>464038.82515367179</v>
+      </c>
+      <c r="E23" s="37">
+        <f t="shared" si="1"/>
+        <v>262664.06250000006</v>
+      </c>
+      <c r="F23" s="37">
+        <f t="shared" si="1"/>
+        <v>262335.9375</v>
+      </c>
+      <c r="G23" s="37">
+        <f>$B39*G$45+$C39*G$46+$D39*G$47+$E39*G$48+$F39*G$49+$G39*G$50</f>
+        <v>464038.82515367179</v>
+      </c>
+      <c r="I23" s="151">
+        <f>B57*I28+C57*I29+D57*I30+E57*I31+F57*I32+G57*I33</f>
+        <v>14142.13562373095</v>
+      </c>
+      <c r="L23" s="78">
+        <v>2</v>
+      </c>
+      <c r="M23" s="11">
+        <f>(M6+BA7+AK23)</f>
+        <v>262335.9375</v>
+      </c>
+      <c r="N23" s="11">
+        <f>(N6+BB7+AL23)</f>
+        <v>262664.06249999994</v>
+      </c>
+      <c r="O23" s="11">
+        <f>O6+BC7+AM23</f>
+        <v>464038.82515367185</v>
+      </c>
+      <c r="P23" s="11">
+        <f>P6+BD7+AN23</f>
+        <v>-262335.9375</v>
+      </c>
+      <c r="Q23" s="11">
+        <f>Q6+BE7+AO23</f>
+        <v>-262664.06249999994</v>
+      </c>
+      <c r="R23" s="11">
+        <f>R6+BF7+AP23</f>
+        <v>464038.82515367185</v>
+      </c>
+      <c r="T23" s="4">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3">
+        <f>S6</f>
+        <v>-14142.135623730952</v>
+      </c>
+      <c r="W23" s="144" t="s">
+        <v>51</v>
+      </c>
+      <c r="X23" s="153">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="154"/>
+      <c r="Z23" s="156"/>
+      <c r="AJ23" s="4"/>
+      <c r="AK23" s="4"/>
+      <c r="AL23" s="4"/>
+      <c r="AM23" s="4"/>
+      <c r="AN23" s="4"/>
+      <c r="AO23" s="4"/>
+      <c r="AP23" s="4"/>
+      <c r="AQ23" s="4"/>
+      <c r="AR23" s="4"/>
+      <c r="AS23" s="4"/>
+      <c r="AT23" s="4"/>
+      <c r="AU23" s="4"/>
+      <c r="AV23" s="4"/>
+      <c r="AW23" s="4"/>
+    </row>
+    <row r="24" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B24" s="37">
+        <f t="shared" si="1"/>
+        <v>-262335.9375</v>
+      </c>
+      <c r="C24" s="37">
+        <f t="shared" si="1"/>
+        <v>-262664.06249999994</v>
+      </c>
+      <c r="D24" s="37">
+        <f t="shared" si="1"/>
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="E24" s="37">
+        <f t="shared" si="1"/>
+        <v>262335.9375</v>
+      </c>
+      <c r="F24" s="37">
+        <f t="shared" si="1"/>
+        <v>262664.06249999994</v>
+      </c>
+      <c r="G24" s="37">
+        <f>$B40*G$45+$C40*G$46+$D40*G$47+$E40*G$48+$F40*G$49+$G40*G$50</f>
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="I24" s="151">
+        <f>B58*I28+C58*I29+D58*I30+E58*I31+F58*I32+G58*I33</f>
+        <v>-14142.135623730952</v>
+      </c>
+      <c r="L24" s="78">
+        <v>3</v>
+      </c>
+      <c r="M24" s="11">
+        <f>M7+BA8+AK24</f>
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="N24" s="11">
+        <f>N7+BB8+AL24</f>
+        <v>464038.82515367185</v>
+      </c>
+      <c r="O24" s="11">
+        <f>O7+BC8+AM24</f>
+        <v>1750000000</v>
+      </c>
+      <c r="P24" s="11">
+        <f>P7+BD8+AN24</f>
+        <v>464038.82515367179</v>
+      </c>
+      <c r="Q24" s="11">
+        <f>Q7+BE8+AO24</f>
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="R24" s="11">
+        <f>R7+BF8+AP24</f>
+        <v>875000000</v>
+      </c>
+      <c r="T24" s="4">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <f>S7</f>
+        <v>-13333333.333333334</v>
+      </c>
+      <c r="X24" s="153">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="154"/>
+      <c r="Z24" s="156"/>
+      <c r="AJ24" s="4"/>
+      <c r="AK24" s="4"/>
+      <c r="AL24" s="4"/>
+      <c r="AM24" s="4"/>
+      <c r="AN24" s="4"/>
+      <c r="AO24" s="4"/>
+      <c r="AP24" s="4"/>
+      <c r="AQ24" s="4"/>
+      <c r="AR24" s="4"/>
+      <c r="AS24" s="4"/>
+      <c r="AT24" s="4"/>
+      <c r="AU24" s="4"/>
+      <c r="AV24" s="4"/>
+      <c r="AW24" s="4"/>
+    </row>
+    <row r="25" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B25" s="37">
+        <f t="shared" si="1"/>
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="C25" s="37">
+        <f t="shared" si="1"/>
+        <v>464038.82515367185</v>
+      </c>
+      <c r="D25" s="37">
+        <f t="shared" si="1"/>
+        <v>875000000</v>
+      </c>
+      <c r="E25" s="37">
+        <f t="shared" si="1"/>
+        <v>464038.82515367179</v>
+      </c>
+      <c r="F25" s="37">
+        <f t="shared" si="1"/>
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="G25" s="37">
+        <f>$B41*G$45+$C41*G$46+$D41*G$47+$E41*G$48+$F41*G$49+$G41*G$50</f>
+        <v>1750000000</v>
+      </c>
+      <c r="I25" s="151">
+        <f>B59*I28+C59*I29+D59*I30+E59*I31+F59*I32+G59*I33</f>
+        <v>13333333.333333334</v>
+      </c>
+      <c r="K25" s="2"/>
+      <c r="L25" s="78">
+        <v>4</v>
+      </c>
+      <c r="M25" s="11">
+        <f>M8+BA9+AK25</f>
+        <v>-262664.06250000006</v>
+      </c>
+      <c r="N25" s="11">
+        <f>N8+BB9+AL25</f>
+        <v>-262335.9375</v>
+      </c>
+      <c r="O25" s="11">
+        <f>O8+BC9+AM25</f>
+        <v>464038.82515367179</v>
+      </c>
+      <c r="P25" s="18">
+        <f>(P8+BD9+AN25)</f>
+        <v>262664.06250000006</v>
+      </c>
+      <c r="Q25" s="18">
+        <f>(Q8+BE9+AO25)</f>
+        <v>262335.9375</v>
+      </c>
+      <c r="R25" s="18">
+        <f>R8+BF9+AP25</f>
+        <v>464038.82515367179</v>
+      </c>
+      <c r="T25" s="4">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <f>S8</f>
+        <v>14142.13562373095</v>
+      </c>
+      <c r="W25" s="144" t="s">
+        <v>111</v>
+      </c>
+      <c r="X25" s="153">
+        <f>U66</f>
+        <v>3.611727685778339E-2</v>
+      </c>
+      <c r="Y25" s="154"/>
+      <c r="Z25" s="156"/>
+      <c r="AJ25" s="4"/>
+      <c r="AK25" s="4"/>
+      <c r="AL25" s="4"/>
+      <c r="AM25" s="4"/>
+      <c r="AN25" s="4"/>
+      <c r="AO25" s="4"/>
+      <c r="AP25" s="4"/>
+      <c r="AQ25" s="4"/>
+      <c r="AR25" s="4"/>
+      <c r="AS25" s="4"/>
+      <c r="AT25" s="4"/>
+      <c r="AU25" s="4"/>
+      <c r="AV25" s="4"/>
+      <c r="AW25" s="4"/>
+    </row>
+    <row r="26" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="I26" s="3"/>
+      <c r="L26" s="78">
+        <v>5</v>
+      </c>
+      <c r="M26" s="11">
+        <f>M9+BA10+AK26</f>
+        <v>-262335.9375</v>
+      </c>
+      <c r="N26" s="11">
+        <f>N9+BB10+AL26</f>
+        <v>-262664.06249999994</v>
+      </c>
+      <c r="O26" s="11">
+        <f>O9+BC10+AM26</f>
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="P26" s="18">
+        <f>(P9+BD10+AN26)</f>
+        <v>262335.9375</v>
+      </c>
+      <c r="Q26" s="18">
+        <f>(Q9+BE10+AO26)</f>
+        <v>262664.06249999994</v>
+      </c>
+      <c r="R26" s="18">
+        <f>R9+BF10+AP26</f>
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="T26" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="V26" s="3">
+        <f>S9</f>
+        <v>-14142.135623730952</v>
+      </c>
+      <c r="W26" s="144" t="s">
+        <v>112</v>
+      </c>
+      <c r="X26" s="153">
+        <f>U67</f>
+        <v>-2.4747869728958443E-18</v>
+      </c>
+      <c r="Y26" s="80"/>
+      <c r="Z26" s="80"/>
+      <c r="AJ26" s="4"/>
+      <c r="AK26" s="4"/>
+      <c r="AL26" s="4"/>
+      <c r="AM26" s="4"/>
+      <c r="AN26" s="4"/>
+      <c r="AO26" s="4"/>
+      <c r="AP26" s="4"/>
+      <c r="AQ26" s="4"/>
+      <c r="AR26" s="4"/>
+      <c r="AS26" s="4"/>
+      <c r="AT26" s="4"/>
+      <c r="AU26" s="4"/>
+      <c r="AV26" s="4"/>
+      <c r="AW26" s="4"/>
+      <c r="AY26" s="2"/>
+    </row>
+    <row r="27" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I27" s="143" t="s">
+        <v>31</v>
+      </c>
+      <c r="L27" s="78">
+        <v>6</v>
+      </c>
+      <c r="M27" s="11">
+        <f>M10+BA11+AK27</f>
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="N27" s="11">
+        <f>N10+BB11+AL27</f>
+        <v>464038.82515367185</v>
+      </c>
+      <c r="O27" s="11">
+        <f>O10+BC11+AM27</f>
+        <v>875000000</v>
+      </c>
+      <c r="P27" s="18">
+        <f>P10+BD11+AN27</f>
+        <v>464038.82515367179</v>
+      </c>
+      <c r="Q27" s="18">
+        <f>Q10+BE11+AO27</f>
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="R27" s="18">
+        <f>R10+BF11+AP27</f>
+        <v>1750000000</v>
+      </c>
+      <c r="T27" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="V27" s="3">
+        <f>S10</f>
+        <v>13333333.333333334</v>
+      </c>
+      <c r="X27" s="157">
+        <f>U60</f>
+        <v>7.6083350071789388E-3</v>
+      </c>
+      <c r="Y27" s="154"/>
+      <c r="Z27" s="156"/>
+      <c r="AJ27" s="4"/>
+      <c r="AK27" s="4"/>
+      <c r="AL27" s="4"/>
+      <c r="AM27" s="4"/>
+      <c r="AN27" s="4"/>
+      <c r="AO27" s="4"/>
+      <c r="AP27" s="4"/>
+      <c r="AQ27" s="4"/>
+      <c r="AR27" s="4"/>
+      <c r="AS27" s="4"/>
+      <c r="AT27" s="4"/>
+      <c r="AU27" s="4"/>
+      <c r="AV27" s="4"/>
+      <c r="AW27" s="4"/>
+      <c r="AY27" s="2"/>
+    </row>
+    <row r="28" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B28" s="38">
+        <f>$E$10/E6</f>
+        <v>525000</v>
+      </c>
+      <c r="C28" s="39">
+        <v>0</v>
+      </c>
+      <c r="D28" s="39">
+        <v>0</v>
+      </c>
+      <c r="E28" s="38">
+        <f>-$E$10/E6</f>
+        <v>-525000</v>
+      </c>
+      <c r="F28" s="39">
+        <v>0</v>
+      </c>
+      <c r="G28" s="39">
+        <v>0</v>
+      </c>
+      <c r="I28" s="38">
+        <f>-E6/2*E15*I38</f>
+        <v>1.22514845490862E-12</v>
+      </c>
+      <c r="T28" s="4"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="144"/>
+      <c r="X28" s="153"/>
+      <c r="Y28" s="154"/>
+      <c r="Z28" s="156"/>
+      <c r="AJ28" s="4"/>
+      <c r="AK28" s="4"/>
+      <c r="AL28" s="4"/>
+      <c r="AM28" s="4"/>
+      <c r="AN28" s="4"/>
+      <c r="AO28" s="4"/>
+      <c r="AP28" s="4"/>
+      <c r="AQ28" s="16"/>
+      <c r="AR28" s="16"/>
+      <c r="AS28" s="16"/>
+      <c r="AT28" s="16"/>
+      <c r="AU28" s="16"/>
+      <c r="AV28" s="16"/>
+      <c r="AW28" s="4"/>
+      <c r="AX28" s="3"/>
+      <c r="AY28" s="8"/>
+    </row>
+    <row r="29" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B29" s="39">
+        <v>0</v>
+      </c>
+      <c r="C29" s="38">
+        <f>(12*$E$11)/$E$6^3</f>
+        <v>328.125</v>
+      </c>
+      <c r="D29" s="38">
+        <f>(6*$E$11)/$E$6^2</f>
+        <v>656250</v>
+      </c>
+      <c r="E29" s="39">
+        <v>0</v>
+      </c>
+      <c r="F29" s="38">
+        <f>-(12*$E$11)/$E$6^3</f>
+        <v>-328.125</v>
+      </c>
+      <c r="G29" s="38">
+        <f>(6*$E$11)/$E$6^2</f>
+        <v>656250</v>
+      </c>
+      <c r="I29" s="38">
+        <f>-E6/2*E15*I39</f>
+        <v>-20000</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="T29" s="4"/>
+      <c r="V29" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="W29" s="144"/>
+      <c r="X29" s="153"/>
+      <c r="Y29" s="155"/>
+      <c r="Z29" s="4"/>
+      <c r="AJ29" s="4"/>
+      <c r="AK29" s="4"/>
+      <c r="AL29" s="4"/>
+      <c r="AM29" s="4"/>
+      <c r="AN29" s="4"/>
+      <c r="AO29" s="4"/>
+      <c r="AP29" s="4"/>
+      <c r="AQ29" s="16"/>
+      <c r="AR29" s="16"/>
+      <c r="AS29" s="16"/>
+      <c r="AT29" s="16"/>
+      <c r="AU29" s="16"/>
+      <c r="AV29" s="16"/>
+      <c r="AW29" s="4"/>
+      <c r="AX29" s="3"/>
+      <c r="AY29" s="10"/>
+    </row>
+    <row r="30" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B30" s="39">
+        <v>0</v>
+      </c>
+      <c r="C30" s="38">
+        <f>(6*$E$11)/$E$6^2</f>
+        <v>656250</v>
+      </c>
+      <c r="D30" s="38">
+        <f>4*$E$11/$E$6</f>
+        <v>1750000000</v>
+      </c>
+      <c r="E30" s="39">
+        <v>0</v>
+      </c>
+      <c r="F30" s="38">
+        <f>-(6*$E$11)/$E$6^2</f>
+        <v>-656250</v>
+      </c>
+      <c r="G30" s="38">
+        <f>2*$E$11/$E$6</f>
+        <v>875000000</v>
+      </c>
+      <c r="I30" s="38">
+        <f>-1*(E15*E6^2)/12*I39</f>
+        <v>-13333333.333333334</v>
+      </c>
+      <c r="L30" s="9"/>
+      <c r="M30" s="78">
+        <v>1</v>
+      </c>
+      <c r="N30" s="78">
+        <v>2</v>
+      </c>
+      <c r="O30" s="78">
+        <v>3</v>
+      </c>
+      <c r="P30" s="78">
+        <v>4</v>
+      </c>
+      <c r="Q30" s="78">
+        <v>5</v>
+      </c>
+      <c r="R30" s="78">
+        <v>6</v>
+      </c>
+      <c r="T30" s="4"/>
+      <c r="V30" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="X30" s="153"/>
+      <c r="Y30" s="154"/>
+      <c r="Z30" s="156"/>
+      <c r="AA30" s="4"/>
+      <c r="AJ30" s="4"/>
+      <c r="AK30" s="4"/>
+      <c r="AL30" s="4"/>
+      <c r="AM30" s="4"/>
+      <c r="AN30" s="4"/>
+      <c r="AO30" s="4"/>
+      <c r="AP30" s="4"/>
+      <c r="AQ30" s="16"/>
+      <c r="AR30" s="16"/>
+      <c r="AS30" s="16"/>
+      <c r="AT30" s="16"/>
+      <c r="AU30" s="16"/>
+      <c r="AV30" s="16"/>
+      <c r="AW30" s="4"/>
+      <c r="AX30" s="3"/>
+      <c r="AY30" s="8"/>
+    </row>
+    <row r="31" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B31" s="38">
+        <f>-$E$10/E6</f>
+        <v>-525000</v>
+      </c>
+      <c r="C31" s="39">
+        <v>0</v>
+      </c>
+      <c r="D31" s="39">
+        <v>0</v>
+      </c>
+      <c r="E31" s="38">
+        <f>$E$10/E6</f>
+        <v>525000</v>
+      </c>
+      <c r="F31" s="39">
+        <v>0</v>
+      </c>
+      <c r="G31" s="39">
+        <v>0</v>
+      </c>
+      <c r="I31" s="38">
+        <f>-E6/2*E15*I38</f>
+        <v>1.22514845490862E-12</v>
+      </c>
+      <c r="L31" s="78">
+        <v>1</v>
+      </c>
+      <c r="M31" s="11" cm="1">
+        <f t="array" ref="M31:R36">MMULT(M22:R27,_xlfn.ANCHORARRAY(T13))</f>
+        <v>262664.06250000006</v>
+      </c>
+      <c r="N31" s="11">
+        <v>262335.9375</v>
+      </c>
+      <c r="O31" s="11">
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="P31" s="11">
+        <v>-262335.9375</v>
+      </c>
+      <c r="Q31" s="11">
+        <v>262664.06250000006</v>
+      </c>
+      <c r="R31" s="11">
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="T31" s="4"/>
+      <c r="V31" s="3" cm="1">
+        <f t="array" ref="V31:V36">MMULT(M13:R18,V22:V27)</f>
+        <v>14142.13562373095</v>
+      </c>
+      <c r="X31" s="153"/>
+      <c r="Y31" s="155"/>
+      <c r="Z31" s="4"/>
+      <c r="AJ31" s="4"/>
+      <c r="AK31" s="4"/>
+      <c r="AL31" s="4"/>
+      <c r="AM31" s="4"/>
+      <c r="AN31" s="4"/>
+      <c r="AO31" s="4"/>
+      <c r="AP31" s="4"/>
+      <c r="AQ31" s="16"/>
+      <c r="AR31" s="16"/>
+      <c r="AS31" s="16"/>
+      <c r="AT31" s="16"/>
+      <c r="AU31" s="16"/>
+      <c r="AV31" s="16"/>
+      <c r="AW31" s="4"/>
+      <c r="AX31" s="3"/>
+      <c r="AY31" s="8"/>
+    </row>
+    <row r="32" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B32" s="39">
+        <v>0</v>
+      </c>
+      <c r="C32" s="38">
+        <f>-(12*$E$11)/$E$6^3</f>
+        <v>-328.125</v>
+      </c>
+      <c r="D32" s="38">
+        <f>-(6*$E$11)/$E$6^2</f>
+        <v>-656250</v>
+      </c>
+      <c r="E32" s="39">
+        <v>0</v>
+      </c>
+      <c r="F32" s="38">
+        <f>(12*$E$11)/$E$6^3</f>
+        <v>328.125</v>
+      </c>
+      <c r="G32" s="38">
+        <f>-(6*$E$11)/$E$6^2</f>
+        <v>-656250</v>
+      </c>
+      <c r="I32" s="38">
+        <f>-E6/2*E15*I39</f>
+        <v>-20000</v>
+      </c>
+      <c r="L32" s="78">
+        <v>2</v>
+      </c>
+      <c r="M32" s="11">
+        <v>262335.9375</v>
+      </c>
+      <c r="N32" s="11">
+        <v>262664.06249999994</v>
+      </c>
+      <c r="O32" s="11">
+        <v>464038.82515367185</v>
+      </c>
+      <c r="P32" s="11">
+        <v>-262664.06249999994</v>
+      </c>
+      <c r="Q32" s="11">
+        <v>262335.9375</v>
+      </c>
+      <c r="R32" s="11">
+        <v>464038.82515367185</v>
+      </c>
+      <c r="V32" s="3">
+        <v>-14142.135623730952</v>
+      </c>
+      <c r="AJ32" s="4"/>
+      <c r="AK32" s="4"/>
+      <c r="AL32" s="4"/>
+      <c r="AM32" s="4"/>
+      <c r="AN32" s="4"/>
+      <c r="AO32" s="4"/>
+      <c r="AP32" s="4"/>
+      <c r="AQ32" s="16"/>
+      <c r="AR32" s="16"/>
+      <c r="AS32" s="16"/>
+      <c r="AT32" s="16"/>
+      <c r="AU32" s="16"/>
+      <c r="AV32" s="16"/>
+      <c r="AW32" s="4"/>
+      <c r="AX32" s="3"/>
+      <c r="AY32" s="10"/>
+    </row>
+    <row r="33" spans="2:83" x14ac:dyDescent="0.2">
+      <c r="B33" s="39">
+        <v>0</v>
+      </c>
+      <c r="C33" s="38">
+        <f>(6*$E$11)/$E$6^2</f>
+        <v>656250</v>
+      </c>
+      <c r="D33" s="38">
+        <f>2*$E$11/$E$6</f>
+        <v>875000000</v>
+      </c>
+      <c r="E33" s="39">
+        <v>0</v>
+      </c>
+      <c r="F33" s="38">
+        <f>-(6*$E$11)/$E$6^2</f>
+        <v>-656250</v>
+      </c>
+      <c r="G33" s="38">
+        <f>4*$E$11/$E$6</f>
+        <v>1750000000</v>
+      </c>
+      <c r="I33" s="38">
+        <f>1*(E15*E6^2)/12*I39</f>
+        <v>13333333.333333334</v>
+      </c>
+      <c r="L33" s="78">
+        <v>3</v>
+      </c>
+      <c r="M33" s="11">
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="N33" s="11">
+        <v>464038.82515367185</v>
+      </c>
+      <c r="O33" s="11">
+        <v>1750000000</v>
+      </c>
+      <c r="P33" s="11">
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="Q33" s="11">
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="R33" s="11">
+        <v>875000000</v>
+      </c>
+      <c r="V33" s="3">
+        <v>-13333333.333333334</v>
+      </c>
+      <c r="AJ33" s="4"/>
+      <c r="AK33" s="4"/>
+      <c r="AL33" s="4"/>
+      <c r="AM33" s="4"/>
+      <c r="AN33" s="4"/>
+      <c r="AO33" s="4"/>
+      <c r="AP33" s="4"/>
+      <c r="AQ33" s="16"/>
+      <c r="AR33" s="16"/>
+      <c r="AS33" s="16"/>
+      <c r="AT33" s="16"/>
+      <c r="AU33" s="16"/>
+      <c r="AV33" s="16"/>
+      <c r="AW33" s="4"/>
+      <c r="AX33" s="3"/>
+      <c r="AY33" s="8"/>
+    </row>
+    <row r="34" spans="2:83" x14ac:dyDescent="0.2">
+      <c r="L34" s="78">
+        <v>4</v>
+      </c>
+      <c r="M34" s="11">
+        <v>-262664.06250000006</v>
+      </c>
+      <c r="N34" s="11">
+        <v>-262335.9375</v>
+      </c>
+      <c r="O34" s="11">
+        <v>464038.82515367179</v>
+      </c>
+      <c r="P34" s="11">
+        <v>262335.9375</v>
+      </c>
+      <c r="Q34" s="11">
+        <v>-262664.06250000006</v>
+      </c>
+      <c r="R34" s="11">
+        <v>464038.82515367179</v>
+      </c>
+      <c r="V34" s="3">
+        <v>-14142.135623730952</v>
+      </c>
+      <c r="AB34" s="12"/>
+      <c r="AD34" s="153"/>
+      <c r="AE34" s="155"/>
+      <c r="AF34" s="155"/>
+      <c r="BB34" s="4"/>
+      <c r="BC34" s="4"/>
+      <c r="BD34" s="4"/>
+      <c r="BE34" s="4"/>
+      <c r="BF34" s="4"/>
+      <c r="BG34" s="4"/>
+      <c r="BH34" s="4"/>
+      <c r="BI34" s="4"/>
+      <c r="BJ34" s="4"/>
+      <c r="BK34" s="4"/>
+      <c r="BL34" s="4"/>
+      <c r="BM34" s="4"/>
+      <c r="BN34" s="4"/>
+      <c r="BO34" s="4"/>
+      <c r="BP34" s="4"/>
+    </row>
+    <row r="35" spans="2:83" x14ac:dyDescent="0.2">
+      <c r="B35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L35" s="78">
+        <v>5</v>
+      </c>
+      <c r="M35" s="11">
+        <v>-262335.9375</v>
+      </c>
+      <c r="N35" s="11">
+        <v>-262664.06249999994</v>
+      </c>
+      <c r="O35" s="11">
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="P35" s="11">
+        <v>262664.06249999994</v>
+      </c>
+      <c r="Q35" s="11">
+        <v>-262335.9375</v>
+      </c>
+      <c r="R35" s="11">
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="V35" s="3">
+        <v>-14142.13562373095</v>
+      </c>
+      <c r="AB35" s="12"/>
+      <c r="AD35" s="153"/>
+      <c r="AE35" s="80"/>
+      <c r="AF35" s="80"/>
+      <c r="BF35" s="4"/>
+      <c r="BG35" s="4"/>
+      <c r="BH35" s="4"/>
+      <c r="BI35" s="4"/>
+      <c r="BJ35" s="4"/>
+      <c r="BK35" s="4"/>
+      <c r="BL35" s="4"/>
+      <c r="BM35" s="4"/>
+      <c r="BN35" s="4"/>
+      <c r="BO35" s="4"/>
+      <c r="BP35" s="4"/>
+    </row>
+    <row r="36" spans="2:83" x14ac:dyDescent="0.2">
+      <c r="B36" s="38">
+        <f t="shared" ref="B36:G36" si="2">$B54*B28+$C54*B29+$D54*B30+$E54*B31+$F54*B32+$G54*B33</f>
+        <v>371231.06012293749</v>
+      </c>
+      <c r="C36" s="38">
+        <f t="shared" si="2"/>
+        <v>-232.01941257683589</v>
+      </c>
+      <c r="D36" s="38">
+        <f t="shared" si="2"/>
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="E36" s="38">
+        <f t="shared" si="2"/>
+        <v>-371231.06012293749</v>
+      </c>
+      <c r="F36" s="38">
+        <f t="shared" si="2"/>
+        <v>232.01941257683589</v>
+      </c>
+      <c r="G36" s="38">
+        <f t="shared" si="2"/>
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L36" s="78">
+        <v>6</v>
+      </c>
+      <c r="M36" s="11">
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="N36" s="11">
+        <v>464038.82515367185</v>
+      </c>
+      <c r="O36" s="11">
+        <v>875000000</v>
+      </c>
+      <c r="P36" s="11">
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="Q36" s="11">
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="R36" s="11">
+        <v>1750000000</v>
+      </c>
+      <c r="V36" s="3">
+        <v>13333333.333333334</v>
+      </c>
+      <c r="AB36" s="12"/>
+      <c r="AD36" s="4"/>
+    </row>
+    <row r="37" spans="2:83" x14ac:dyDescent="0.2">
+      <c r="B37" s="38">
+        <f t="shared" ref="B37:G37" si="3">$B55*B28+$C55*B29+$D55*B30+$E55*B31+$F55*B32+$G55*B33</f>
+        <v>371231.06012293743</v>
+      </c>
+      <c r="C37" s="38">
+        <f t="shared" si="3"/>
+        <v>232.01941257683592</v>
+      </c>
+      <c r="D37" s="38">
+        <f t="shared" si="3"/>
+        <v>464038.82515367185</v>
+      </c>
+      <c r="E37" s="38">
+        <f t="shared" si="3"/>
+        <v>-371231.06012293743</v>
+      </c>
+      <c r="F37" s="38">
+        <f t="shared" si="3"/>
+        <v>-232.01941257683592</v>
+      </c>
+      <c r="G37" s="38">
+        <f t="shared" si="3"/>
+        <v>464038.82515367185</v>
+      </c>
+      <c r="I37" s="33">
+        <v>-90</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB37" s="12"/>
+      <c r="AC37" s="4"/>
+      <c r="AD37" s="12"/>
+      <c r="AE37" s="28"/>
+      <c r="AF37" s="28"/>
+    </row>
+    <row r="38" spans="2:83" x14ac:dyDescent="0.2">
+      <c r="B38" s="38">
+        <f t="shared" ref="B38:G38" si="4">$B56*B28+$C56*B29+$D56*B30+$E56*B31+$F56*B32+$G56*B33</f>
+        <v>0</v>
+      </c>
+      <c r="C38" s="38">
+        <f t="shared" si="4"/>
+        <v>656250</v>
+      </c>
+      <c r="D38" s="38">
+        <f t="shared" si="4"/>
+        <v>1750000000</v>
+      </c>
+      <c r="E38" s="38">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="38">
+        <f t="shared" si="4"/>
+        <v>-656250</v>
+      </c>
+      <c r="G38" s="38">
+        <f t="shared" si="4"/>
+        <v>875000000</v>
+      </c>
+      <c r="I38" s="25">
+        <f>-COS(RADIANS(I37))</f>
+        <v>-6.1257422745431001E-17</v>
+      </c>
+      <c r="L38" s="9"/>
+      <c r="M38" s="78">
+        <v>1</v>
+      </c>
+      <c r="N38" s="78">
+        <v>2</v>
+      </c>
+      <c r="O38" s="78">
+        <v>3</v>
+      </c>
+      <c r="P38" s="78">
+        <v>4</v>
+      </c>
+      <c r="Q38" s="78">
+        <v>5</v>
+      </c>
+      <c r="R38" s="78">
+        <v>6</v>
+      </c>
+      <c r="AD38" s="12"/>
+    </row>
+    <row r="39" spans="2:83" x14ac:dyDescent="0.2">
+      <c r="B39" s="38">
+        <f t="shared" ref="B39:G41" si="5">$B57*B$28+$C57*B$29+$D57*B$30+$E57*B$31+$F57*B$32+$G57*B$33</f>
+        <v>-371231.06012293749</v>
+      </c>
+      <c r="C39" s="38">
+        <f t="shared" si="5"/>
+        <v>232.01941257683589</v>
+      </c>
+      <c r="D39" s="38">
+        <f t="shared" si="5"/>
+        <v>464038.82515367179</v>
+      </c>
+      <c r="E39" s="38">
+        <f t="shared" si="5"/>
+        <v>371231.06012293749</v>
+      </c>
+      <c r="F39" s="38">
+        <f t="shared" si="5"/>
+        <v>-232.01941257683589</v>
+      </c>
+      <c r="G39" s="38">
+        <f t="shared" si="5"/>
+        <v>464038.82515367179</v>
+      </c>
+      <c r="I39" s="25">
+        <f>-SIN(RADIANS(I37))</f>
+        <v>1</v>
+      </c>
+      <c r="L39" s="78">
+        <v>1</v>
+      </c>
+      <c r="M39" s="11" cm="1">
+        <f t="array" ref="M39:R44">MMULT(M13:R18,_xlfn.ANCHORARRAY(M31))</f>
+        <v>262664.06250000006</v>
+      </c>
+      <c r="N39" s="11">
+        <v>262335.9375</v>
+      </c>
+      <c r="O39" s="11">
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="P39" s="11">
+        <v>-262335.9375</v>
+      </c>
+      <c r="Q39" s="11">
+        <v>262664.06250000006</v>
+      </c>
+      <c r="R39" s="11">
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="AD39" s="12"/>
+    </row>
+    <row r="40" spans="2:83" x14ac:dyDescent="0.2">
+      <c r="B40" s="38">
+        <f t="shared" si="5"/>
+        <v>-371231.06012293743</v>
+      </c>
+      <c r="C40" s="38">
+        <f t="shared" si="5"/>
+        <v>-232.01941257683592</v>
+      </c>
+      <c r="D40" s="38">
+        <f t="shared" si="5"/>
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="E40" s="38">
+        <f t="shared" si="5"/>
+        <v>371231.06012293743</v>
+      </c>
+      <c r="F40" s="38">
+        <f t="shared" si="5"/>
+        <v>232.01941257683592</v>
+      </c>
+      <c r="G40" s="38">
+        <f t="shared" si="5"/>
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="L40" s="78">
+        <v>2</v>
+      </c>
+      <c r="M40" s="11">
+        <v>262335.9375</v>
+      </c>
+      <c r="N40" s="11">
+        <v>262664.06249999994</v>
+      </c>
+      <c r="O40" s="11">
+        <v>464038.82515367185</v>
+      </c>
+      <c r="P40" s="11">
+        <v>-262664.06249999994</v>
+      </c>
+      <c r="Q40" s="11">
+        <v>262335.9375</v>
+      </c>
+      <c r="R40" s="11">
+        <v>464038.82515367185</v>
+      </c>
+      <c r="AC40" s="4"/>
+      <c r="AD40" s="12"/>
+      <c r="AE40" s="4"/>
+      <c r="AF40" s="4"/>
+    </row>
+    <row r="41" spans="2:83" x14ac:dyDescent="0.2">
+      <c r="B41" s="38">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="C41" s="38">
+        <f t="shared" si="5"/>
+        <v>656250</v>
+      </c>
+      <c r="D41" s="38">
+        <f t="shared" si="5"/>
+        <v>875000000</v>
+      </c>
+      <c r="E41" s="38">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F41" s="38">
+        <f t="shared" si="5"/>
+        <v>-656250</v>
+      </c>
+      <c r="G41" s="38">
+        <f t="shared" si="5"/>
+        <v>1750000000</v>
+      </c>
+      <c r="L41" s="78">
+        <v>3</v>
+      </c>
+      <c r="M41" s="11">
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="N41" s="11">
+        <v>464038.82515367185</v>
+      </c>
+      <c r="O41" s="11">
+        <v>1750000000</v>
+      </c>
+      <c r="P41" s="11">
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="Q41" s="11">
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="R41" s="11">
+        <v>875000000</v>
+      </c>
+      <c r="AD41" s="12"/>
+    </row>
+    <row r="42" spans="2:83" x14ac:dyDescent="0.2">
+      <c r="L42" s="78">
+        <v>4</v>
+      </c>
+      <c r="M42" s="11">
+        <v>-262335.9375</v>
+      </c>
+      <c r="N42" s="11">
+        <v>-262664.06249999994</v>
+      </c>
+      <c r="O42" s="11">
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="P42" s="11">
+        <v>262664.06249999994</v>
+      </c>
+      <c r="Q42" s="11">
+        <v>-262335.9375</v>
+      </c>
+      <c r="R42" s="11">
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="AD42" s="12"/>
+    </row>
+    <row r="43" spans="2:83" x14ac:dyDescent="0.2">
+      <c r="H43" s="27"/>
+      <c r="L43" s="78">
+        <v>5</v>
+      </c>
+      <c r="M43" s="11">
+        <v>262664.06250000006</v>
+      </c>
+      <c r="N43" s="11">
+        <v>262335.9375</v>
+      </c>
+      <c r="O43" s="11">
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="P43" s="11">
+        <v>-262335.9375</v>
+      </c>
+      <c r="Q43" s="11">
+        <v>262664.06250000006</v>
+      </c>
+      <c r="R43" s="11">
+        <v>-464038.82515367179</v>
+      </c>
+    </row>
+    <row r="44" spans="2:83" x14ac:dyDescent="0.2">
+      <c r="B44" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L44" s="78">
+        <v>6</v>
+      </c>
+      <c r="M44" s="11">
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="N44" s="11">
+        <v>464038.82515367185</v>
+      </c>
+      <c r="O44" s="11">
+        <v>875000000</v>
+      </c>
+      <c r="P44" s="11">
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="Q44" s="11">
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="R44" s="11">
+        <v>1750000000</v>
+      </c>
+    </row>
+    <row r="45" spans="2:83" x14ac:dyDescent="0.2">
+      <c r="B45" s="152">
+        <f>$C$5</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="C45" s="152">
+        <f>$E$5</f>
+        <v>0.70710678118654746</v>
+      </c>
+      <c r="D45" s="152">
+        <v>0</v>
+      </c>
+      <c r="E45" s="152">
+        <v>0</v>
+      </c>
+      <c r="F45" s="152">
+        <v>0</v>
+      </c>
+      <c r="G45" s="152">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="29"/>
+      <c r="AF45" s="29"/>
+    </row>
+    <row r="46" spans="2:83" x14ac:dyDescent="0.2">
+      <c r="B46" s="152">
+        <f>-$E$5</f>
+        <v>-0.70710678118654746</v>
+      </c>
+      <c r="C46" s="152">
+        <f>$C$5</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="D46" s="152">
+        <v>0</v>
+      </c>
+      <c r="E46" s="152">
+        <v>0</v>
+      </c>
+      <c r="F46" s="152">
+        <v>0</v>
+      </c>
+      <c r="G46" s="152">
+        <v>0</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="CE46" s="2"/>
+    </row>
+    <row r="47" spans="2:83" x14ac:dyDescent="0.2">
+      <c r="B47" s="152">
+        <v>0</v>
+      </c>
+      <c r="C47" s="152">
+        <v>0</v>
+      </c>
+      <c r="D47" s="152">
+        <v>1</v>
+      </c>
+      <c r="E47" s="152">
+        <v>0</v>
+      </c>
+      <c r="F47" s="152">
+        <v>0</v>
+      </c>
+      <c r="G47" s="152">
+        <v>0</v>
+      </c>
+      <c r="L47" s="9"/>
+      <c r="M47" s="9"/>
+      <c r="N47" s="9">
+        <v>5</v>
+      </c>
+      <c r="O47" s="9">
+        <v>6</v>
+      </c>
+      <c r="R47" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="S47" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="T47" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="U47" s="141" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS47" s="3"/>
+      <c r="CE47" s="2"/>
+    </row>
+    <row r="48" spans="2:83" x14ac:dyDescent="0.2">
+      <c r="B48" s="152">
+        <v>0</v>
+      </c>
+      <c r="C48" s="152">
+        <v>0</v>
+      </c>
+      <c r="D48" s="152">
+        <v>0</v>
+      </c>
+      <c r="E48" s="152">
+        <f>$C$5</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="F48" s="152">
+        <f>$E$5</f>
+        <v>0.70710678118654746</v>
+      </c>
+      <c r="G48" s="152">
+        <v>0</v>
+      </c>
+      <c r="L48" s="9"/>
+      <c r="M48" s="3" cm="1">
+        <f t="array" ref="M48:N49">Q43:R44</f>
+        <v>262664.06250000006</v>
+      </c>
+      <c r="N48" s="1">
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="O48" s="3"/>
+      <c r="P48" s="3"/>
+      <c r="Q48" s="3"/>
+      <c r="R48" s="3"/>
+      <c r="S48" s="7" t="str" cm="1">
+        <f t="array" ref="S48:S49">T26:T27</f>
+        <v>r14</v>
+      </c>
+      <c r="U48" s="145" cm="1">
+        <f t="array" ref="U48:U49">V35:V36</f>
+        <v>-14142.13562373095</v>
+      </c>
+    </row>
+    <row r="49" spans="2:101" x14ac:dyDescent="0.2">
+      <c r="B49" s="152">
+        <v>0</v>
+      </c>
+      <c r="C49" s="152">
+        <v>0</v>
+      </c>
+      <c r="D49" s="152">
+        <v>0</v>
+      </c>
+      <c r="E49" s="152">
+        <f>-$E$5</f>
+        <v>-0.70710678118654746</v>
+      </c>
+      <c r="F49" s="152">
+        <f>$C$5</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="G49" s="152">
+        <v>0</v>
+      </c>
+      <c r="L49" s="9">
+        <v>5</v>
+      </c>
+      <c r="M49" s="3">
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="N49" s="3">
+        <v>1750000000</v>
+      </c>
+      <c r="P49" s="3"/>
+      <c r="Q49" s="3"/>
+      <c r="R49" s="3"/>
+      <c r="S49" s="7" t="str">
+        <v>r16</v>
+      </c>
+      <c r="U49" s="3">
+        <v>13333333.333333334</v>
+      </c>
+      <c r="AH49" s="2"/>
+      <c r="AI49" s="2"/>
+      <c r="CW49" s="2"/>
+    </row>
+    <row r="50" spans="2:101" x14ac:dyDescent="0.2">
+      <c r="B50" s="152">
+        <v>0</v>
+      </c>
+      <c r="C50" s="152">
+        <v>0</v>
+      </c>
+      <c r="D50" s="152">
+        <v>0</v>
+      </c>
+      <c r="E50" s="152">
+        <v>0</v>
+      </c>
+      <c r="F50" s="152">
+        <v>0</v>
+      </c>
+      <c r="G50" s="152">
+        <f>D47</f>
+        <v>1</v>
+      </c>
+      <c r="L50" s="9">
+        <v>6</v>
+      </c>
+      <c r="M50" s="3"/>
+      <c r="P50" s="3"/>
+      <c r="AH50" s="2"/>
+      <c r="AI50" s="2"/>
+      <c r="BK50" s="2"/>
+      <c r="CW50" s="2"/>
+    </row>
+    <row r="51" spans="2:101" x14ac:dyDescent="0.2">
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="Q51" s="3"/>
+      <c r="R51" s="3"/>
+      <c r="U51" s="145"/>
+      <c r="AA51" s="4"/>
+      <c r="AH51" s="8"/>
+      <c r="AI51" s="8"/>
+      <c r="BK51" s="6"/>
+      <c r="BL51" s="6"/>
+      <c r="BM51" s="6"/>
+      <c r="BN51" s="6"/>
+      <c r="BO51" s="6"/>
+      <c r="BP51" s="6"/>
+      <c r="BR51" s="4"/>
+      <c r="BT51" s="4"/>
+      <c r="BV51" s="4"/>
+      <c r="BY51" s="4"/>
+    </row>
+    <row r="52" spans="2:101" x14ac:dyDescent="0.2">
+      <c r="L52" s="4"/>
+      <c r="M52" s="3"/>
+      <c r="Q52" s="3"/>
+      <c r="V52" s="4"/>
+      <c r="X52" s="3"/>
+      <c r="AA52" s="4"/>
+      <c r="AD52" s="4"/>
+      <c r="AH52" s="10"/>
+      <c r="AI52" s="10"/>
+      <c r="BE52" s="16"/>
+      <c r="BK52" s="6"/>
+      <c r="BL52" s="6"/>
+      <c r="BM52" s="6"/>
+      <c r="BN52" s="6"/>
+      <c r="BO52" s="6"/>
+      <c r="BP52" s="6"/>
+      <c r="BR52" s="4"/>
+      <c r="BT52" s="4"/>
+      <c r="BV52" s="4"/>
+      <c r="BY52" s="4"/>
+    </row>
+    <row r="53" spans="2:101" x14ac:dyDescent="0.2">
+      <c r="B53" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I53" s="3"/>
+      <c r="L53" s="4"/>
+      <c r="V53" s="4"/>
+      <c r="AB53" s="12"/>
+      <c r="AD53" s="12"/>
+      <c r="AH53" s="8"/>
+      <c r="AI53" s="8"/>
+      <c r="BE53" s="16"/>
+      <c r="BK53" s="6"/>
+      <c r="BL53" s="6"/>
+      <c r="BM53" s="6"/>
+      <c r="BN53" s="6"/>
+      <c r="BO53" s="6"/>
+      <c r="BP53" s="6"/>
+      <c r="BQ53" s="4"/>
+      <c r="BR53" s="4"/>
+      <c r="BS53" s="4"/>
+      <c r="BT53" s="4"/>
+      <c r="BU53" s="4"/>
+      <c r="BV53" s="4"/>
+      <c r="BW53" s="4"/>
+      <c r="BX53" s="4"/>
+      <c r="BY53" s="4"/>
+    </row>
+    <row r="54" spans="2:101" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="152">
+        <f>$C$5</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="C54" s="152">
+        <f>-$E$5</f>
+        <v>-0.70710678118654746</v>
+      </c>
+      <c r="D54" s="152">
+        <v>0</v>
+      </c>
+      <c r="E54" s="152">
+        <v>0</v>
+      </c>
+      <c r="F54" s="152">
+        <v>0</v>
+      </c>
+      <c r="G54" s="152">
+        <v>0</v>
+      </c>
+      <c r="L54" s="4"/>
+      <c r="V54" s="4"/>
+      <c r="AB54" s="12"/>
+      <c r="AD54" s="12"/>
+      <c r="AH54" s="8"/>
+      <c r="AI54" s="8"/>
+      <c r="BE54" s="16"/>
+      <c r="BK54" s="6"/>
+      <c r="BL54" s="6"/>
+      <c r="BM54" s="6"/>
+      <c r="BN54" s="6"/>
+      <c r="BO54" s="6"/>
+      <c r="BP54" s="6"/>
+      <c r="BR54" s="67"/>
+      <c r="BT54" s="4"/>
+      <c r="BV54" s="4"/>
+      <c r="BY54" s="4"/>
+    </row>
+    <row r="55" spans="2:101" x14ac:dyDescent="0.2">
+      <c r="B55" s="152">
+        <f>$E$5</f>
+        <v>0.70710678118654746</v>
+      </c>
+      <c r="C55" s="152">
+        <f>$C$5</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="D55" s="152">
+        <v>0</v>
+      </c>
+      <c r="E55" s="152">
+        <v>0</v>
+      </c>
+      <c r="F55" s="152">
+        <v>0</v>
+      </c>
+      <c r="G55" s="152">
+        <v>0</v>
+      </c>
+      <c r="L55" s="4"/>
+      <c r="V55" s="4"/>
+      <c r="AB55" s="12"/>
+      <c r="AD55" s="12"/>
+      <c r="AH55" s="10"/>
+      <c r="AI55" s="10"/>
+      <c r="BE55" s="16"/>
+      <c r="BK55" s="6"/>
+      <c r="BL55" s="6"/>
+      <c r="BM55" s="6"/>
+      <c r="BN55" s="6"/>
+      <c r="BO55" s="6"/>
+      <c r="BP55" s="6"/>
+      <c r="BR55" s="67"/>
+      <c r="BT55" s="4"/>
+      <c r="BV55" s="4"/>
+      <c r="BY55" s="4"/>
+    </row>
+    <row r="56" spans="2:101" x14ac:dyDescent="0.2">
+      <c r="B56" s="152">
+        <v>0</v>
+      </c>
+      <c r="C56" s="152">
+        <v>0</v>
+      </c>
+      <c r="D56" s="152">
+        <f>D47</f>
+        <v>1</v>
+      </c>
+      <c r="E56" s="152">
+        <v>0</v>
+      </c>
+      <c r="F56" s="152">
+        <v>0</v>
+      </c>
+      <c r="G56" s="152">
+        <v>0</v>
+      </c>
+      <c r="AB56" s="30"/>
+      <c r="AD56" s="4"/>
+      <c r="AH56" s="8"/>
+      <c r="AI56" s="8"/>
+      <c r="BE56" s="16"/>
+      <c r="BK56" s="6"/>
+      <c r="BL56" s="6"/>
+      <c r="BM56" s="6"/>
+      <c r="BN56" s="6"/>
+      <c r="BO56" s="6"/>
+      <c r="BP56" s="6"/>
+      <c r="BR56" s="67"/>
+      <c r="BT56" s="4"/>
+      <c r="BV56" s="4"/>
+      <c r="BY56" s="4"/>
+    </row>
+    <row r="57" spans="2:101" x14ac:dyDescent="0.2">
+      <c r="B57" s="152">
+        <v>0</v>
+      </c>
+      <c r="C57" s="152">
+        <v>0</v>
+      </c>
+      <c r="D57" s="152">
+        <v>0</v>
+      </c>
+      <c r="E57" s="152">
+        <f>$C$5</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="F57" s="152">
+        <f>-$E$5</f>
+        <v>-0.70710678118654746</v>
+      </c>
+      <c r="G57" s="152">
+        <v>0</v>
+      </c>
+      <c r="U57" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB57" s="4"/>
+      <c r="AD57" s="4"/>
+      <c r="BE57" s="16"/>
+    </row>
+    <row r="58" spans="2:101" x14ac:dyDescent="0.2">
+      <c r="B58" s="152">
+        <v>0</v>
+      </c>
+      <c r="C58" s="152">
+        <v>0</v>
+      </c>
+      <c r="D58" s="152">
+        <v>0</v>
+      </c>
+      <c r="E58" s="152">
+        <f>$E$5</f>
+        <v>0.70710678118654746</v>
+      </c>
+      <c r="F58" s="152">
+        <f>$C$5</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="G58" s="152">
+        <v>0</v>
+      </c>
+      <c r="L58" s="9"/>
+      <c r="M58" s="9">
+        <v>5</v>
+      </c>
+      <c r="N58" s="9">
+        <v>6</v>
+      </c>
+      <c r="O58" s="9"/>
+      <c r="P58" s="9"/>
+      <c r="R58" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="S58" s="141" t="s">
+        <v>50</v>
+      </c>
+      <c r="T58" s="146" t="s">
+        <v>49</v>
+      </c>
+      <c r="U58" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB58" s="30"/>
+      <c r="AC58" s="4"/>
+      <c r="AD58" s="4"/>
+      <c r="AE58" s="28"/>
+      <c r="AF58" s="28"/>
+      <c r="BE58" s="12"/>
+      <c r="BK58" s="2"/>
+    </row>
+    <row r="59" spans="2:101" x14ac:dyDescent="0.2">
+      <c r="B59" s="152">
+        <v>0</v>
+      </c>
+      <c r="C59" s="152">
+        <v>0</v>
+      </c>
+      <c r="D59" s="152">
+        <v>0</v>
+      </c>
+      <c r="E59" s="152">
+        <v>0</v>
+      </c>
+      <c r="F59" s="152">
+        <v>0</v>
+      </c>
+      <c r="G59" s="152">
+        <f>D47</f>
+        <v>1</v>
+      </c>
+      <c r="L59" s="9">
+        <v>5</v>
+      </c>
+      <c r="M59" s="1" cm="1">
+        <f t="array" ref="M59:N60">MINVERSE(_xlfn.ANCHORARRAY(M48))</f>
+        <v>3.8089286644199935E-6</v>
+      </c>
+      <c r="N59" s="1">
+        <v>1.0099947328751306E-9</v>
+      </c>
+      <c r="S59" s="3" cm="1">
+        <f t="array" ref="S59:S60">U48:U49</f>
+        <v>-14142.13562373095</v>
+      </c>
+      <c r="U59" s="153" cm="1">
+        <f t="array" ref="U59:U60">MMULT(_xlfn.ANCHORARRAY(M59),_xlfn.ANCHORARRAY(S59))</f>
+        <v>-4.0399789315008865E-2</v>
+      </c>
+      <c r="V59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="W59" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="AB59" s="30"/>
+      <c r="AC59" s="4"/>
+      <c r="AD59" s="4"/>
+      <c r="AE59" s="28"/>
+      <c r="AF59" s="28"/>
+      <c r="BE59" s="12"/>
+      <c r="BK59" s="7"/>
+      <c r="BL59" s="4"/>
+      <c r="BM59" s="4"/>
+      <c r="BN59" s="4"/>
+      <c r="BO59" s="4"/>
+      <c r="BP59" s="4"/>
+      <c r="BR59" s="4"/>
+      <c r="BT59" s="6"/>
+      <c r="BV59" s="4"/>
+      <c r="BY59" s="65"/>
+      <c r="CA59" s="63"/>
+    </row>
+    <row r="60" spans="2:101" x14ac:dyDescent="0.2">
+      <c r="L60" s="9">
+        <v>6</v>
+      </c>
+      <c r="M60" s="1">
+        <v>1.0099947328751989E-9</v>
+      </c>
+      <c r="N60" s="3">
+        <v>5.7169638672528847E-10</v>
+      </c>
+      <c r="P60" s="3"/>
+      <c r="S60" s="1">
+        <v>13333333.333333334</v>
+      </c>
+      <c r="U60" s="153">
+        <v>7.6083350071789388E-3</v>
+      </c>
+      <c r="V60" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="W60" s="1">
+        <f>1000*U60</f>
+        <v>7.6083350071789386</v>
+      </c>
+      <c r="X60" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB60" s="4"/>
+      <c r="AD60" s="12"/>
+      <c r="BE60" s="12"/>
+      <c r="BK60" s="7"/>
+      <c r="BL60" s="4"/>
+      <c r="BM60" s="4"/>
+      <c r="BN60" s="4"/>
+      <c r="BO60" s="4"/>
+      <c r="BP60" s="4"/>
+      <c r="BR60" s="4"/>
+      <c r="BT60" s="6"/>
+      <c r="BV60" s="4"/>
+      <c r="BY60" s="65"/>
+      <c r="CA60" s="63"/>
+    </row>
+    <row r="61" spans="2:101" x14ac:dyDescent="0.2">
+      <c r="L61" s="9"/>
+      <c r="N61" s="3"/>
+      <c r="P61" s="3"/>
+      <c r="U61" s="153"/>
+      <c r="AB61" s="4"/>
+      <c r="AD61" s="12"/>
+      <c r="BE61" s="12"/>
+      <c r="BF61" s="4"/>
+      <c r="BK61" s="7"/>
+      <c r="BL61" s="4"/>
+      <c r="BM61" s="4"/>
+      <c r="BN61" s="4"/>
+      <c r="BO61" s="4"/>
+      <c r="BP61" s="4"/>
+      <c r="BQ61" s="4"/>
+      <c r="BR61" s="4"/>
+      <c r="BS61" s="4"/>
+      <c r="BT61" s="6"/>
+      <c r="BU61" s="4"/>
+      <c r="BV61" s="4"/>
+      <c r="BW61" s="4"/>
+      <c r="BX61" s="4"/>
+      <c r="BY61" s="65"/>
+      <c r="BZ61" s="4"/>
+      <c r="CA61" s="63"/>
+      <c r="CE61" s="45"/>
+    </row>
+    <row r="62" spans="2:101" x14ac:dyDescent="0.2">
+      <c r="L62" s="9"/>
+      <c r="U62" s="153"/>
+      <c r="AB62" s="12"/>
+      <c r="AD62" s="12"/>
+      <c r="BE62" s="12"/>
+      <c r="BK62" s="7"/>
+      <c r="BL62" s="4"/>
+      <c r="BM62" s="4"/>
+      <c r="BN62" s="4"/>
+      <c r="BO62" s="4"/>
+      <c r="BP62" s="4"/>
+      <c r="BR62" s="4"/>
+      <c r="BT62" s="6"/>
+      <c r="BV62" s="4"/>
+      <c r="BY62" s="65"/>
+      <c r="CA62" s="63"/>
+    </row>
+    <row r="63" spans="2:101" x14ac:dyDescent="0.2">
+      <c r="V63" s="3"/>
+      <c r="X63" s="153"/>
+      <c r="AB63" s="12"/>
+      <c r="AD63" s="12"/>
+      <c r="BE63" s="12"/>
+      <c r="BK63" s="7"/>
+      <c r="BL63" s="4"/>
+      <c r="BM63" s="4"/>
+      <c r="BN63" s="4"/>
+      <c r="BO63" s="4"/>
+      <c r="BP63" s="4"/>
+      <c r="BR63" s="4"/>
+      <c r="BT63" s="6"/>
+      <c r="BV63" s="4"/>
+      <c r="BY63" s="65"/>
+      <c r="CA63" s="63"/>
+    </row>
+    <row r="64" spans="2:101" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3"/>
+      <c r="U64" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="X64" s="153"/>
+      <c r="AB64" s="4"/>
+      <c r="AD64" s="4"/>
+      <c r="BR64" s="66"/>
+    </row>
+    <row r="65" spans="5:74" x14ac:dyDescent="0.2">
+      <c r="U65" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB65" s="4"/>
+      <c r="AD65" s="4"/>
+      <c r="BR65" s="66"/>
+    </row>
+    <row r="66" spans="5:74" x14ac:dyDescent="0.2">
+      <c r="T66" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="U66" s="1">
+        <f>-SIN(Q12)*U59</f>
+        <v>3.611727685778339E-2</v>
+      </c>
+      <c r="V66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB66" s="4"/>
+      <c r="AD66" s="4"/>
+      <c r="BR66" s="66"/>
+    </row>
+    <row r="67" spans="5:74" x14ac:dyDescent="0.2">
+      <c r="I67" s="25"/>
+      <c r="T67" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="U67" s="1">
+        <f>COS(RADIANS(Q12))*U59</f>
+        <v>-2.4747869728958443E-18</v>
+      </c>
+      <c r="V67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BR67" s="66"/>
+    </row>
+    <row r="68" spans="5:74" x14ac:dyDescent="0.2">
+      <c r="BR68" s="66"/>
+    </row>
+    <row r="69" spans="5:74" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BR69" s="66"/>
+    </row>
+    <row r="70" spans="5:74" x14ac:dyDescent="0.2">
+      <c r="E70" s="26"/>
+      <c r="AG70" s="2"/>
+      <c r="AH70" s="2"/>
+    </row>
+    <row r="71" spans="5:74" x14ac:dyDescent="0.2">
+      <c r="AG71" s="2"/>
+      <c r="AH71" s="2"/>
+      <c r="AI71" s="2"/>
+    </row>
+    <row r="72" spans="5:74" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" spans="5:74" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BK73" s="2"/>
+    </row>
+    <row r="74" spans="5:74" x14ac:dyDescent="0.2">
+      <c r="L74" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="BE74" s="12"/>
+      <c r="BK74" s="6"/>
+      <c r="BL74" s="6"/>
+      <c r="BM74" s="6"/>
+      <c r="BN74" s="6"/>
+      <c r="BO74" s="6"/>
+      <c r="BP74" s="6"/>
+      <c r="BR74" s="67"/>
+      <c r="BT74" s="4"/>
+      <c r="BV74" s="68"/>
+    </row>
+    <row r="75" spans="5:74" ht="24" x14ac:dyDescent="0.2">
+      <c r="G75" s="147"/>
+      <c r="L75" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="V75" s="160" t="s">
+        <v>104</v>
+      </c>
+      <c r="X75" s="160" t="s">
+        <v>106</v>
+      </c>
+      <c r="BE75" s="12"/>
+      <c r="BK75" s="6"/>
+      <c r="BL75" s="6"/>
+      <c r="BM75" s="6"/>
+      <c r="BN75" s="6"/>
+      <c r="BO75" s="6"/>
+      <c r="BP75" s="6"/>
+      <c r="BR75" s="67"/>
+      <c r="BT75" s="4"/>
+      <c r="BV75" s="68"/>
+    </row>
+    <row r="76" spans="5:74" x14ac:dyDescent="0.2">
+      <c r="L76" s="9"/>
+      <c r="M76" s="9">
+        <v>1</v>
+      </c>
+      <c r="N76" s="9">
+        <v>2</v>
+      </c>
+      <c r="O76" s="9">
+        <v>3</v>
+      </c>
+      <c r="P76" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q76" s="9">
+        <v>5</v>
+      </c>
+      <c r="R76" s="9">
+        <v>6</v>
+      </c>
+      <c r="S76" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="T76" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="U76" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="V76" s="160"/>
+      <c r="W76" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="X76" s="160"/>
+      <c r="BE76" s="12"/>
+      <c r="BK76" s="6"/>
+      <c r="BL76" s="6"/>
+      <c r="BM76" s="6"/>
+      <c r="BN76" s="6"/>
+      <c r="BO76" s="6"/>
+      <c r="BP76" s="6"/>
+      <c r="BQ76" s="4"/>
+      <c r="BR76" s="67"/>
+      <c r="BS76" s="4"/>
+      <c r="BT76" s="4"/>
+      <c r="BU76" s="4"/>
+      <c r="BV76" s="68"/>
+    </row>
+    <row r="77" spans="5:74" x14ac:dyDescent="0.2">
+      <c r="L77" s="9">
+        <v>1</v>
+      </c>
+      <c r="M77" s="3">
+        <f>B28</f>
+        <v>525000</v>
+      </c>
+      <c r="N77" s="3">
+        <f>C28</f>
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <f>D28</f>
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <f>E28</f>
+        <v>-525000</v>
+      </c>
+      <c r="Q77" s="3">
+        <f>F28</f>
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <f>G28</f>
+        <v>0</v>
+      </c>
+      <c r="T77" s="1" cm="1">
+        <f t="array" ref="T77:T82">MMULT(B45:G50,X22:X27)</f>
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <f>I28</f>
+        <v>1.22514845490862E-12</v>
+      </c>
+      <c r="X77" s="3" cm="1">
+        <f t="array" ref="X77:X82">MMULT(M77:R82,_xlfn.ANCHORARRAY(T77))-V77:V82</f>
+        <v>-13407.854976668563</v>
+      </c>
+      <c r="BE77" s="4"/>
+      <c r="BK77" s="6"/>
+      <c r="BL77" s="6"/>
+      <c r="BM77" s="6"/>
+      <c r="BN77" s="6"/>
+      <c r="BO77" s="6"/>
+      <c r="BP77" s="6"/>
+      <c r="BR77" s="67"/>
+      <c r="BT77" s="4"/>
+      <c r="BV77" s="68"/>
+    </row>
+    <row r="78" spans="5:74" x14ac:dyDescent="0.2">
+      <c r="L78" s="9">
+        <v>2</v>
+      </c>
+      <c r="M78" s="3">
+        <f>B29</f>
+        <v>0</v>
+      </c>
+      <c r="N78" s="3">
+        <f>C29</f>
+        <v>328.125</v>
+      </c>
+      <c r="O78" s="3">
+        <f>D29</f>
+        <v>656250</v>
+      </c>
+      <c r="P78" s="3">
+        <f>E29</f>
+        <v>0</v>
+      </c>
+      <c r="Q78" s="3">
+        <f>F29</f>
+        <v>-328.125</v>
+      </c>
+      <c r="R78" s="3">
+        <f>G29</f>
+        <v>656250</v>
+      </c>
+      <c r="T78" s="1">
+        <v>0</v>
+      </c>
+      <c r="V78" s="3">
+        <f>I29</f>
+        <v>-20000</v>
+      </c>
+      <c r="X78" s="1">
+        <v>25001.349757821597</v>
+      </c>
+      <c r="BE78" s="12"/>
+      <c r="BK78" s="6"/>
+      <c r="BL78" s="6"/>
+      <c r="BM78" s="6"/>
+      <c r="BN78" s="6"/>
+      <c r="BO78" s="6"/>
+      <c r="BP78" s="6"/>
+      <c r="BR78" s="67"/>
+      <c r="BT78" s="4"/>
+      <c r="BV78" s="68"/>
+    </row>
+    <row r="79" spans="5:74" x14ac:dyDescent="0.2">
+      <c r="L79" s="9">
+        <v>3</v>
+      </c>
+      <c r="M79" s="3">
+        <f>B30</f>
+        <v>0</v>
+      </c>
+      <c r="N79" s="3">
+        <f>C30</f>
+        <v>656250</v>
+      </c>
+      <c r="O79" s="3">
+        <f>D30</f>
+        <v>1750000000</v>
+      </c>
+      <c r="P79" s="3">
+        <f>E30</f>
+        <v>0</v>
+      </c>
+      <c r="Q79" s="3">
+        <f>F30</f>
+        <v>-656250</v>
+      </c>
+      <c r="R79" s="3">
+        <f>G30</f>
+        <v>875000000</v>
+      </c>
+      <c r="T79" s="1">
+        <v>0</v>
+      </c>
+      <c r="V79" s="3">
+        <f>I30</f>
+        <v>-13333333.333333334</v>
+      </c>
+      <c r="X79" s="1">
+        <v>20007386.283335742</v>
+      </c>
+      <c r="BE79" s="12"/>
+      <c r="BK79" s="6"/>
+      <c r="BL79" s="6"/>
+      <c r="BM79" s="6"/>
+      <c r="BN79" s="6"/>
+      <c r="BO79" s="6"/>
+      <c r="BP79" s="6"/>
+      <c r="BR79" s="67"/>
+      <c r="BT79" s="4"/>
+      <c r="BV79" s="68"/>
+    </row>
+    <row r="80" spans="5:74" x14ac:dyDescent="0.2">
+      <c r="L80" s="9">
+        <v>4</v>
+      </c>
+      <c r="M80" s="3">
+        <f>B31</f>
+        <v>-525000</v>
+      </c>
+      <c r="N80" s="3">
+        <f>C31</f>
+        <v>0</v>
+      </c>
+      <c r="O80" s="3">
+        <f>D31</f>
+        <v>0</v>
+      </c>
+      <c r="P80" s="3">
+        <f>E31</f>
+        <v>525000</v>
+      </c>
+      <c r="Q80" s="3">
+        <f>F31</f>
+        <v>0</v>
+      </c>
+      <c r="R80" s="3">
+        <f>G31</f>
+        <v>0</v>
+      </c>
+      <c r="T80" s="1">
+        <v>2.5538771384130594E-2</v>
+      </c>
+      <c r="V80" s="3">
+        <f>I31</f>
+        <v>1.22514845490862E-12</v>
+      </c>
+      <c r="X80" s="1">
+        <v>13407.854976668559</v>
+      </c>
+      <c r="BE80" s="12"/>
+    </row>
+    <row r="81" spans="12:83" x14ac:dyDescent="0.2">
+      <c r="L81" s="9">
+        <v>5</v>
+      </c>
+      <c r="M81" s="3">
+        <f>B32</f>
+        <v>0</v>
+      </c>
+      <c r="N81" s="3">
+        <f>C32</f>
+        <v>-328.125</v>
+      </c>
+      <c r="O81" s="3">
+        <f>D32</f>
+        <v>-656250</v>
+      </c>
+      <c r="P81" s="3">
+        <f>E32</f>
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3">
+        <f>F32</f>
+        <v>328.125</v>
+      </c>
+      <c r="R81" s="3">
+        <f>G32</f>
+        <v>-656250</v>
+      </c>
+      <c r="T81" s="1">
+        <v>-2.5538771384130597E-2</v>
+      </c>
+      <c r="V81" s="3">
+        <f>I32</f>
+        <v>-20000</v>
+      </c>
+      <c r="X81" s="1">
+        <v>14998.650242178403</v>
+      </c>
+      <c r="BE81" s="12"/>
+      <c r="BK81" s="2"/>
+    </row>
+    <row r="82" spans="12:83" x14ac:dyDescent="0.2">
+      <c r="L82" s="9">
+        <v>6</v>
+      </c>
+      <c r="M82" s="3">
+        <f>B33</f>
+        <v>0</v>
+      </c>
+      <c r="N82" s="3">
+        <f>C33</f>
+        <v>656250</v>
+      </c>
+      <c r="O82" s="3">
+        <f>D33</f>
+        <v>875000000</v>
+      </c>
+      <c r="P82" s="3">
+        <f>E33</f>
+        <v>0</v>
+      </c>
+      <c r="Q82" s="3">
+        <f>F33</f>
+        <v>-656250</v>
+      </c>
+      <c r="R82" s="3">
+        <f>G33</f>
+        <v>1750000000</v>
+      </c>
+      <c r="T82" s="1">
+        <v>7.6083350071789388E-3</v>
+      </c>
+      <c r="V82" s="3">
+        <f>I33</f>
+        <v>13333333.333333334</v>
+      </c>
+      <c r="X82" s="1">
+        <v>-1987.2520493548363</v>
+      </c>
+      <c r="BE82" s="12"/>
+      <c r="BK82" s="7"/>
+      <c r="BL82" s="7"/>
+      <c r="BM82" s="7"/>
+      <c r="BN82" s="7"/>
+      <c r="BO82" s="7"/>
+      <c r="BP82" s="7"/>
+      <c r="BR82" s="67"/>
+      <c r="BT82" s="6"/>
+      <c r="BV82" s="4"/>
+      <c r="BY82" s="65"/>
+      <c r="CA82" s="63"/>
+    </row>
+    <row r="83" spans="12:83" x14ac:dyDescent="0.2">
+      <c r="BE83" s="12"/>
+      <c r="BK83" s="7"/>
+      <c r="BL83" s="7"/>
+      <c r="BM83" s="7"/>
+      <c r="BN83" s="7"/>
+      <c r="BO83" s="7"/>
+      <c r="BP83" s="7"/>
+      <c r="BR83" s="67"/>
+      <c r="BT83" s="7"/>
+      <c r="BV83" s="4"/>
+      <c r="BY83" s="65"/>
+      <c r="CA83" s="63"/>
+      <c r="CE83" s="45"/>
+    </row>
+    <row r="84" spans="12:83" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BE84" s="12"/>
+      <c r="BK84" s="7"/>
+      <c r="BL84" s="7"/>
+      <c r="BM84" s="7"/>
+      <c r="BN84" s="7"/>
+      <c r="BO84" s="7"/>
+      <c r="BP84" s="7"/>
+      <c r="BQ84" s="4"/>
+      <c r="BR84" s="67"/>
+      <c r="BS84" s="4"/>
+      <c r="BT84" s="7"/>
+      <c r="BU84" s="4"/>
+      <c r="BV84" s="4"/>
+      <c r="BW84" s="4"/>
+      <c r="BX84" s="4"/>
+      <c r="BY84" s="65"/>
+      <c r="BZ84" s="4"/>
+      <c r="CA84" s="63"/>
+    </row>
+    <row r="85" spans="12:83" x14ac:dyDescent="0.2">
+      <c r="BE85" s="12"/>
+      <c r="BK85" s="7"/>
+      <c r="BL85" s="7"/>
+      <c r="BM85" s="7"/>
+      <c r="BN85" s="7"/>
+      <c r="BO85" s="7"/>
+      <c r="BP85" s="7"/>
+      <c r="BR85" s="67"/>
+      <c r="BT85" s="6"/>
+      <c r="BV85" s="4"/>
+      <c r="BY85" s="65"/>
+      <c r="CA85" s="63"/>
+    </row>
+    <row r="86" spans="12:83" x14ac:dyDescent="0.2">
+      <c r="BE86" s="12"/>
+      <c r="BK86" s="7"/>
+      <c r="BL86" s="7"/>
+      <c r="BM86" s="7"/>
+      <c r="BN86" s="7"/>
+      <c r="BO86" s="7"/>
+      <c r="BP86" s="7"/>
+      <c r="BR86" s="67"/>
+      <c r="BT86" s="7"/>
+      <c r="BV86" s="4"/>
+      <c r="BY86" s="65"/>
+      <c r="CA86" s="63"/>
+    </row>
+    <row r="87" spans="12:83" x14ac:dyDescent="0.2">
+      <c r="BE87" s="12"/>
+      <c r="BK87" s="7"/>
+      <c r="BL87" s="7"/>
+      <c r="BM87" s="7"/>
+      <c r="BN87" s="7"/>
+      <c r="BO87" s="7"/>
+      <c r="BP87" s="7"/>
+      <c r="BR87" s="67"/>
+      <c r="BT87" s="7"/>
+      <c r="BV87" s="4"/>
+      <c r="BY87" s="65"/>
+      <c r="CA87" s="63"/>
+    </row>
+    <row r="94" spans="12:83" x14ac:dyDescent="0.2">
+      <c r="BC94" s="29"/>
+      <c r="BD94" s="29"/>
+    </row>
+    <row r="101" spans="23:79" x14ac:dyDescent="0.2">
+      <c r="BB101" s="4"/>
+    </row>
+    <row r="102" spans="23:79" x14ac:dyDescent="0.2">
+      <c r="AZ102" s="12"/>
+      <c r="BB102" s="12"/>
+      <c r="BE102" s="12"/>
+      <c r="BK102" s="2"/>
+    </row>
+    <row r="103" spans="23:79" x14ac:dyDescent="0.2">
+      <c r="AZ103" s="12"/>
+      <c r="BB103" s="12"/>
+      <c r="BE103" s="12"/>
+      <c r="BK103" s="6"/>
+      <c r="BL103" s="6"/>
+      <c r="BM103" s="6"/>
+      <c r="BN103" s="6"/>
+      <c r="BO103" s="6"/>
+      <c r="BP103" s="6"/>
+      <c r="BR103" s="4"/>
+      <c r="BT103" s="4"/>
+      <c r="BV103" s="4"/>
+      <c r="BY103" s="4"/>
+    </row>
+    <row r="104" spans="23:79" x14ac:dyDescent="0.2">
+      <c r="W104" s="7"/>
+      <c r="X104" s="4"/>
+      <c r="Y104" s="4"/>
+      <c r="Z104" s="4"/>
+      <c r="AA104" s="4"/>
+      <c r="AB104" s="4"/>
+      <c r="AC104" s="4"/>
+      <c r="AD104" s="4"/>
+      <c r="AE104" s="4"/>
+      <c r="AF104" s="4"/>
+      <c r="AZ104" s="12"/>
+      <c r="BB104" s="12"/>
+      <c r="BE104" s="12"/>
+      <c r="BK104" s="6"/>
+      <c r="BL104" s="6"/>
+      <c r="BM104" s="6"/>
+      <c r="BN104" s="6"/>
+      <c r="BO104" s="6"/>
+      <c r="BP104" s="6"/>
+      <c r="BR104" s="4"/>
+      <c r="BT104" s="4"/>
+      <c r="BV104" s="4"/>
+      <c r="BY104" s="4"/>
+    </row>
+    <row r="105" spans="23:79" x14ac:dyDescent="0.2">
+      <c r="W105" s="4"/>
+      <c r="X105" s="7"/>
+      <c r="Y105" s="4"/>
+      <c r="Z105" s="4"/>
+      <c r="AA105" s="4"/>
+      <c r="AB105" s="4"/>
+      <c r="AC105" s="4"/>
+      <c r="AD105" s="4"/>
+      <c r="AE105" s="7"/>
+      <c r="AF105" s="4"/>
+      <c r="AZ105" s="30"/>
+      <c r="BB105" s="4"/>
+      <c r="BE105" s="4"/>
+      <c r="BK105" s="6"/>
+      <c r="BL105" s="6"/>
+      <c r="BM105" s="6"/>
+      <c r="BN105" s="6"/>
+      <c r="BO105" s="6"/>
+      <c r="BP105" s="6"/>
+      <c r="BQ105" s="4"/>
+      <c r="BR105" s="4"/>
+      <c r="BS105" s="4"/>
+      <c r="BT105" s="4"/>
+      <c r="BU105" s="4"/>
+      <c r="BV105" s="4"/>
+      <c r="BW105" s="4"/>
+      <c r="BX105" s="4"/>
+      <c r="BY105" s="4"/>
+    </row>
+    <row r="106" spans="23:79" x14ac:dyDescent="0.2">
+      <c r="W106" s="4"/>
+      <c r="X106" s="4"/>
+      <c r="Y106" s="7"/>
+      <c r="Z106" s="4"/>
+      <c r="AA106" s="7"/>
+      <c r="AB106" s="4"/>
+      <c r="AC106" s="4"/>
+      <c r="AD106" s="4"/>
+      <c r="AE106" s="4"/>
+      <c r="AF106" s="7"/>
+      <c r="AZ106" s="4"/>
+      <c r="BB106" s="4"/>
+      <c r="BE106" s="4"/>
+      <c r="BK106" s="6"/>
+      <c r="BL106" s="6"/>
+      <c r="BM106" s="6"/>
+      <c r="BN106" s="6"/>
+      <c r="BO106" s="6"/>
+      <c r="BP106" s="6"/>
+      <c r="BR106" s="67"/>
+      <c r="BT106" s="4"/>
+      <c r="BV106" s="4"/>
+      <c r="BY106" s="4"/>
+    </row>
+    <row r="107" spans="23:79" x14ac:dyDescent="0.2">
+      <c r="W107" s="4"/>
+      <c r="X107" s="4"/>
+      <c r="Y107" s="4"/>
+      <c r="Z107" s="4"/>
+      <c r="AA107" s="4"/>
+      <c r="AB107" s="4"/>
+      <c r="AC107" s="4"/>
+      <c r="AD107" s="4"/>
+      <c r="AE107" s="4"/>
+      <c r="AF107" s="4"/>
+      <c r="AZ107" s="12"/>
+      <c r="BB107" s="12"/>
+      <c r="BE107" s="12"/>
+      <c r="BK107" s="6"/>
+      <c r="BL107" s="6"/>
+      <c r="BM107" s="6"/>
+      <c r="BN107" s="6"/>
+      <c r="BO107" s="6"/>
+      <c r="BP107" s="6"/>
+      <c r="BR107" s="67"/>
+      <c r="BT107" s="4"/>
+      <c r="BV107" s="4"/>
+      <c r="BY107" s="4"/>
+    </row>
+    <row r="108" spans="23:79" x14ac:dyDescent="0.2">
+      <c r="W108" s="4"/>
+      <c r="X108" s="4"/>
+      <c r="Y108" s="7"/>
+      <c r="Z108" s="4"/>
+      <c r="AA108" s="7"/>
+      <c r="AB108" s="4"/>
+      <c r="AC108" s="4"/>
+      <c r="AD108" s="4"/>
+      <c r="AE108" s="4"/>
+      <c r="AF108" s="7"/>
+      <c r="AZ108" s="4"/>
+      <c r="BB108" s="12"/>
+      <c r="BE108" s="31"/>
+      <c r="BK108" s="6"/>
+      <c r="BL108" s="6"/>
+      <c r="BM108" s="6"/>
+      <c r="BN108" s="6"/>
+      <c r="BO108" s="6"/>
+      <c r="BP108" s="6"/>
+      <c r="BR108" s="67"/>
+      <c r="BT108" s="4"/>
+      <c r="BV108" s="4"/>
+      <c r="BY108" s="4"/>
+    </row>
+    <row r="109" spans="23:79" x14ac:dyDescent="0.2">
+      <c r="W109" s="4"/>
+      <c r="X109" s="4"/>
+      <c r="Y109" s="4"/>
+      <c r="Z109" s="4"/>
+      <c r="AA109" s="4"/>
+      <c r="AB109" s="4"/>
+      <c r="AC109" s="4"/>
+      <c r="AD109" s="4"/>
+      <c r="AE109" s="4"/>
+      <c r="AF109" s="4"/>
+      <c r="AZ109" s="4"/>
+      <c r="BB109" s="12"/>
+      <c r="BE109" s="31"/>
+    </row>
+    <row r="110" spans="23:79" x14ac:dyDescent="0.2">
+      <c r="W110" s="4"/>
+      <c r="X110" s="4"/>
+      <c r="Y110" s="4"/>
+      <c r="Z110" s="4"/>
+      <c r="AA110" s="4"/>
+      <c r="AB110" s="4"/>
+      <c r="AC110" s="4"/>
+      <c r="AD110" s="4"/>
+      <c r="AE110" s="4"/>
+      <c r="AF110" s="4"/>
+      <c r="AZ110" s="12"/>
+      <c r="BB110" s="12"/>
+      <c r="BE110" s="31"/>
+      <c r="BK110" s="2"/>
+    </row>
+    <row r="111" spans="23:79" x14ac:dyDescent="0.2">
+      <c r="W111" s="4"/>
+      <c r="X111" s="4"/>
+      <c r="Y111" s="4"/>
+      <c r="Z111" s="4"/>
+      <c r="AA111" s="4"/>
+      <c r="AB111" s="4"/>
+      <c r="AC111" s="4"/>
+      <c r="AD111" s="4"/>
+      <c r="AE111" s="4"/>
+      <c r="AF111" s="4"/>
+      <c r="AZ111" s="12"/>
+      <c r="BB111" s="7"/>
+      <c r="BE111" s="31"/>
+      <c r="BK111" s="7"/>
+      <c r="BL111" s="7"/>
+      <c r="BM111" s="7"/>
+      <c r="BN111" s="7"/>
+      <c r="BO111" s="7"/>
+      <c r="BP111" s="7"/>
+      <c r="BR111" s="4"/>
+      <c r="BT111" s="6"/>
+      <c r="BV111" s="4"/>
+      <c r="BY111" s="65"/>
+      <c r="CA111" s="63"/>
+    </row>
+    <row r="112" spans="23:79" x14ac:dyDescent="0.2">
+      <c r="W112" s="4"/>
+      <c r="X112" s="7"/>
+      <c r="Y112" s="4"/>
+      <c r="Z112" s="4"/>
+      <c r="AA112" s="4"/>
+      <c r="AB112" s="4"/>
+      <c r="AC112" s="4"/>
+      <c r="AD112" s="4"/>
+      <c r="AE112" s="7"/>
+      <c r="AF112" s="4"/>
+      <c r="AZ112" s="12"/>
+      <c r="BB112" s="7"/>
+      <c r="BE112" s="31"/>
+      <c r="BK112" s="7"/>
+      <c r="BL112" s="7"/>
+      <c r="BM112" s="7"/>
+      <c r="BN112" s="7"/>
+      <c r="BO112" s="7"/>
+      <c r="BP112" s="7"/>
+      <c r="BR112" s="4"/>
+      <c r="BT112" s="6"/>
+      <c r="BV112" s="4"/>
+      <c r="BY112" s="65"/>
+      <c r="CA112" s="63"/>
+    </row>
+    <row r="113" spans="2:79" x14ac:dyDescent="0.2">
+      <c r="W113" s="4"/>
+      <c r="X113" s="4"/>
+      <c r="Y113" s="7"/>
+      <c r="Z113" s="4"/>
+      <c r="AA113" s="7"/>
+      <c r="AB113" s="4"/>
+      <c r="AC113" s="4"/>
+      <c r="AD113" s="4"/>
+      <c r="AE113" s="4"/>
+      <c r="AF113" s="7"/>
+      <c r="AZ113" s="4"/>
+      <c r="BB113" s="4"/>
+      <c r="BE113" s="31"/>
+      <c r="BK113" s="7"/>
+      <c r="BL113" s="7"/>
+      <c r="BM113" s="7"/>
+      <c r="BN113" s="7"/>
+      <c r="BO113" s="7"/>
+      <c r="BP113" s="7"/>
+      <c r="BQ113" s="4"/>
+      <c r="BR113" s="4"/>
+      <c r="BS113" s="4"/>
+      <c r="BT113" s="6"/>
+      <c r="BU113" s="4"/>
+      <c r="BV113" s="4"/>
+      <c r="BW113" s="4"/>
+      <c r="BX113" s="4"/>
+      <c r="BY113" s="65"/>
+      <c r="BZ113" s="4"/>
+      <c r="CA113" s="63"/>
+    </row>
+    <row r="114" spans="2:79" x14ac:dyDescent="0.2">
+      <c r="W114" s="4"/>
+      <c r="X114" s="4"/>
+      <c r="Y114" s="4"/>
+      <c r="Z114" s="4"/>
+      <c r="AA114" s="4"/>
+      <c r="AB114" s="4"/>
+      <c r="AC114" s="4"/>
+      <c r="AD114" s="4"/>
+      <c r="AE114" s="4"/>
+      <c r="AF114" s="4"/>
+      <c r="AZ114" s="4"/>
+      <c r="BB114" s="4"/>
+      <c r="BE114" s="31"/>
+      <c r="BK114" s="7"/>
+      <c r="BL114" s="7"/>
+      <c r="BM114" s="7"/>
+      <c r="BN114" s="7"/>
+      <c r="BO114" s="7"/>
+      <c r="BP114" s="7"/>
+      <c r="BR114" s="4"/>
+      <c r="BT114" s="6"/>
+      <c r="BV114" s="4"/>
+      <c r="BY114" s="65"/>
+      <c r="CA114" s="63"/>
+    </row>
+    <row r="115" spans="2:79" x14ac:dyDescent="0.2">
+      <c r="W115" s="4"/>
+      <c r="X115" s="4"/>
+      <c r="Y115" s="7"/>
+      <c r="Z115" s="4"/>
+      <c r="AA115" s="7"/>
+      <c r="AB115" s="4"/>
+      <c r="AC115" s="4"/>
+      <c r="AD115" s="4"/>
+      <c r="AE115" s="4"/>
+      <c r="AF115" s="7"/>
+      <c r="AZ115" s="4"/>
+      <c r="BB115" s="4"/>
+      <c r="BE115" s="4"/>
+      <c r="BK115" s="7"/>
+      <c r="BL115" s="7"/>
+      <c r="BM115" s="7"/>
+      <c r="BN115" s="7"/>
+      <c r="BO115" s="7"/>
+      <c r="BP115" s="7"/>
+      <c r="BR115" s="4"/>
+      <c r="BT115" s="6"/>
+      <c r="BV115" s="4"/>
+      <c r="BY115" s="65"/>
+      <c r="CA115" s="63"/>
+    </row>
+    <row r="116" spans="2:79" x14ac:dyDescent="0.2">
+      <c r="BK116" s="7"/>
+      <c r="BL116" s="7"/>
+      <c r="BM116" s="7"/>
+      <c r="BN116" s="7"/>
+      <c r="BO116" s="7"/>
+      <c r="BP116" s="7"/>
+      <c r="BR116" s="4"/>
+      <c r="BT116" s="6"/>
+      <c r="BV116" s="4"/>
+      <c r="BY116" s="65"/>
+      <c r="CA116" s="63"/>
+    </row>
+    <row r="118" spans="2:79" x14ac:dyDescent="0.2">
+      <c r="B118" s="2"/>
+      <c r="AF118" s="2"/>
+    </row>
+    <row r="119" spans="2:79" x14ac:dyDescent="0.2">
+      <c r="E119" s="26"/>
+      <c r="F119" s="25"/>
+      <c r="V119" s="4"/>
+    </row>
+    <row r="120" spans="2:79" x14ac:dyDescent="0.2">
+      <c r="E120" s="26"/>
+      <c r="F120" s="25"/>
+      <c r="V120" s="4"/>
+      <c r="AW120" s="4"/>
+      <c r="AX120" s="4"/>
+    </row>
+    <row r="121" spans="2:79" x14ac:dyDescent="0.2">
+      <c r="E121" s="26"/>
+      <c r="F121" s="25"/>
+      <c r="V121" s="4"/>
+      <c r="AW121" s="7"/>
+      <c r="AX121" s="7"/>
+      <c r="AZ121" s="12"/>
+      <c r="BB121" s="12"/>
+      <c r="BE121" s="31"/>
+    </row>
+    <row r="122" spans="2:79" x14ac:dyDescent="0.2">
+      <c r="V122" s="4"/>
+      <c r="AW122" s="7"/>
+      <c r="AX122" s="7"/>
+      <c r="AZ122" s="12"/>
+      <c r="BB122" s="12"/>
+      <c r="BE122" s="31"/>
+    </row>
+    <row r="123" spans="2:79" x14ac:dyDescent="0.2">
+      <c r="V123" s="4"/>
+      <c r="AW123" s="7"/>
+      <c r="AX123" s="7"/>
+      <c r="AZ123" s="12"/>
+      <c r="BB123" s="12"/>
+      <c r="BE123" s="31"/>
+    </row>
+    <row r="124" spans="2:79" x14ac:dyDescent="0.2">
+      <c r="V124" s="4"/>
+      <c r="AW124" s="7"/>
+      <c r="AX124" s="16"/>
+      <c r="AZ124" s="30"/>
+      <c r="BB124" s="7"/>
+      <c r="BE124" s="31"/>
+    </row>
+    <row r="125" spans="2:79" x14ac:dyDescent="0.2">
+      <c r="V125" s="4"/>
+      <c r="AW125" s="7"/>
+      <c r="AX125" s="16"/>
+      <c r="AZ125" s="30"/>
+      <c r="BB125" s="7"/>
+      <c r="BE125" s="31"/>
+    </row>
+    <row r="126" spans="2:79" x14ac:dyDescent="0.2">
+      <c r="V126" s="4"/>
+      <c r="AW126" s="7"/>
+      <c r="AX126" s="7"/>
+      <c r="AY126" s="4"/>
+      <c r="AZ126" s="30"/>
+      <c r="BB126" s="12"/>
+      <c r="BE126" s="31"/>
+    </row>
+    <row r="127" spans="2:79" x14ac:dyDescent="0.2">
+      <c r="V127" s="4"/>
+      <c r="AW127" s="7"/>
+      <c r="AX127" s="16"/>
+      <c r="AZ127" s="30"/>
+      <c r="BA127" s="4"/>
+      <c r="BB127" s="12"/>
+      <c r="BC127" s="28"/>
+      <c r="BD127" s="28"/>
+      <c r="BE127" s="31"/>
+    </row>
+    <row r="128" spans="2:79" x14ac:dyDescent="0.2">
+      <c r="V128" s="4"/>
+      <c r="AW128" s="16"/>
+      <c r="AX128" s="7"/>
+      <c r="AZ128" s="30"/>
+      <c r="BB128" s="12"/>
+      <c r="BE128" s="31"/>
+    </row>
+    <row r="129" spans="22:90" x14ac:dyDescent="0.2">
+      <c r="V129" s="4"/>
+      <c r="AW129" s="16"/>
+      <c r="AX129" s="7"/>
+      <c r="AY129" s="3"/>
+      <c r="AZ129" s="30"/>
+      <c r="BB129" s="12"/>
+      <c r="BE129" s="31"/>
+    </row>
+    <row r="130" spans="22:90" x14ac:dyDescent="0.2">
+      <c r="V130" s="4"/>
+      <c r="AW130" s="16"/>
+      <c r="AX130" s="7"/>
+      <c r="AZ130" s="30"/>
+      <c r="BB130" s="12"/>
+      <c r="BE130" s="31"/>
+    </row>
+    <row r="131" spans="22:90" x14ac:dyDescent="0.2">
+      <c r="V131" s="4"/>
+      <c r="AW131" s="16"/>
+      <c r="AX131" s="16"/>
+      <c r="AZ131" s="30"/>
+      <c r="BB131" s="7"/>
+      <c r="BE131" s="31"/>
+    </row>
+    <row r="132" spans="22:90" x14ac:dyDescent="0.2">
+      <c r="V132" s="4"/>
+      <c r="AW132" s="16"/>
+      <c r="AX132" s="16"/>
+      <c r="AZ132" s="30"/>
+      <c r="BB132" s="7"/>
+      <c r="BE132" s="31"/>
+    </row>
+    <row r="133" spans="22:90" x14ac:dyDescent="0.2">
+      <c r="V133" s="4"/>
+      <c r="AJ133" s="4"/>
+      <c r="AK133" s="7"/>
+      <c r="AL133" s="7"/>
+      <c r="AM133" s="7"/>
+      <c r="AN133" s="7"/>
+      <c r="AO133" s="7"/>
+      <c r="AP133" s="7"/>
+      <c r="AQ133" s="7"/>
+      <c r="AR133" s="16"/>
+      <c r="AS133" s="16"/>
+      <c r="AT133" s="16"/>
+      <c r="AU133" s="16"/>
+      <c r="AV133" s="16"/>
+      <c r="AW133" s="16"/>
+      <c r="AX133" s="7"/>
+      <c r="AZ133" s="30"/>
+      <c r="BB133" s="12"/>
+      <c r="BE133" s="31"/>
+    </row>
+    <row r="134" spans="22:90" x14ac:dyDescent="0.2">
+      <c r="V134" s="4"/>
+      <c r="AJ134" s="4"/>
+      <c r="AK134" s="7"/>
+      <c r="AL134" s="7"/>
+      <c r="AM134" s="7"/>
+      <c r="AN134" s="16"/>
+      <c r="AO134" s="16"/>
+      <c r="AP134" s="7"/>
+      <c r="AQ134" s="16"/>
+      <c r="AR134" s="8"/>
+      <c r="AS134" s="8"/>
+      <c r="AT134" s="8"/>
+      <c r="AU134" s="16"/>
+      <c r="AV134" s="16"/>
+      <c r="AW134" s="7"/>
+      <c r="AX134" s="16"/>
+      <c r="AZ134" s="30"/>
+      <c r="BB134" s="12"/>
+      <c r="BE134" s="31"/>
+    </row>
+    <row r="135" spans="22:90" x14ac:dyDescent="0.2">
+      <c r="V135" s="4"/>
+      <c r="AK135" s="32"/>
+      <c r="AL135" s="32"/>
+      <c r="AM135" s="32"/>
+    </row>
+    <row r="136" spans="22:90" x14ac:dyDescent="0.2">
+      <c r="V136" s="4"/>
+    </row>
+    <row r="137" spans="22:90" x14ac:dyDescent="0.2">
+      <c r="BX137" s="33"/>
+    </row>
+    <row r="138" spans="22:90" x14ac:dyDescent="0.2">
+      <c r="BX138" s="33"/>
+    </row>
+    <row r="139" spans="22:90" x14ac:dyDescent="0.2">
+      <c r="BX139" s="33"/>
+    </row>
+    <row r="141" spans="22:90" x14ac:dyDescent="0.2">
+      <c r="BX141" s="33"/>
+      <c r="CL141" s="29"/>
+    </row>
+    <row r="142" spans="22:90" x14ac:dyDescent="0.2">
+      <c r="BX142" s="33"/>
+    </row>
+    <row r="143" spans="22:90" x14ac:dyDescent="0.2">
+      <c r="BX143" s="33"/>
+    </row>
+    <row r="144" spans="22:90" x14ac:dyDescent="0.2">
+      <c r="BL144" s="4"/>
+      <c r="BT144" s="2"/>
+    </row>
+    <row r="145" spans="39:92" x14ac:dyDescent="0.2">
+      <c r="BL145" s="4"/>
+      <c r="BN145" s="4"/>
+      <c r="BP145" s="4"/>
+      <c r="BR145" s="4"/>
+      <c r="BT145" s="6"/>
+      <c r="BU145" s="4"/>
+      <c r="BV145" s="4"/>
+      <c r="BW145" s="4"/>
+      <c r="BX145" s="4"/>
+      <c r="BY145" s="4"/>
+      <c r="BZ145" s="4"/>
+      <c r="CA145" s="42"/>
+      <c r="CB145" s="4"/>
+      <c r="CD145" s="4"/>
+      <c r="CF145" s="4"/>
+    </row>
+    <row r="146" spans="39:92" x14ac:dyDescent="0.2">
+      <c r="BL146" s="4"/>
+      <c r="BN146" s="4"/>
+      <c r="BP146" s="4"/>
+      <c r="BR146" s="4"/>
+      <c r="BT146" s="4"/>
+      <c r="BU146" s="6"/>
+      <c r="BV146" s="4"/>
+      <c r="BW146" s="4"/>
+      <c r="BX146" s="4"/>
+      <c r="BY146" s="4"/>
+      <c r="BZ146" s="4"/>
+      <c r="CA146" s="43"/>
+      <c r="CB146" s="4"/>
+      <c r="CD146" s="4"/>
+      <c r="CF146" s="4"/>
+    </row>
+    <row r="147" spans="39:92" x14ac:dyDescent="0.2">
+      <c r="BL147" s="4"/>
+      <c r="BN147" s="4"/>
+      <c r="BP147" s="4"/>
+      <c r="BR147" s="4"/>
+      <c r="BT147" s="4"/>
+      <c r="BU147" s="4"/>
+      <c r="BV147" s="4"/>
+      <c r="BW147" s="4"/>
+      <c r="BX147" s="4"/>
+      <c r="BY147" s="4"/>
+      <c r="BZ147" s="4"/>
+      <c r="CA147" s="42"/>
+      <c r="CB147" s="4"/>
+      <c r="CC147" s="4"/>
+      <c r="CD147" s="4"/>
+      <c r="CE147" s="4"/>
+      <c r="CF147" s="4"/>
+    </row>
+    <row r="148" spans="39:92" x14ac:dyDescent="0.2">
+      <c r="BL148" s="4"/>
+      <c r="BN148" s="4"/>
+      <c r="BP148" s="4"/>
+      <c r="BR148" s="4"/>
+      <c r="BT148" s="4"/>
+      <c r="BU148" s="4"/>
+      <c r="BV148" s="4"/>
+      <c r="BW148" s="6"/>
+      <c r="BX148" s="6"/>
+      <c r="BY148" s="4"/>
+      <c r="BZ148" s="4"/>
+      <c r="CA148" s="43"/>
+      <c r="CB148" s="7"/>
+      <c r="CD148" s="4"/>
+      <c r="CF148" s="7"/>
+    </row>
+    <row r="149" spans="39:92" x14ac:dyDescent="0.2">
+      <c r="AM149" s="2"/>
+      <c r="BL149" s="4"/>
+      <c r="BN149" s="4"/>
+      <c r="BP149" s="4"/>
+      <c r="BR149" s="4"/>
+      <c r="BT149" s="4"/>
+      <c r="BU149" s="4"/>
+      <c r="BV149" s="4"/>
+      <c r="BW149" s="4"/>
+      <c r="BX149" s="4"/>
+      <c r="BY149" s="6"/>
+      <c r="BZ149" s="4"/>
+      <c r="CA149" s="43"/>
+      <c r="CB149" s="7"/>
+      <c r="CD149" s="4"/>
+      <c r="CF149" s="7"/>
+    </row>
+    <row r="150" spans="39:92" x14ac:dyDescent="0.2">
+      <c r="AN150" s="4"/>
+      <c r="AO150" s="4"/>
+      <c r="AP150" s="4"/>
+      <c r="AQ150" s="4"/>
+      <c r="AR150" s="4"/>
+      <c r="AS150" s="4"/>
+      <c r="AT150" s="4"/>
+      <c r="AU150" s="4"/>
+      <c r="BL150" s="4"/>
+      <c r="BN150" s="4"/>
+      <c r="BP150" s="4"/>
+      <c r="BR150" s="4"/>
+      <c r="BT150" s="4"/>
+      <c r="BU150" s="4"/>
+      <c r="BV150" s="4"/>
+      <c r="BW150" s="4"/>
+      <c r="BX150" s="4"/>
+      <c r="BY150" s="4"/>
+      <c r="BZ150" s="4"/>
+      <c r="CA150" s="43"/>
+      <c r="CB150" s="7"/>
+      <c r="CD150" s="4"/>
+      <c r="CF150" s="7"/>
+    </row>
+    <row r="151" spans="39:92" x14ac:dyDescent="0.2">
+      <c r="AM151" s="4"/>
+      <c r="AN151" s="7"/>
+      <c r="AO151" s="7"/>
+      <c r="AP151" s="7"/>
+      <c r="AQ151" s="7"/>
+      <c r="AR151" s="7"/>
+      <c r="AS151" s="7"/>
+      <c r="AT151" s="7"/>
+      <c r="AU151" s="7"/>
+      <c r="AV151" s="4"/>
+      <c r="AW151" s="12"/>
+      <c r="AX151" s="4"/>
+      <c r="AY151" s="7"/>
+      <c r="BL151" s="4"/>
+      <c r="BM151" s="4"/>
+      <c r="BN151" s="4"/>
+      <c r="BO151" s="4"/>
+      <c r="BP151" s="4"/>
+      <c r="BQ151" s="28"/>
+      <c r="BR151" s="4"/>
+    </row>
+    <row r="152" spans="39:92" x14ac:dyDescent="0.2">
+      <c r="AM152" s="4"/>
+      <c r="AN152" s="7"/>
+      <c r="AO152" s="7"/>
+      <c r="AP152" s="7"/>
+      <c r="AQ152" s="7"/>
+      <c r="AR152" s="7"/>
+      <c r="AS152" s="7"/>
+      <c r="AT152" s="7"/>
+      <c r="AU152" s="7"/>
+      <c r="AW152" s="12"/>
+      <c r="AY152" s="7"/>
+      <c r="BL152" s="6"/>
+      <c r="BN152" s="12"/>
+      <c r="BP152" s="26"/>
+      <c r="BR152" s="16"/>
+      <c r="BT152" s="2"/>
+    </row>
+    <row r="153" spans="39:92" x14ac:dyDescent="0.2">
+      <c r="AM153" s="4"/>
+      <c r="AN153" s="7"/>
+      <c r="AO153" s="7"/>
+      <c r="AP153" s="7"/>
+      <c r="AQ153" s="7"/>
+      <c r="AR153" s="7"/>
+      <c r="AS153" s="7"/>
+      <c r="AT153" s="7"/>
+      <c r="AU153" s="7"/>
+      <c r="AW153" s="12"/>
+      <c r="AY153" s="7"/>
+      <c r="BL153" s="6"/>
+      <c r="BN153" s="12"/>
+      <c r="BP153" s="26"/>
+      <c r="BR153" s="22"/>
+      <c r="BT153" s="7"/>
+      <c r="BU153" s="4"/>
+      <c r="BV153" s="6"/>
+      <c r="BW153" s="7"/>
+      <c r="BX153" s="7"/>
+      <c r="BY153" s="4"/>
+      <c r="BZ153" s="6"/>
+      <c r="CB153" s="4"/>
+      <c r="CD153" s="4"/>
+      <c r="CF153" s="4"/>
+      <c r="CH153" s="44"/>
+    </row>
+    <row r="154" spans="39:92" x14ac:dyDescent="0.2">
+      <c r="AM154" s="4"/>
+      <c r="AN154" s="7"/>
+      <c r="AO154" s="7"/>
+      <c r="AP154" s="7"/>
+      <c r="AQ154" s="7"/>
+      <c r="AR154" s="7"/>
+      <c r="AS154" s="7"/>
+      <c r="AT154" s="7"/>
+      <c r="AU154" s="7"/>
+      <c r="AW154" s="12"/>
+      <c r="AY154" s="7"/>
+      <c r="BL154" s="6"/>
+      <c r="BN154" s="12"/>
+      <c r="BP154" s="26"/>
+      <c r="BR154" s="16"/>
+      <c r="BT154" s="4"/>
+      <c r="BU154" s="7"/>
+      <c r="BV154" s="7"/>
+      <c r="BW154" s="4"/>
+      <c r="BX154" s="4"/>
+      <c r="BY154" s="7"/>
+      <c r="BZ154" s="7"/>
+      <c r="CB154" s="4"/>
+      <c r="CD154" s="7"/>
+      <c r="CF154" s="4"/>
+      <c r="CH154" s="44"/>
+    </row>
+    <row r="155" spans="39:92" x14ac:dyDescent="0.2">
+      <c r="AM155" s="4"/>
+      <c r="AN155" s="7"/>
+      <c r="AO155" s="7"/>
+      <c r="AP155" s="7"/>
+      <c r="AQ155" s="7"/>
+      <c r="AR155" s="7"/>
+      <c r="AS155" s="7"/>
+      <c r="AT155" s="7"/>
+      <c r="AU155" s="7"/>
+      <c r="AW155" s="12"/>
+      <c r="AY155" s="7"/>
+      <c r="BL155" s="6"/>
+      <c r="BN155" s="12"/>
+      <c r="BP155" s="7"/>
+      <c r="BR155" s="16"/>
+      <c r="BT155" s="6"/>
+      <c r="BU155" s="7"/>
+      <c r="BV155" s="7"/>
+      <c r="BW155" s="7"/>
+      <c r="BX155" s="7"/>
+      <c r="BY155" s="7"/>
+      <c r="BZ155" s="7"/>
+      <c r="CA155" s="4"/>
+      <c r="CB155" s="4"/>
+      <c r="CC155" s="4"/>
+      <c r="CD155" s="7"/>
+      <c r="CE155" s="4"/>
+      <c r="CF155" s="4"/>
+      <c r="CG155" s="4"/>
+      <c r="CH155" s="44"/>
+      <c r="CN155" s="45"/>
+    </row>
+    <row r="156" spans="39:92" x14ac:dyDescent="0.2">
+      <c r="AM156" s="4"/>
+      <c r="AN156" s="7"/>
+      <c r="AO156" s="7"/>
+      <c r="AP156" s="7"/>
+      <c r="AQ156" s="7"/>
+      <c r="AR156" s="7"/>
+      <c r="AS156" s="7"/>
+      <c r="AT156" s="7"/>
+      <c r="AU156" s="7"/>
+      <c r="AW156" s="12"/>
+      <c r="AY156" s="7"/>
+      <c r="BL156" s="6"/>
+      <c r="BN156" s="12"/>
+      <c r="BP156" s="7"/>
+      <c r="BR156" s="22"/>
+      <c r="BT156" s="7"/>
+      <c r="BU156" s="4"/>
+      <c r="BV156" s="6"/>
+      <c r="BW156" s="46"/>
+      <c r="BX156" s="46"/>
+      <c r="BY156" s="4"/>
+      <c r="BZ156" s="6"/>
+      <c r="CB156" s="7"/>
+      <c r="CD156" s="4"/>
+      <c r="CF156" s="4"/>
+      <c r="CH156" s="44"/>
+    </row>
+    <row r="157" spans="39:92" x14ac:dyDescent="0.2">
+      <c r="AM157" s="4"/>
+      <c r="AN157" s="7"/>
+      <c r="AO157" s="7"/>
+      <c r="AP157" s="7"/>
+      <c r="AQ157" s="7"/>
+      <c r="AR157" s="7"/>
+      <c r="AS157" s="7"/>
+      <c r="AT157" s="7"/>
+      <c r="AU157" s="7"/>
+      <c r="AW157" s="12"/>
+      <c r="AY157" s="7"/>
+      <c r="BD157" s="47"/>
+      <c r="BL157" s="6"/>
+      <c r="BN157" s="12"/>
+      <c r="BO157" s="32"/>
+      <c r="BP157" s="4"/>
+      <c r="BR157" s="16"/>
+      <c r="BT157" s="4"/>
+      <c r="BU157" s="7"/>
+      <c r="BV157" s="7"/>
+      <c r="BW157" s="4"/>
+      <c r="BX157" s="4"/>
+      <c r="BY157" s="7"/>
+      <c r="BZ157" s="7"/>
+      <c r="CB157" s="7"/>
+      <c r="CD157" s="7"/>
+      <c r="CF157" s="4"/>
+      <c r="CH157" s="44"/>
+    </row>
+    <row r="158" spans="39:92" x14ac:dyDescent="0.2">
+      <c r="AM158" s="4"/>
+      <c r="AN158" s="7"/>
+      <c r="AO158" s="7"/>
+      <c r="AP158" s="7"/>
+      <c r="AQ158" s="7"/>
+      <c r="AR158" s="7"/>
+      <c r="AS158" s="7"/>
+      <c r="AT158" s="7"/>
+      <c r="AU158" s="7"/>
+      <c r="AW158" s="12"/>
+      <c r="AY158" s="7"/>
+      <c r="BD158" s="47"/>
+      <c r="BL158" s="6"/>
+      <c r="BN158" s="4"/>
+      <c r="BP158" s="4"/>
+      <c r="BR158" s="4"/>
+      <c r="BT158" s="6"/>
+      <c r="BU158" s="7"/>
+      <c r="BV158" s="7"/>
+      <c r="BW158" s="6"/>
+      <c r="BX158" s="6"/>
+      <c r="BY158" s="7"/>
+      <c r="BZ158" s="7"/>
+      <c r="CB158" s="7"/>
+      <c r="CD158" s="7"/>
+      <c r="CF158" s="4"/>
+      <c r="CH158" s="48"/>
+    </row>
+    <row r="159" spans="39:92" x14ac:dyDescent="0.2">
+      <c r="BD159" s="47"/>
+      <c r="BR159" s="32"/>
+    </row>
+    <row r="160" spans="39:92" x14ac:dyDescent="0.2">
+      <c r="AS160" s="29"/>
+      <c r="BD160" s="47"/>
+      <c r="BK160" s="2"/>
+      <c r="BP160" s="32"/>
+    </row>
+    <row r="161" spans="39:91" x14ac:dyDescent="0.2">
+      <c r="BD161" s="47"/>
+      <c r="BJ161" s="4"/>
+      <c r="BK161" s="4"/>
+      <c r="BL161" s="4"/>
+      <c r="BM161" s="4"/>
+      <c r="BN161" s="4"/>
+      <c r="BO161" s="4"/>
+      <c r="BP161" s="4"/>
+      <c r="BQ161" s="4"/>
+      <c r="BR161" s="4"/>
+      <c r="BW161" s="49"/>
+      <c r="BX161" s="49"/>
+      <c r="CC161" s="29"/>
+    </row>
+    <row r="162" spans="39:91" x14ac:dyDescent="0.2">
+      <c r="AM162" s="2"/>
+      <c r="AZ162" s="50"/>
+      <c r="BA162" s="50"/>
+      <c r="BB162" s="50"/>
+      <c r="BC162" s="50"/>
+      <c r="BD162" s="47"/>
+      <c r="BK162" s="33"/>
+      <c r="BL162" s="33"/>
+      <c r="BN162" s="32"/>
+      <c r="BT162" s="2"/>
+      <c r="CA162" s="33"/>
+      <c r="CB162" s="33"/>
+      <c r="CC162" s="32"/>
+    </row>
+    <row r="163" spans="39:91" x14ac:dyDescent="0.2">
+      <c r="AN163" s="4"/>
+      <c r="AO163" s="4"/>
+      <c r="AP163" s="4"/>
+      <c r="AQ163" s="4"/>
+      <c r="AR163" s="4"/>
+      <c r="AS163" s="4"/>
+      <c r="AT163" s="4"/>
+      <c r="AU163" s="4"/>
+      <c r="AZ163" s="50"/>
+      <c r="BA163" s="50"/>
+      <c r="BB163" s="50"/>
+      <c r="BC163" s="50"/>
+      <c r="BD163" s="50"/>
+      <c r="BE163" s="50"/>
+    </row>
+    <row r="164" spans="39:91" x14ac:dyDescent="0.2">
+      <c r="AM164" s="4"/>
+      <c r="AN164" s="7"/>
+      <c r="AO164" s="7"/>
+      <c r="AP164" s="7"/>
+      <c r="AQ164" s="7"/>
+      <c r="AR164" s="7"/>
+      <c r="AS164" s="7"/>
+      <c r="AT164" s="7"/>
+      <c r="AU164" s="7"/>
+      <c r="AV164" s="4"/>
+      <c r="AW164" s="3"/>
+      <c r="AX164" s="4"/>
+      <c r="AY164" s="12"/>
+      <c r="AZ164" s="30"/>
+      <c r="BA164" s="51"/>
+      <c r="BB164" s="50"/>
+      <c r="BC164" s="50"/>
+      <c r="BD164" s="52"/>
+      <c r="BE164" s="50"/>
+      <c r="BQ164" s="33"/>
+    </row>
+    <row r="165" spans="39:91" x14ac:dyDescent="0.2">
+      <c r="AM165" s="4"/>
+      <c r="AN165" s="7"/>
+      <c r="AO165" s="7"/>
+      <c r="AP165" s="7"/>
+      <c r="AQ165" s="7"/>
+      <c r="AR165" s="7"/>
+      <c r="AS165" s="7"/>
+      <c r="AT165" s="7"/>
+      <c r="AU165" s="7"/>
+      <c r="AW165" s="3"/>
+      <c r="AY165" s="12"/>
+      <c r="AZ165" s="50"/>
+      <c r="BA165" s="51"/>
+      <c r="BB165" s="50"/>
+      <c r="BC165" s="50"/>
+      <c r="BD165" s="52"/>
+      <c r="BE165" s="50"/>
+      <c r="BK165" s="2"/>
+      <c r="BT165" s="2"/>
+      <c r="BY165" s="2"/>
+    </row>
+    <row r="166" spans="39:91" x14ac:dyDescent="0.2">
+      <c r="AM166" s="4"/>
+      <c r="AN166" s="7"/>
+      <c r="AO166" s="7"/>
+      <c r="AP166" s="7"/>
+      <c r="AQ166" s="7"/>
+      <c r="AR166" s="7"/>
+      <c r="AS166" s="7"/>
+      <c r="AT166" s="7"/>
+      <c r="AU166" s="7"/>
+      <c r="AW166" s="3"/>
+      <c r="AY166" s="12"/>
+      <c r="AZ166" s="50"/>
+      <c r="BA166" s="51"/>
+      <c r="BB166" s="53"/>
+      <c r="BC166" s="50"/>
+      <c r="BD166" s="54"/>
+      <c r="BE166" s="50"/>
+      <c r="BP166" s="55"/>
+      <c r="BQ166" s="56"/>
+      <c r="BR166" s="57"/>
+      <c r="BT166" s="12"/>
+      <c r="BU166" s="58"/>
+      <c r="BV166" s="2"/>
+      <c r="BY166" s="12"/>
+      <c r="BZ166" s="56"/>
+      <c r="CA166" s="2"/>
+    </row>
+    <row r="167" spans="39:91" x14ac:dyDescent="0.2">
+      <c r="AM167" s="4"/>
+      <c r="AN167" s="7"/>
+      <c r="AO167" s="7"/>
+      <c r="AP167" s="7"/>
+      <c r="AQ167" s="7"/>
+      <c r="AR167" s="7"/>
+      <c r="AS167" s="7"/>
+      <c r="AT167" s="7"/>
+      <c r="AU167" s="7"/>
+      <c r="AW167" s="3"/>
+      <c r="AY167" s="12"/>
+      <c r="BA167" s="51"/>
+      <c r="BB167" s="53"/>
+      <c r="BC167" s="50"/>
+      <c r="BD167" s="52"/>
+      <c r="BE167" s="50"/>
+      <c r="BP167" s="55"/>
+      <c r="BQ167" s="56"/>
+      <c r="BR167" s="57"/>
+      <c r="BT167" s="12"/>
+      <c r="BU167" s="58"/>
+      <c r="BV167" s="2"/>
+      <c r="BY167" s="12"/>
+      <c r="BZ167" s="56"/>
+      <c r="CA167" s="2"/>
+    </row>
+    <row r="168" spans="39:91" x14ac:dyDescent="0.2">
+      <c r="AM168" s="4"/>
+      <c r="AN168" s="7"/>
+      <c r="AO168" s="7"/>
+      <c r="AP168" s="7"/>
+      <c r="AQ168" s="7"/>
+      <c r="AR168" s="7"/>
+      <c r="AS168" s="7"/>
+      <c r="AT168" s="7"/>
+      <c r="AU168" s="7"/>
+      <c r="AW168" s="3"/>
+      <c r="AY168" s="12"/>
+      <c r="AZ168" s="50"/>
+      <c r="BA168" s="51"/>
+      <c r="BB168" s="50"/>
+      <c r="BC168" s="50"/>
+      <c r="BD168" s="52"/>
+      <c r="BE168" s="50"/>
+      <c r="BP168" s="55"/>
+      <c r="BQ168" s="56"/>
+      <c r="BR168" s="57"/>
+      <c r="BT168" s="12"/>
+      <c r="BU168" s="58"/>
+      <c r="BV168" s="2"/>
+      <c r="BW168" s="59"/>
+      <c r="BX168" s="59"/>
+      <c r="BY168" s="12"/>
+      <c r="BZ168" s="56"/>
+      <c r="CA168" s="2"/>
+    </row>
+    <row r="169" spans="39:91" x14ac:dyDescent="0.2">
+      <c r="AM169" s="4"/>
+      <c r="AN169" s="7"/>
+      <c r="AO169" s="7"/>
+      <c r="AP169" s="7"/>
+      <c r="AQ169" s="7"/>
+      <c r="AR169" s="7"/>
+      <c r="AS169" s="7"/>
+      <c r="AT169" s="7"/>
+      <c r="AU169" s="7"/>
+      <c r="AW169" s="3"/>
+      <c r="AY169" s="12"/>
+      <c r="AZ169" s="50"/>
+      <c r="BA169" s="51"/>
+      <c r="BB169" s="50"/>
+      <c r="BC169" s="50"/>
+      <c r="BD169" s="52"/>
+      <c r="BE169" s="50"/>
+      <c r="BL169" s="60"/>
+      <c r="BM169" s="61"/>
+      <c r="BN169" s="61"/>
+      <c r="BP169" s="55"/>
+      <c r="BQ169" s="56"/>
+      <c r="BT169" s="12"/>
+      <c r="BU169" s="58"/>
+      <c r="BV169" s="2"/>
+      <c r="BW169" s="59"/>
+      <c r="BX169" s="59"/>
+      <c r="BY169" s="12"/>
+      <c r="BZ169" s="56"/>
+      <c r="CA169" s="2"/>
+    </row>
+    <row r="170" spans="39:91" x14ac:dyDescent="0.2">
+      <c r="AM170" s="4"/>
+      <c r="AN170" s="7"/>
+      <c r="AO170" s="7"/>
+      <c r="AP170" s="7"/>
+      <c r="AQ170" s="7"/>
+      <c r="AR170" s="7"/>
+      <c r="AS170" s="7"/>
+      <c r="AT170" s="7"/>
+      <c r="AU170" s="7"/>
+      <c r="AW170" s="3"/>
+      <c r="AY170" s="12"/>
+      <c r="AZ170" s="50"/>
+      <c r="BA170" s="51"/>
+      <c r="BB170" s="53"/>
+      <c r="BC170" s="50"/>
+      <c r="BD170" s="52"/>
+      <c r="BE170" s="50"/>
+      <c r="BP170" s="55"/>
+      <c r="BQ170" s="47"/>
+      <c r="BT170" s="12"/>
+      <c r="BU170" s="58"/>
+      <c r="BV170" s="2"/>
+      <c r="BY170" s="12"/>
+      <c r="BZ170" s="56"/>
+      <c r="CA170" s="2"/>
+    </row>
+    <row r="171" spans="39:91" x14ac:dyDescent="0.2">
+      <c r="AM171" s="4"/>
+      <c r="AN171" s="7"/>
+      <c r="AO171" s="7"/>
+      <c r="AP171" s="7"/>
+      <c r="AQ171" s="7"/>
+      <c r="AR171" s="7"/>
+      <c r="AS171" s="7"/>
+      <c r="AT171" s="7"/>
+      <c r="AU171" s="7"/>
+      <c r="AW171" s="3"/>
+      <c r="AY171" s="12"/>
+      <c r="AZ171" s="50"/>
+      <c r="BA171" s="51"/>
+      <c r="BB171" s="53"/>
+      <c r="BC171" s="50"/>
+      <c r="BD171" s="52"/>
+      <c r="BE171" s="50"/>
+      <c r="BP171" s="55"/>
+      <c r="BQ171" s="47"/>
+      <c r="BT171" s="12"/>
+      <c r="BU171" s="58"/>
+      <c r="BV171" s="2"/>
+      <c r="BY171" s="12"/>
+      <c r="BZ171" s="56"/>
+      <c r="CA171" s="2"/>
+      <c r="CF171" s="2"/>
+    </row>
+    <row r="172" spans="39:91" x14ac:dyDescent="0.2">
+      <c r="BB172" s="50"/>
+      <c r="BC172" s="50"/>
+      <c r="BD172" s="50"/>
+      <c r="BE172" s="50"/>
+      <c r="BW172" s="59"/>
+      <c r="BX172" s="59"/>
+      <c r="BY172" s="12"/>
+      <c r="BZ172" s="56"/>
+      <c r="CA172" s="2"/>
+    </row>
+    <row r="173" spans="39:91" x14ac:dyDescent="0.2">
+      <c r="AZ173" s="50"/>
+      <c r="BA173" s="50"/>
+      <c r="BB173" s="62"/>
+      <c r="BC173" s="50"/>
+      <c r="BD173" s="50"/>
+      <c r="BE173" s="50"/>
+      <c r="BF173" s="50"/>
+      <c r="BW173" s="59"/>
+      <c r="BX173" s="59"/>
+      <c r="BY173" s="12"/>
+      <c r="BZ173" s="56"/>
+      <c r="CA173" s="2"/>
+    </row>
+    <row r="174" spans="39:91" x14ac:dyDescent="0.2">
+      <c r="AZ174" s="50"/>
+      <c r="BA174" s="50"/>
+      <c r="BB174" s="50"/>
+      <c r="BC174" s="50"/>
+      <c r="BD174" s="50"/>
+      <c r="BE174" s="50"/>
+      <c r="BF174" s="50"/>
+    </row>
+    <row r="175" spans="39:91" x14ac:dyDescent="0.2">
+      <c r="AM175" s="2"/>
+      <c r="AZ175" s="50"/>
+      <c r="BA175" s="50"/>
+      <c r="BB175" s="50"/>
+      <c r="BC175" s="50"/>
+      <c r="BD175" s="50"/>
+      <c r="BE175" s="50"/>
+      <c r="BF175" s="50"/>
+    </row>
+    <row r="176" spans="39:91" x14ac:dyDescent="0.2">
+      <c r="AN176" s="4"/>
+      <c r="AO176" s="4"/>
+      <c r="AP176" s="4"/>
+      <c r="AQ176" s="4"/>
+      <c r="AR176" s="4"/>
+      <c r="AS176" s="4"/>
+      <c r="AT176" s="4"/>
+      <c r="AU176" s="4"/>
+      <c r="AW176" s="7"/>
+      <c r="AZ176" s="50"/>
+      <c r="BA176" s="50"/>
+      <c r="BB176" s="50"/>
+      <c r="BC176" s="50"/>
+      <c r="BD176" s="50"/>
+      <c r="BE176" s="50"/>
+      <c r="BF176" s="50"/>
+      <c r="BK176" s="2"/>
+      <c r="BP176" s="2"/>
+      <c r="BT176" s="2"/>
+      <c r="BY176" s="2"/>
+      <c r="CD176" s="2"/>
+      <c r="CI176" s="2"/>
+      <c r="CM176" s="2"/>
+    </row>
+    <row r="177" spans="39:93" x14ac:dyDescent="0.2">
+      <c r="AM177" s="4"/>
+      <c r="AN177" s="7"/>
+      <c r="AO177" s="7"/>
+      <c r="AP177" s="7"/>
+      <c r="AQ177" s="7"/>
+      <c r="AR177" s="6"/>
+      <c r="AS177" s="6"/>
+      <c r="AT177" s="6"/>
+      <c r="AU177" s="6"/>
+      <c r="AW177" s="7"/>
+      <c r="AY177" s="7"/>
+      <c r="AZ177" s="50"/>
+      <c r="BA177" s="26"/>
+      <c r="BB177" s="50"/>
+      <c r="BC177" s="48"/>
+      <c r="BD177" s="48"/>
+      <c r="BE177" s="50"/>
+      <c r="BF177" s="63"/>
+      <c r="BK177" s="26"/>
+      <c r="BL177" s="47"/>
+      <c r="BM177" s="2"/>
+      <c r="BP177" s="4"/>
+      <c r="BQ177" s="47"/>
+      <c r="BR177" s="2"/>
+      <c r="BT177" s="4"/>
+      <c r="BU177" s="47"/>
+      <c r="BV177" s="2"/>
+      <c r="BY177" s="4"/>
+      <c r="BZ177" s="47"/>
+      <c r="CA177" s="2"/>
+      <c r="CD177" s="4"/>
+      <c r="CE177" s="47"/>
+      <c r="CF177" s="2"/>
+      <c r="CI177" s="4"/>
+      <c r="CJ177" s="47"/>
+      <c r="CK177" s="2"/>
+      <c r="CM177" s="4"/>
+      <c r="CN177" s="47"/>
+      <c r="CO177" s="2"/>
+    </row>
+    <row r="178" spans="39:93" x14ac:dyDescent="0.2">
+      <c r="AM178" s="4"/>
+      <c r="AN178" s="7"/>
+      <c r="AO178" s="7"/>
+      <c r="AP178" s="7"/>
+      <c r="AQ178" s="7"/>
+      <c r="AR178" s="6"/>
+      <c r="AS178" s="6"/>
+      <c r="AT178" s="6"/>
+      <c r="AU178" s="6"/>
+      <c r="AW178" s="7"/>
+      <c r="AY178" s="7"/>
+      <c r="AZ178" s="50"/>
+      <c r="BA178" s="26"/>
+      <c r="BB178" s="50"/>
+      <c r="BC178" s="48"/>
+      <c r="BD178" s="48"/>
+      <c r="BE178" s="50"/>
+      <c r="BF178" s="63"/>
+      <c r="BK178" s="26"/>
+      <c r="BL178" s="47"/>
+      <c r="BM178" s="2"/>
+      <c r="BP178" s="4"/>
+      <c r="BQ178" s="47"/>
+      <c r="BR178" s="2"/>
+      <c r="BT178" s="4"/>
+      <c r="BU178" s="47"/>
+      <c r="BV178" s="2"/>
+      <c r="BY178" s="4"/>
+      <c r="BZ178" s="47"/>
+      <c r="CA178" s="2"/>
+      <c r="CD178" s="4"/>
+      <c r="CE178" s="47"/>
+      <c r="CF178" s="2"/>
+      <c r="CI178" s="4"/>
+      <c r="CJ178" s="47"/>
+      <c r="CK178" s="2"/>
+      <c r="CM178" s="4"/>
+      <c r="CN178" s="47"/>
+      <c r="CO178" s="2"/>
+    </row>
+    <row r="179" spans="39:93" x14ac:dyDescent="0.2">
+      <c r="AM179" s="4"/>
+      <c r="AN179" s="7"/>
+      <c r="AO179" s="7"/>
+      <c r="AP179" s="7"/>
+      <c r="AQ179" s="7"/>
+      <c r="AR179" s="6"/>
+      <c r="AS179" s="6"/>
+      <c r="AT179" s="6"/>
+      <c r="AU179" s="6"/>
+      <c r="AV179" s="4"/>
+      <c r="AW179" s="7"/>
+      <c r="AX179" s="4"/>
+      <c r="AY179" s="7"/>
+      <c r="AZ179" s="30"/>
+      <c r="BA179" s="26"/>
+      <c r="BB179" s="30"/>
+      <c r="BC179" s="48"/>
+      <c r="BD179" s="48"/>
+      <c r="BE179" s="30"/>
+      <c r="BF179" s="63"/>
+      <c r="BK179" s="26"/>
+      <c r="BL179" s="47"/>
+      <c r="BM179" s="2"/>
+      <c r="BP179" s="4"/>
+      <c r="BQ179" s="47"/>
+      <c r="BR179" s="2"/>
+      <c r="BT179" s="4"/>
+      <c r="BU179" s="47"/>
+      <c r="BV179" s="2"/>
+      <c r="BY179" s="4"/>
+      <c r="BZ179" s="47"/>
+      <c r="CA179" s="2"/>
+      <c r="CD179" s="4"/>
+      <c r="CE179" s="47"/>
+      <c r="CF179" s="2"/>
+      <c r="CI179" s="4"/>
+      <c r="CJ179" s="47"/>
+      <c r="CK179" s="2"/>
+      <c r="CM179" s="4"/>
+      <c r="CN179" s="47"/>
+      <c r="CO179" s="2"/>
+    </row>
+    <row r="180" spans="39:93" x14ac:dyDescent="0.2">
+      <c r="AM180" s="4"/>
+      <c r="AN180" s="4"/>
+      <c r="AO180" s="4"/>
+      <c r="AP180" s="4"/>
+      <c r="AQ180" s="4"/>
+      <c r="AR180" s="7"/>
+      <c r="AS180" s="7"/>
+      <c r="AT180" s="7"/>
+      <c r="AU180" s="7"/>
+      <c r="AW180" s="7"/>
+      <c r="AY180" s="7"/>
+      <c r="AZ180" s="50"/>
+      <c r="BA180" s="26"/>
+      <c r="BB180" s="50"/>
+      <c r="BC180" s="48"/>
+      <c r="BD180" s="48"/>
+      <c r="BE180" s="50"/>
+      <c r="BF180" s="63"/>
+      <c r="BK180" s="26"/>
+      <c r="BL180" s="47"/>
+      <c r="BM180" s="2"/>
+      <c r="BP180" s="4"/>
+      <c r="BQ180" s="47"/>
+      <c r="BR180" s="2"/>
+      <c r="BT180" s="4"/>
+      <c r="BU180" s="47"/>
+      <c r="BV180" s="2"/>
+      <c r="BY180" s="4"/>
+      <c r="BZ180" s="47"/>
+      <c r="CA180" s="2"/>
+      <c r="CD180" s="4"/>
+      <c r="CE180" s="47"/>
+      <c r="CF180" s="2"/>
+      <c r="CI180" s="4"/>
+      <c r="CJ180" s="47"/>
+      <c r="CK180" s="2"/>
+      <c r="CM180" s="4"/>
+      <c r="CN180" s="47"/>
+      <c r="CO180" s="2"/>
+    </row>
+    <row r="181" spans="39:93" x14ac:dyDescent="0.2">
+      <c r="AM181" s="4"/>
+      <c r="AN181" s="4"/>
+      <c r="AO181" s="4"/>
+      <c r="AP181" s="4"/>
+      <c r="AQ181" s="4"/>
+      <c r="AR181" s="7"/>
+      <c r="AS181" s="7"/>
+      <c r="AT181" s="7"/>
+      <c r="AU181" s="7"/>
+      <c r="AW181" s="7"/>
+      <c r="AY181" s="7"/>
+      <c r="AZ181" s="50"/>
+      <c r="BA181" s="26"/>
+      <c r="BB181" s="50"/>
+      <c r="BC181" s="48"/>
+      <c r="BD181" s="48"/>
+      <c r="BE181" s="50"/>
+      <c r="BF181" s="63"/>
+      <c r="BK181" s="26"/>
+      <c r="BL181" s="47"/>
+      <c r="BM181" s="2"/>
+      <c r="BP181" s="4"/>
+      <c r="BQ181" s="47"/>
+      <c r="BR181" s="2"/>
+      <c r="BT181" s="4"/>
+      <c r="BU181" s="47"/>
+      <c r="BV181" s="2"/>
+      <c r="BY181" s="4"/>
+      <c r="BZ181" s="47"/>
+      <c r="CA181" s="2"/>
+      <c r="CD181" s="4"/>
+      <c r="CE181" s="47"/>
+      <c r="CF181" s="2"/>
+      <c r="CI181" s="4"/>
+      <c r="CJ181" s="47"/>
+      <c r="CK181" s="2"/>
+      <c r="CM181" s="4"/>
+      <c r="CN181" s="47"/>
+      <c r="CO181" s="2"/>
+    </row>
+    <row r="182" spans="39:93" x14ac:dyDescent="0.2">
+      <c r="AM182" s="4"/>
+      <c r="AN182" s="4"/>
+      <c r="AO182" s="4"/>
+      <c r="AP182" s="4"/>
+      <c r="AQ182" s="4"/>
+      <c r="AR182" s="7"/>
+      <c r="AS182" s="7"/>
+      <c r="AT182" s="7"/>
+      <c r="AU182" s="7"/>
+      <c r="AW182" s="7"/>
+      <c r="AY182" s="7"/>
+      <c r="AZ182" s="50"/>
+      <c r="BA182" s="26"/>
+      <c r="BB182" s="50"/>
+      <c r="BC182" s="48"/>
+      <c r="BD182" s="48"/>
+      <c r="BE182" s="50"/>
+      <c r="BF182" s="63"/>
+      <c r="BK182" s="26"/>
+      <c r="BL182" s="47"/>
+      <c r="BM182" s="2"/>
+      <c r="BP182" s="4"/>
+      <c r="BQ182" s="47"/>
+      <c r="BR182" s="2"/>
+      <c r="BT182" s="4"/>
+      <c r="BU182" s="47"/>
+      <c r="BV182" s="2"/>
+      <c r="BY182" s="4"/>
+      <c r="BZ182" s="47"/>
+      <c r="CA182" s="2"/>
+      <c r="CD182" s="4"/>
+      <c r="CE182" s="47"/>
+      <c r="CF182" s="2"/>
+      <c r="CI182" s="4"/>
+      <c r="CJ182" s="47"/>
+      <c r="CK182" s="2"/>
+      <c r="CM182" s="4"/>
+      <c r="CN182" s="47"/>
+      <c r="CO182" s="2"/>
+    </row>
+    <row r="183" spans="39:93" x14ac:dyDescent="0.2">
+      <c r="AW183" s="7"/>
+      <c r="AZ183" s="50"/>
+      <c r="BA183" s="50"/>
+      <c r="BB183" s="50"/>
+      <c r="BC183" s="50"/>
+      <c r="BD183" s="50"/>
+      <c r="BE183" s="50"/>
+      <c r="BF183" s="50"/>
+      <c r="BT183" s="47"/>
+    </row>
+    <row r="184" spans="39:93" x14ac:dyDescent="0.2">
+      <c r="AW184" s="7"/>
+      <c r="BE184" s="50"/>
+      <c r="BF184" s="50"/>
+    </row>
+    <row r="185" spans="39:93" x14ac:dyDescent="0.2">
+      <c r="AW185" s="7"/>
+      <c r="AZ185" s="50"/>
+      <c r="BA185" s="50"/>
+      <c r="BB185" s="50"/>
+      <c r="BC185" s="50"/>
+      <c r="BD185" s="50"/>
+      <c r="BE185" s="50"/>
+      <c r="BF185" s="50"/>
+      <c r="BK185" s="2"/>
+      <c r="BR185" s="64"/>
+    </row>
+    <row r="186" spans="39:93" x14ac:dyDescent="0.2">
+      <c r="AW186" s="7"/>
+      <c r="BL186" s="56"/>
+      <c r="BM186" s="2"/>
+    </row>
+    <row r="187" spans="39:93" x14ac:dyDescent="0.2">
+      <c r="BL187" s="56"/>
+      <c r="BM187" s="2"/>
+    </row>
+    <row r="190" spans="39:93" x14ac:dyDescent="0.2">
+      <c r="BL190" s="56"/>
+      <c r="BM190" s="2"/>
+    </row>
+    <row r="191" spans="39:93" x14ac:dyDescent="0.2">
+      <c r="BL191" s="56"/>
+      <c r="BM191" s="2"/>
+    </row>
+    <row r="192" spans="39:93" x14ac:dyDescent="0.2">
+      <c r="BL192" s="56"/>
+      <c r="BM192" s="2"/>
+    </row>
+    <row r="193" spans="64:65" x14ac:dyDescent="0.2">
+      <c r="BL193" s="56"/>
+      <c r="BM193" s="2"/>
+    </row>
+    <row r="195" spans="64:65" x14ac:dyDescent="0.2">
+      <c r="BL195" s="56"/>
+      <c r="BM195" s="2"/>
+    </row>
+    <row r="198" spans="64:65" x14ac:dyDescent="0.2">
+      <c r="BL198" s="56"/>
+      <c r="BM198" s="2"/>
+    </row>
+    <row r="199" spans="64:65" x14ac:dyDescent="0.2">
+      <c r="BL199" s="56"/>
+      <c r="BM199" s="2"/>
+    </row>
+    <row r="200" spans="64:65" x14ac:dyDescent="0.2">
+      <c r="BL200" s="56"/>
+      <c r="BM200" s="2"/>
+    </row>
+    <row r="201" spans="64:65" x14ac:dyDescent="0.2">
+      <c r="BL201" s="56"/>
+      <c r="BM201" s="2"/>
+    </row>
+    <row r="203" spans="64:65" x14ac:dyDescent="0.2">
+      <c r="BL203" s="56"/>
+      <c r="BM203" s="2"/>
+    </row>
+    <row r="206" spans="64:65" x14ac:dyDescent="0.2">
+      <c r="BL206" s="56"/>
+      <c r="BM206" s="2"/>
+    </row>
+    <row r="207" spans="64:65" x14ac:dyDescent="0.2">
+      <c r="BL207" s="56"/>
+      <c r="BM207" s="2"/>
+    </row>
+    <row r="208" spans="64:65" x14ac:dyDescent="0.2">
+      <c r="BL208" s="56"/>
+      <c r="BM208" s="2"/>
+    </row>
+    <row r="209" spans="58:65" x14ac:dyDescent="0.2">
+      <c r="BL209" s="56"/>
+      <c r="BM209" s="2"/>
+    </row>
+    <row r="219" spans="58:65" x14ac:dyDescent="0.2">
+      <c r="BF219" s="50"/>
+    </row>
+    <row r="220" spans="58:65" x14ac:dyDescent="0.2">
+      <c r="BF220" s="50"/>
+    </row>
+    <row r="221" spans="58:65" x14ac:dyDescent="0.2">
+      <c r="BF221" s="50"/>
+    </row>
+    <row r="222" spans="58:65" x14ac:dyDescent="0.2">
+      <c r="BF222" s="50"/>
+    </row>
+    <row r="223" spans="58:65" x14ac:dyDescent="0.2">
+      <c r="BF223" s="50"/>
+    </row>
+    <row r="224" spans="58:65" x14ac:dyDescent="0.2">
+      <c r="BF224" s="50"/>
+    </row>
+    <row r="225" spans="58:58" x14ac:dyDescent="0.2">
+      <c r="BF225" s="50"/>
+    </row>
+    <row r="226" spans="58:58" x14ac:dyDescent="0.2">
+      <c r="BF226" s="50"/>
+    </row>
+    <row r="227" spans="58:58" x14ac:dyDescent="0.2">
+      <c r="BF227" s="50"/>
+    </row>
+  </sheetData>
   <conditionalFormatting sqref="M22:R27">
     <cfRule type="expression" dxfId="7" priority="6">
       <formula>ABS(M22)&lt;0.1</formula>

--- a/theory/FEM matriisit.xlsx
+++ b/theory/FEM matriisit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_Ohjelmointi\2_Rust\vefem\theory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F58154E-8FF7-4C85-A919-D1E2E8ED6AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CD85FD-1372-4E3B-B0B6-EC092CF9DB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{27180542-B0D2-4BFE-946B-7857B24C93C8}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{27180542-B0D2-4BFE-946B-7857B24C93C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Ilman vapautuksia" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="127">
   <si>
     <t>°</t>
   </si>
@@ -514,6 +514,12 @@
   </si>
   <si>
     <t>Siirtymä tuen lokaalin Y-akselin suuntaan</t>
+  </si>
+  <si>
+    <t>Alku</t>
+  </si>
+  <si>
+    <t>Loppu</t>
   </si>
 </sst>
 </file>
@@ -32045,7 +32051,7 @@
       </c>
       <c r="S5" s="7">
         <f>I20</f>
-        <v>-14142.135623730954</v>
+        <v>20000</v>
       </c>
       <c r="T5" s="4"/>
       <c r="U5" s="4"/>
@@ -32107,7 +32113,7 @@
       </c>
       <c r="S6" s="7">
         <f>I21</f>
-        <v>-14142.135623730948</v>
+        <v>0</v>
       </c>
       <c r="T6" s="4"/>
       <c r="U6" s="146"/>
@@ -32172,7 +32178,7 @@
       </c>
       <c r="S7" s="7">
         <f>I22</f>
-        <v>1.6335312732114935E-9</v>
+        <v>-9428090.415820634</v>
       </c>
       <c r="T7" s="4"/>
       <c r="U7" s="4"/>
@@ -32237,7 +32243,7 @@
       </c>
       <c r="S8" s="7">
         <f>I23</f>
-        <v>-14142.135623730954</v>
+        <v>20000</v>
       </c>
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
@@ -32302,7 +32308,7 @@
       </c>
       <c r="S9" s="7">
         <f>I24</f>
-        <v>-14142.135623730948</v>
+        <v>0</v>
       </c>
       <c r="T9" s="4"/>
       <c r="U9" s="4"/>
@@ -32368,7 +32374,7 @@
       </c>
       <c r="S10" s="7">
         <f>I25</f>
-        <v>-1.6335312732114935E-9</v>
+        <v>9428090.415820634</v>
       </c>
       <c r="T10" s="4"/>
       <c r="U10" s="4"/>
@@ -32928,7 +32934,7 @@
       </c>
       <c r="I20" s="151">
         <f>B54*I28+C54*I29+D54*I30+E54*I31+F54*I32+G54*I33</f>
-        <v>-14142.135623730954</v>
+        <v>20000</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>36</v>
@@ -32969,7 +32975,7 @@
       </c>
       <c r="I21" s="151">
         <f>B55*I28+C55*I29+D55*I30+E55*I31+F55*I32+G55*I33</f>
-        <v>-14142.135623730948</v>
+        <v>0</v>
       </c>
       <c r="L21" s="9"/>
       <c r="M21" s="78">
@@ -33050,7 +33056,7 @@
       </c>
       <c r="I22" s="151">
         <f>B56*I28+C56*I29+D56*I30+E56*I31+F56*I32+G56*I33</f>
-        <v>1.6335312732114935E-9</v>
+        <v>-9428090.415820634</v>
       </c>
       <c r="L22" s="78">
         <v>1</v>
@@ -33084,7 +33090,7 @@
       </c>
       <c r="V22" s="3">
         <f>S5</f>
-        <v>-14142.135623730954</v>
+        <v>20000</v>
       </c>
       <c r="W22" s="144" t="s">
         <v>52</v>
@@ -33137,7 +33143,7 @@
       </c>
       <c r="I23" s="151">
         <f>B57*I28+C57*I29+D57*I30+E57*I31+F57*I32+G57*I33</f>
-        <v>-14142.135623730954</v>
+        <v>20000</v>
       </c>
       <c r="L23" s="78">
         <v>2</v>
@@ -33171,7 +33177,7 @@
       </c>
       <c r="V23" s="3">
         <f>S6</f>
-        <v>-14142.135623730948</v>
+        <v>0</v>
       </c>
       <c r="W23" s="144" t="s">
         <v>51</v>
@@ -33223,7 +33229,7 @@
       </c>
       <c r="I24" s="151">
         <f>B58*I28+C58*I29+D58*I30+E58*I31+F58*I32+G58*I33</f>
-        <v>-14142.135623730948</v>
+        <v>0</v>
       </c>
       <c r="L24" s="78">
         <v>3</v>
@@ -33257,11 +33263,11 @@
       </c>
       <c r="V24" s="3">
         <f>S7</f>
-        <v>1.6335312732114935E-9</v>
+        <v>-9428090.415820634</v>
       </c>
       <c r="X24" s="153">
         <f>U59</f>
-        <v>1.2439023074359774E-18</v>
+        <v>-7.1779195032447753E-3</v>
       </c>
       <c r="Y24" s="154"/>
       <c r="Z24" s="156"/>
@@ -33307,7 +33313,7 @@
       </c>
       <c r="I25" s="151">
         <f>B59*I28+C59*I29+D59*I30+E59*I31+F59*I32+G59*I33</f>
-        <v>-1.6335312732114935E-9</v>
+        <v>9428090.415820634</v>
       </c>
       <c r="K25" s="2"/>
       <c r="L25" s="78">
@@ -33342,14 +33348,14 @@
       </c>
       <c r="V25" s="3">
         <f>S8</f>
-        <v>-14142.135623730954</v>
+        <v>20000</v>
       </c>
       <c r="W25" s="144" t="s">
         <v>111</v>
       </c>
       <c r="X25" s="153">
         <f>U66</f>
-        <v>-2.6937401188058954E-2</v>
+        <v>1.9047619047619049E-2</v>
       </c>
       <c r="Y25" s="154"/>
       <c r="Z25" s="156"/>
@@ -33402,14 +33408,14 @@
       </c>
       <c r="V26" s="3">
         <f>S9</f>
-        <v>-14142.135623730948</v>
+        <v>0</v>
       </c>
       <c r="W26" s="144" t="s">
         <v>112</v>
       </c>
       <c r="X26" s="153">
         <f>U67</f>
-        <v>-2.693740118805895E-2</v>
+        <v>1.9047619047619046E-2</v>
       </c>
       <c r="Y26" s="80"/>
       <c r="Z26" s="80"/>
@@ -33468,11 +33474,11 @@
       </c>
       <c r="V27" s="3">
         <f>S10</f>
-        <v>-1.6335312732114935E-9</v>
+        <v>9428090.415820634</v>
       </c>
       <c r="X27" s="157">
         <f>U61</f>
-        <v>-6.2091173120167685E-19</v>
+        <v>3.58087853126597E-3</v>
       </c>
       <c r="Y27" s="154"/>
       <c r="Z27" s="156"/>
@@ -33515,7 +33521,7 @@
       </c>
       <c r="I28" s="38">
         <f>-E6/2*E15*I38</f>
-        <v>-20000</v>
+        <v>14142.135623730952</v>
       </c>
       <c r="T28" s="4"/>
       <c r="V28" s="3"/>
@@ -33565,7 +33571,7 @@
       </c>
       <c r="I29" s="38">
         <f>-E6/2*E15*I39</f>
-        <v>2.45029690981724E-12</v>
+        <v>-14142.13562373095</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>119</v>
@@ -33620,7 +33626,7 @@
       </c>
       <c r="I30" s="38">
         <f>-1*(E15*E6^2)/12*I39</f>
-        <v>1.6335312732114935E-9</v>
+        <v>-9428090.415820634</v>
       </c>
       <c r="L30" s="9"/>
       <c r="M30" s="78">
@@ -33689,7 +33695,7 @@
       </c>
       <c r="I31" s="38">
         <f>-E6/2*E15*I38</f>
-        <v>-20000</v>
+        <v>14142.135623730952</v>
       </c>
       <c r="L31" s="78">
         <v>1</v>
@@ -33716,7 +33722,7 @@
       <c r="T31" s="4"/>
       <c r="V31" s="3" cm="1">
         <f t="array" ref="V31:V36">MMULT(M13:R18,V22:V27)</f>
-        <v>-14142.135623730954</v>
+        <v>20000</v>
       </c>
       <c r="X31" s="153"/>
       <c r="Y31" s="155"/>
@@ -33763,7 +33769,7 @@
       </c>
       <c r="I32" s="38">
         <f>-E6/2*E15*I39</f>
-        <v>2.45029690981724E-12</v>
+        <v>-14142.13562373095</v>
       </c>
       <c r="L32" s="78">
         <v>2</v>
@@ -33787,7 +33793,7 @@
         <v>464038.82515367185</v>
       </c>
       <c r="V32" s="3">
-        <v>-14142.135623730948</v>
+        <v>0</v>
       </c>
       <c r="AJ32" s="4"/>
       <c r="AK32" s="4"/>
@@ -33831,7 +33837,7 @@
       </c>
       <c r="I33" s="38">
         <f>1*(E15*E6^2)/12*I39</f>
-        <v>-1.6335312732114935E-9</v>
+        <v>9428090.415820634</v>
       </c>
       <c r="L33" s="78">
         <v>3</v>
@@ -33855,7 +33861,7 @@
         <v>875000000</v>
       </c>
       <c r="V33" s="3">
-        <v>1.6335312732114935E-9</v>
+        <v>-9428090.415820634</v>
       </c>
       <c r="AJ33" s="4"/>
       <c r="AK33" s="4"/>
@@ -33897,7 +33903,7 @@
         <v>464038.82515367179</v>
       </c>
       <c r="V34" s="3">
-        <v>-20000</v>
+        <v>14142.135623730952</v>
       </c>
       <c r="AB34" s="12"/>
       <c r="AD34" s="153"/>
@@ -33948,7 +33954,7 @@
         <v>-464038.82515367185</v>
       </c>
       <c r="V35" s="3">
-        <v>1.8189894035458565E-12</v>
+        <v>-14142.13562373095</v>
       </c>
       <c r="AB35" s="12"/>
       <c r="AD35" s="153"/>
@@ -34016,7 +34022,17 @@
         <v>1750000000</v>
       </c>
       <c r="V36" s="3">
-        <v>-1.6335312732114935E-9</v>
+        <v>9428090.415820634</v>
+      </c>
+      <c r="Y36" s="1" cm="1">
+        <f t="array" ref="Y36:AA41">MMULT(P22:R27,T13:V15)</f>
+        <v>-262664.06250000006</v>
+      </c>
+      <c r="Z36" s="1">
+        <v>-262335.9375</v>
+      </c>
+      <c r="AA36" s="1">
+        <v>-464038.82515367179</v>
       </c>
       <c r="AB36" s="12"/>
       <c r="AD36" s="4"/>
@@ -34047,10 +34063,19 @@
         <v>464038.82515367185</v>
       </c>
       <c r="I37" s="33">
-        <v>180</v>
+        <v>-45</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>120</v>
+      </c>
+      <c r="Y37" s="1">
+        <v>-262335.9375</v>
+      </c>
+      <c r="Z37" s="1">
+        <v>-262664.06249999994</v>
+      </c>
+      <c r="AA37" s="1">
+        <v>464038.82515367185</v>
       </c>
       <c r="AB37" s="12"/>
       <c r="AC37" s="4"/>
@@ -34085,7 +34110,7 @@
       </c>
       <c r="I38" s="25">
         <f>-COS(RADIANS(I37))</f>
-        <v>1</v>
+        <v>-0.70710678118654757</v>
       </c>
       <c r="L38" s="9"/>
       <c r="M38" s="78">
@@ -34105,6 +34130,15 @@
       </c>
       <c r="R38" s="78">
         <v>6</v>
+      </c>
+      <c r="Y38" s="1">
+        <v>464038.82515367179</v>
+      </c>
+      <c r="Z38" s="1">
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="AA38" s="1">
+        <v>875000000</v>
       </c>
       <c r="AD38" s="12"/>
     </row>
@@ -34135,7 +34169,7 @@
       </c>
       <c r="I39" s="25">
         <f>-SIN(RADIANS(I37))</f>
-        <v>-1.22514845490862E-16</v>
+        <v>0.70710678118654746</v>
       </c>
       <c r="L39" s="78">
         <v>1</v>
@@ -34158,6 +34192,15 @@
       </c>
       <c r="R39" s="11">
         <v>-464038.82515367179</v>
+      </c>
+      <c r="Y39" s="1">
+        <v>262664.06250000006</v>
+      </c>
+      <c r="Z39" s="1">
+        <v>262335.9375</v>
+      </c>
+      <c r="AA39" s="1">
+        <v>464038.82515367179</v>
       </c>
       <c r="AD39" s="12"/>
     </row>
@@ -34207,6 +34250,15 @@
       <c r="R40" s="11">
         <v>464038.82515367185</v>
       </c>
+      <c r="Y40" s="1">
+        <v>262335.9375</v>
+      </c>
+      <c r="Z40" s="1">
+        <v>262664.06249999994</v>
+      </c>
+      <c r="AA40" s="1">
+        <v>-464038.82515367185</v>
+      </c>
       <c r="AC40" s="4"/>
       <c r="AD40" s="12"/>
       <c r="AE40" s="4"/>
@@ -34258,6 +34310,15 @@
       <c r="R41" s="11">
         <v>875000000</v>
       </c>
+      <c r="Y41" s="1">
+        <v>464038.82515367179</v>
+      </c>
+      <c r="Z41" s="1">
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="AA41" s="1">
+        <v>1750000000</v>
+      </c>
       <c r="AD41" s="12"/>
     </row>
     <row r="42" spans="2:83" x14ac:dyDescent="0.2">
@@ -34307,6 +34368,25 @@
       <c r="R43" s="11">
         <v>-656250</v>
       </c>
+      <c r="Y43" s="1" cm="1">
+        <f t="array" ref="Y43:AD45">MMULT(M13:O15,M34:R36)</f>
+        <v>-262664.06250000006</v>
+      </c>
+      <c r="Z43" s="1">
+        <v>-262335.9375</v>
+      </c>
+      <c r="AA43" s="1">
+        <v>464038.82515367179</v>
+      </c>
+      <c r="AB43" s="1">
+        <v>371231.06012293749</v>
+      </c>
+      <c r="AC43" s="1">
+        <v>-232.01941257686121</v>
+      </c>
+      <c r="AD43" s="1">
+        <v>464038.82515367179</v>
+      </c>
     </row>
     <row r="44" spans="2:83" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
@@ -34332,6 +34412,24 @@
       </c>
       <c r="R44" s="11">
         <v>1750000000</v>
+      </c>
+      <c r="Y44" s="1">
+        <v>-262335.9375</v>
+      </c>
+      <c r="Z44" s="1">
+        <v>-262664.06249999994</v>
+      </c>
+      <c r="AA44" s="1">
+        <v>-464038.82515367185</v>
+      </c>
+      <c r="AB44" s="1">
+        <v>371231.06012293743</v>
+      </c>
+      <c r="AC44" s="1">
+        <v>232.01941257683211</v>
+      </c>
+      <c r="AD44" s="1">
+        <v>-464038.82515367185</v>
       </c>
     </row>
     <row r="45" spans="2:83" x14ac:dyDescent="0.2">
@@ -34354,6 +34452,24 @@
       </c>
       <c r="G45" s="152">
         <v>0</v>
+      </c>
+      <c r="Y45" s="1">
+        <v>-464038.82515367179</v>
+      </c>
+      <c r="Z45" s="1">
+        <v>464038.82515367185</v>
+      </c>
+      <c r="AA45" s="1">
+        <v>875000000</v>
+      </c>
+      <c r="AB45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="1">
+        <v>-656250</v>
+      </c>
+      <c r="AD45" s="1">
+        <v>1750000000</v>
       </c>
       <c r="AE45" s="29"/>
       <c r="AF45" s="29"/>
@@ -34472,7 +34588,7 @@
       </c>
       <c r="U48" s="145" cm="1">
         <f t="array" ref="U48:U49">V33:V34</f>
-        <v>1.6335312732114935E-9</v>
+        <v>-9428090.415820634</v>
       </c>
     </row>
     <row r="49" spans="2:101" x14ac:dyDescent="0.2">
@@ -34516,7 +34632,7 @@
         <v>r14</v>
       </c>
       <c r="U49" s="142">
-        <v>-20000</v>
+        <v>14142.135623730952</v>
       </c>
       <c r="AH49" s="2"/>
       <c r="AI49" s="2"/>
@@ -34563,7 +34679,7 @@
       </c>
       <c r="U50" s="3">
         <f>V35</f>
-        <v>1.8189894035458565E-12</v>
+        <v>-14142.13562373095</v>
       </c>
       <c r="AH50" s="2"/>
       <c r="AI50" s="2"/>
@@ -34871,18 +34987,18 @@
       </c>
       <c r="S59" s="3" cm="1">
         <f t="array" ref="S59:S61">U48:U50</f>
-        <v>1.6335312732114935E-9</v>
+        <v>-9428090.415820634</v>
       </c>
       <c r="U59" s="153" cm="1">
         <f t="array" ref="U59:U61">MMULT(_xlfn.ANCHORARRAY(M59),_xlfn.ANCHORARRAY(S59))</f>
-        <v>1.2439023074359774E-18</v>
+        <v>-7.1779195032447753E-3</v>
       </c>
       <c r="V59" s="1" t="s">
         <v>57</v>
       </c>
       <c r="W59" s="1">
         <f>1000*U59</f>
-        <v>1.2439023074359774E-15</v>
+        <v>-7.1779195032447749</v>
       </c>
       <c r="X59" s="1" t="s">
         <v>55</v>
@@ -34920,10 +35036,10 @@
       </c>
       <c r="P60" s="3"/>
       <c r="S60" s="1">
-        <v>-20000</v>
+        <v>14142.135623730952</v>
       </c>
       <c r="U60" s="153">
-        <v>-3.8095238095238092E-2</v>
+        <v>2.6937401188058954E-2</v>
       </c>
       <c r="V60" s="1" t="s">
         <v>3</v>
@@ -34961,17 +35077,17 @@
       </c>
       <c r="P61" s="3"/>
       <c r="S61" s="1">
-        <v>1.8189894035458565E-12</v>
+        <v>-14142.13562373095</v>
       </c>
       <c r="U61" s="153">
-        <v>-6.2091173120167685E-19</v>
+        <v>3.58087853126597E-3</v>
       </c>
       <c r="V61" s="1" t="s">
         <v>57</v>
       </c>
       <c r="W61" s="1">
         <f>1000*U61</f>
-        <v>-6.209117312016769E-16</v>
+        <v>3.5808785312659701</v>
       </c>
       <c r="X61" s="1" t="s">
         <v>55</v>
@@ -35061,7 +35177,7 @@
       </c>
       <c r="U66" s="1">
         <f>COS(RADIANS(Q12))*U60</f>
-        <v>-2.6937401188058954E-2</v>
+        <v>1.9047619047619049E-2</v>
       </c>
       <c r="V66" s="1" t="s">
         <v>3</v>
@@ -35077,7 +35193,7 @@
       </c>
       <c r="U67" s="1">
         <f>SIN(RADIANS(Q12))*U60</f>
-        <v>-2.693740118805895E-2</v>
+        <v>1.9047619047619046E-2</v>
       </c>
       <c r="V67" s="1" t="s">
         <v>3</v>
@@ -35223,11 +35339,11 @@
       </c>
       <c r="V77" s="3">
         <f>I28</f>
-        <v>-20000</v>
+        <v>14142.135623730952</v>
       </c>
       <c r="X77" s="3" cm="1">
         <f t="array" ref="X77:X82">MMULT(M77:R82,_xlfn.ANCHORARRAY(T77))-V77:V82</f>
-        <v>40000</v>
+        <v>-28284.271247461904</v>
       </c>
       <c r="BE77" s="4"/>
       <c r="BK77" s="6"/>
@@ -35273,10 +35389,10 @@
       </c>
       <c r="V78" s="3">
         <f>I29</f>
-        <v>2.45029690981724E-12</v>
+        <v>-14142.13562373095</v>
       </c>
       <c r="X78" s="1">
-        <v>-2.0414593441634803E-12</v>
+        <v>11781.577485869859</v>
       </c>
       <c r="BE78" s="12"/>
       <c r="BK78" s="6"/>
@@ -35318,11 +35434,11 @@
         <v>875000000</v>
       </c>
       <c r="T79" s="1">
-        <v>1.2439023074359774E-18</v>
+        <v>-7.1779195032447753E-3</v>
       </c>
       <c r="V79" s="3">
         <f>I30</f>
-        <v>1.6335312732114935E-9</v>
+        <v>-9428090.415820634</v>
       </c>
       <c r="X79" s="1">
         <v>0</v>
@@ -35367,11 +35483,11 @@
         <v>0</v>
       </c>
       <c r="T80" s="1">
-        <v>-3.8095238095238092E-2</v>
+        <v>2.6937401188058954E-2</v>
       </c>
       <c r="V80" s="3">
         <f>I31</f>
-        <v>-20000</v>
+        <v>14142.135623730952</v>
       </c>
       <c r="X80" s="1">
         <v>0</v>
@@ -35411,10 +35527,10 @@
       </c>
       <c r="V81" s="3">
         <f>I32</f>
-        <v>2.45029690981724E-12</v>
+        <v>-14142.13562373095</v>
       </c>
       <c r="X81" s="1">
-        <v>-2.8591344754709997E-12</v>
+        <v>16502.69376159204</v>
       </c>
       <c r="BE81" s="12"/>
       <c r="BK81" s="2"/>
@@ -35448,14 +35564,14 @@
         <v>1750000000</v>
       </c>
       <c r="T82" s="1">
-        <v>-6.2091173120167685E-19</v>
+        <v>3.58087853126597E-3</v>
       </c>
       <c r="V82" s="3">
         <f>I33</f>
-        <v>-1.6335312732114935E-9</v>
+        <v>9428090.415820634</v>
       </c>
       <c r="X82" s="1">
-        <v>1.6353502626150393E-9</v>
+        <v>-9442232.5514443666</v>
       </c>
       <c r="BE82" s="12"/>
       <c r="BK82" s="7"/>
@@ -37999,6 +38115,13 @@
       <c r="BN16" s="12"/>
     </row>
     <row r="17" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B17" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E17" s="1">
+        <f>C5*E6</f>
+        <v>2828.4271247461902</v>
+      </c>
       <c r="L17" s="78">
         <v>5</v>
       </c>
@@ -38059,6 +38182,13 @@
       <c r="BN17" s="12"/>
     </row>
     <row r="18" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B18" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E18" s="1">
+        <f>E5*E6</f>
+        <v>2828.4271247461897</v>
+      </c>
       <c r="L18" s="78">
         <v>6</v>
       </c>
@@ -42350,7 +42480,8 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/theory/FEM matriisit.xlsx
+++ b/theory/FEM matriisit.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="144">
   <si>
     <t xml:space="preserve">Laskenta perustuu Savonia AMK opintoihin, Ville Pekkalan opinnäytetyöhön ja netistä löytyneeseen (ei tällä hetkellä löydettävissä) Matti Lähteenmäki, Elementtimenetelmän perusteet opukseen</t>
   </si>
@@ -583,13 +583,25 @@
     <t xml:space="preserve">Yhdistetty jäykkyysmatriisi tukien kierto huomioituna</t>
   </si>
   <si>
+    <t xml:space="preserve">Kierretyt siirtymät</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kierretyt voimat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kierretyt tukireaktiot</t>
   </si>
   <si>
     <t xml:space="preserve">r22’</t>
   </si>
   <si>
     <t xml:space="preserve">r41’</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Globaalit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">siirtymät</t>
   </si>
 </sst>
 </file>
@@ -50240,10 +50252,15 @@
       <c r="AU88" s="0"/>
       <c r="AV88" s="0"/>
       <c r="AW88" s="0"/>
-      <c r="AX88" s="0"/>
+      <c r="AX88" s="0" t="s">
+        <v>137</v>
+      </c>
       <c r="AY88" s="0"/>
       <c r="AZ88" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
+      </c>
+      <c r="BB88" s="0" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51116,7 +51133,7 @@
       </c>
       <c r="AQ106" s="13"/>
       <c r="AR106" s="13" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AS106" s="13"/>
       <c r="AT106" s="21"/>
@@ -51294,7 +51311,7 @@
         <v>656250</v>
       </c>
       <c r="AR109" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AT109" s="7"/>
       <c r="AV109" s="13"/>
@@ -51517,7 +51534,9 @@
       </c>
       <c r="AX115" s="0"/>
       <c r="AY115" s="0"/>
-      <c r="AZ115" s="7"/>
+      <c r="AZ115" s="7" t="s">
+        <v>142</v>
+      </c>
       <c r="BB115" s="7"/>
       <c r="BE115" s="7"/>
       <c r="BK115" s="21"/>
@@ -51575,6 +51594,9 @@
       </c>
       <c r="AX116" s="0"/>
       <c r="AY116" s="0"/>
+      <c r="AZ116" s="1" t="s">
+        <v>143</v>
+      </c>
       <c r="BK116" s="21"/>
       <c r="BL116" s="21"/>
       <c r="BM116" s="21"/>

--- a/theory/FEM matriisit.xlsx
+++ b/theory/FEM matriisit.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="155">
   <si>
     <t xml:space="preserve">Laskenta perustuu Savonia AMK opintoihin, Ville Pekkalan opinnäytetyöhön ja netistä löytyneeseen (ei tällä hetkellä löydettävissä) Matti Lähteenmäki, Elementtimenetelmän perusteet opukseen</t>
   </si>
@@ -605,10 +605,37 @@
     <t xml:space="preserve">siirtymät</t>
   </si>
   <si>
+    <t xml:space="preserve">sx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">er</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ex</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tukien ja vapautusten kiertomatriisi</t>
   </si>
   <si>
     <t xml:space="preserve">Tukien ja vapautusten kiertomatriisin transpoosi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-sin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">r17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sauvan lokaalin X-akselin suuunnassa</t>
   </si>
 </sst>
 </file>
@@ -628,7 +655,7 @@
     <numFmt numFmtId="173" formatCode="0.000000"/>
     <numFmt numFmtId="174" formatCode="0.00"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -755,8 +782,15 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -809,6 +843,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF81D41A"/>
         <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF999999"/>
+        <bgColor rgb="FF9999FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2A6099"/>
+        <bgColor rgb="FF666699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EA6B"/>
+        <bgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -912,52 +964,52 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="166">
+  <cellXfs count="177">
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -965,15 +1017,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -985,11 +1037,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -997,43 +1049,43 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1041,23 +1093,23 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1065,7 +1117,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1073,15 +1125,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1089,15 +1141,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1105,59 +1157,59 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1165,19 +1217,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1185,107 +1237,107 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1293,15 +1345,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1313,7 +1365,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1329,15 +1381,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1353,15 +1405,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1377,15 +1429,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1397,7 +1449,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1405,11 +1457,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1417,27 +1469,27 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1445,27 +1497,27 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1477,11 +1529,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1489,91 +1541,135 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="10" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="18" fillId="5" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1792,14 +1888,14 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF92D050"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FF2A6099"/>
       <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -1811,7 +1907,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFD4EA6B"/>
       <rgbColor rgb="FFFFEB9C"/>
       <rgbColor rgb="FF84E291"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -1824,7 +1920,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF92D050"/>
+      <rgbColor rgb="FF999999"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF13501B"/>
@@ -1849,9 +1945,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>61</xdr:col>
-      <xdr:colOff>271440</xdr:colOff>
+      <xdr:colOff>271080</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>30960</xdr:rowOff>
+      <xdr:rowOff>30600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1864,8 +1960,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="30732840" y="3491280"/>
-          <a:ext cx="4558680" cy="2788200"/>
+          <a:off x="30748680" y="3491280"/>
+          <a:ext cx="4562280" cy="2787840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1887,9 +1983,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>270720</xdr:colOff>
+      <xdr:colOff>270360</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>73440</xdr:rowOff>
+      <xdr:rowOff>73080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1902,8 +1998,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3841200" y="293760"/>
-          <a:ext cx="1477800" cy="2370600"/>
+          <a:off x="3843720" y="293760"/>
+          <a:ext cx="1478160" cy="2370240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1925,9 +2021,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>551160</xdr:colOff>
+      <xdr:colOff>550800</xdr:colOff>
       <xdr:row>99</xdr:row>
-      <xdr:rowOff>64800</xdr:rowOff>
+      <xdr:rowOff>64440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1940,8 +2036,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2841120" y="11925000"/>
-          <a:ext cx="3309480" cy="3265560"/>
+          <a:off x="2842920" y="11925000"/>
+          <a:ext cx="3310560" cy="3265200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1963,9 +2059,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>220680</xdr:colOff>
+      <xdr:colOff>220320</xdr:colOff>
       <xdr:row>92</xdr:row>
-      <xdr:rowOff>71280</xdr:rowOff>
+      <xdr:rowOff>70920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1978,8 +2074,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6639120" y="11823120"/>
-          <a:ext cx="3678120" cy="2307240"/>
+          <a:off x="6642360" y="11823120"/>
+          <a:ext cx="3680280" cy="2306880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2006,9 +2102,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>63</xdr:col>
-      <xdr:colOff>165600</xdr:colOff>
+      <xdr:colOff>165240</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>27360</xdr:rowOff>
+      <xdr:rowOff>27000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2021,8 +2117,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="30974040" y="3263760"/>
-          <a:ext cx="6159240" cy="3469320"/>
+          <a:off x="30974760" y="3263760"/>
+          <a:ext cx="6158880" cy="3468960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2044,9 +2140,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>98280</xdr:colOff>
+      <xdr:colOff>97920</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>133200</xdr:rowOff>
+      <xdr:rowOff>132840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2060,7 +2156,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3556080" y="276480"/>
-          <a:ext cx="1503000" cy="2447640"/>
+          <a:ext cx="1502640" cy="2447280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2087,9 +2183,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>63</xdr:col>
-      <xdr:colOff>15480</xdr:colOff>
+      <xdr:colOff>15120</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>27360</xdr:rowOff>
+      <xdr:rowOff>27000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2102,8 +2198,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="32666040" y="3263760"/>
-          <a:ext cx="5859000" cy="3469320"/>
+          <a:off x="32661360" y="3263760"/>
+          <a:ext cx="5859000" cy="3468960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2125,9 +2221,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>98280</xdr:colOff>
+      <xdr:colOff>97920</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>133200</xdr:rowOff>
+      <xdr:rowOff>132840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2141,7 +2237,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3556080" y="276480"/>
-          <a:ext cx="1503000" cy="2447640"/>
+          <a:ext cx="1502640" cy="2447280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2168,9 +2264,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>458280</xdr:colOff>
+      <xdr:colOff>457920</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>151200</xdr:rowOff>
+      <xdr:rowOff>150840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2184,7 +2280,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="5798520" cy="9104760"/>
+          <a:ext cx="5798160" cy="9104400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2211,9 +2307,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>270720</xdr:colOff>
+      <xdr:colOff>270360</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>34920</xdr:rowOff>
+      <xdr:rowOff>34560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2226,8 +2322,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3841200" y="293760"/>
-          <a:ext cx="1477800" cy="2332080"/>
+          <a:off x="3843720" y="293760"/>
+          <a:ext cx="1478160" cy="2331720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2260,8 +2356,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="16203240" y="2990520"/>
-          <a:ext cx="2916360" cy="1705680"/>
+          <a:off x="16210080" y="2990520"/>
+          <a:ext cx="2917080" cy="1705680"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2296,7 +2392,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="16241400" y="4286160"/>
+          <a:off x="16248240" y="4286160"/>
           <a:ext cx="389520" cy="219600"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -2333,8 +2429,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="16735320" y="3943080"/>
-          <a:ext cx="398160" cy="257760"/>
+          <a:off x="16742160" y="3943080"/>
+          <a:ext cx="399240" cy="257760"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2370,7 +2466,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="17218800" y="3695760"/>
+          <a:off x="17226720" y="3695760"/>
           <a:ext cx="389880" cy="238320"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -2407,8 +2503,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="17732160" y="3409920"/>
-          <a:ext cx="332640" cy="209880"/>
+          <a:off x="17740080" y="3409920"/>
+          <a:ext cx="332280" cy="209880"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2444,7 +2540,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="18188280" y="3162240"/>
+          <a:off x="18195840" y="3162240"/>
           <a:ext cx="362160" cy="209880"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -2481,7 +2577,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="18615600" y="2905200"/>
+          <a:off x="18623160" y="2905200"/>
           <a:ext cx="390960" cy="219600"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -2518,7 +2614,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="19109520" y="2533320"/>
+          <a:off x="19117080" y="2533320"/>
           <a:ext cx="419760" cy="267480"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -2544,9 +2640,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>56160</xdr:colOff>
+      <xdr:colOff>55800</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>27360</xdr:rowOff>
+      <xdr:rowOff>27000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2555,16 +2651,16 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="1143000">
-          <a:off x="16165080" y="4743000"/>
-          <a:ext cx="197640" cy="313200"/>
+          <a:off x="16172280" y="4743000"/>
+          <a:ext cx="197280" cy="312840"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
           <a:gdLst>
-            <a:gd name="textAreaLeft" fmla="*/ 0 w 197640"/>
-            <a:gd name="textAreaRight" fmla="*/ 198720 w 197640"/>
-            <a:gd name="textAreaTop" fmla="*/ 0 h 313200"/>
-            <a:gd name="textAreaBottom" fmla="*/ 314280 h 313200"/>
+            <a:gd name="textAreaLeft" fmla="*/ 0 w 197280"/>
+            <a:gd name="textAreaRight" fmla="*/ 198720 w 197280"/>
+            <a:gd name="textAreaTop" fmla="*/ 0 h 312840"/>
+            <a:gd name="textAreaBottom" fmla="*/ 314280 h 312840"/>
             <a:gd name="GluePoint1X" fmla="*/ 0 w 257175"/>
             <a:gd name="GluePoint1Y" fmla="*/ 0 h 314325"/>
             <a:gd name="GluePoint2X" fmla="*/ 47625 w 257175"/>
@@ -2640,11 +2736,11 @@
       <xdr:col>33</xdr:col>
       <xdr:colOff>49320</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>-360</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>246960</xdr:colOff>
+      <xdr:colOff>246600</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>8280</xdr:rowOff>
     </xdr:to>
@@ -2655,16 +2751,16 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="775800">
-          <a:off x="19120680" y="3047760"/>
-          <a:ext cx="197640" cy="313200"/>
+          <a:off x="19128240" y="3047760"/>
+          <a:ext cx="197280" cy="312840"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
           <a:gdLst>
-            <a:gd name="textAreaLeft" fmla="*/ 0 w 197640"/>
-            <a:gd name="textAreaRight" fmla="*/ 198720 w 197640"/>
-            <a:gd name="textAreaTop" fmla="*/ 0 h 313200"/>
-            <a:gd name="textAreaBottom" fmla="*/ 314280 h 313200"/>
+            <a:gd name="textAreaLeft" fmla="*/ 0 w 197280"/>
+            <a:gd name="textAreaRight" fmla="*/ 198720 w 197280"/>
+            <a:gd name="textAreaTop" fmla="*/ 0 h 312840"/>
+            <a:gd name="textAreaBottom" fmla="*/ 314280 h 312840"/>
             <a:gd name="GluePoint1X" fmla="*/ 0 w 257175"/>
             <a:gd name="GluePoint1Y" fmla="*/ 0 h 314325"/>
             <a:gd name="GluePoint2X" fmla="*/ 47625 w 257175"/>
@@ -2744,9 +2840,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>113400</xdr:colOff>
+      <xdr:colOff>113040</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>65880</xdr:rowOff>
+      <xdr:rowOff>65520</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2755,8 +2851,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19120680" y="3305160"/>
-          <a:ext cx="64440" cy="113400"/>
+          <a:off x="19128240" y="3305160"/>
+          <a:ext cx="64080" cy="113040"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -2797,9 +2893,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>322920</xdr:colOff>
+      <xdr:colOff>322560</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>65880</xdr:rowOff>
+      <xdr:rowOff>65520</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2808,8 +2904,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19271880" y="3152880"/>
-          <a:ext cx="122760" cy="113400"/>
+          <a:off x="19279440" y="3152880"/>
+          <a:ext cx="122400" cy="113040"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -2855,9 +2951,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>270720</xdr:colOff>
+      <xdr:colOff>270360</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>34920</xdr:rowOff>
+      <xdr:rowOff>34560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2870,8 +2966,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3841200" y="293760"/>
-          <a:ext cx="1477800" cy="2332080"/>
+          <a:off x="3843720" y="293760"/>
+          <a:ext cx="1478160" cy="2331720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2904,8 +3000,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="16753680" y="2990520"/>
-          <a:ext cx="2916360" cy="1705680"/>
+          <a:off x="16759440" y="2990520"/>
+          <a:ext cx="2917080" cy="1705680"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2940,7 +3036,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16391880" y="4000320"/>
+          <a:off x="16397640" y="4000320"/>
           <a:ext cx="400320" cy="505440"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -2977,8 +3073,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="16344000" y="2305080"/>
-          <a:ext cx="2974680" cy="1704960"/>
+          <a:off x="16349760" y="2305080"/>
+          <a:ext cx="2975400" cy="1704960"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3013,7 +3109,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19308960" y="2305080"/>
+          <a:off x="19315440" y="2305080"/>
           <a:ext cx="324360" cy="514800"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -3033,9 +3129,9 @@
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>32</xdr:col>
-      <xdr:colOff>325080</xdr:colOff>
+      <xdr:colOff>325440</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>86400</xdr:rowOff>
+      <xdr:rowOff>86760</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
@@ -3050,16 +3146,16 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="5810400">
-          <a:off x="19395360" y="2982600"/>
-          <a:ext cx="256320" cy="254880"/>
+          <a:off x="19402200" y="2982600"/>
+          <a:ext cx="255960" cy="254520"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
           <a:gdLst>
-            <a:gd name="textAreaLeft" fmla="*/ 0 w 256320"/>
-            <a:gd name="textAreaRight" fmla="*/ 257400 w 256320"/>
-            <a:gd name="textAreaTop" fmla="*/ 0 h 254880"/>
-            <a:gd name="textAreaBottom" fmla="*/ 255960 h 254880"/>
+            <a:gd name="textAreaLeft" fmla="*/ 0 w 255960"/>
+            <a:gd name="textAreaRight" fmla="*/ 257400 w 255960"/>
+            <a:gd name="textAreaTop" fmla="*/ 0 h 254520"/>
+            <a:gd name="textAreaBottom" fmla="*/ 255960 h 254520"/>
             <a:gd name="GluePoint1X" fmla="*/ 0 w 257175"/>
             <a:gd name="GluePoint1Y" fmla="*/ 0 h 314325"/>
             <a:gd name="GluePoint2X" fmla="*/ 47625 w 257175"/>
@@ -3138,10 +3234,10 @@
       <xdr:rowOff>133560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>360</xdr:colOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>551160</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>94320</xdr:rowOff>
+      <xdr:rowOff>93960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3150,8 +3246,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19499760" y="3181680"/>
-          <a:ext cx="122760" cy="113040"/>
+          <a:off x="19506240" y="3181680"/>
+          <a:ext cx="122400" cy="112680"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -3192,9 +3288,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
-      <xdr:colOff>332280</xdr:colOff>
+      <xdr:colOff>331920</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>37080</xdr:rowOff>
+      <xdr:rowOff>36720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3203,8 +3299,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19280520" y="2971800"/>
-          <a:ext cx="122760" cy="113400"/>
+          <a:off x="19287000" y="2971800"/>
+          <a:ext cx="122400" cy="113040"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -3256,7 +3352,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16895160" y="3695760"/>
+          <a:off x="16900920" y="3695760"/>
           <a:ext cx="400680" cy="505080"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -3293,7 +3389,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17426880" y="3371760"/>
+          <a:off x="17433000" y="3371760"/>
           <a:ext cx="400320" cy="505080"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -3330,7 +3426,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17987400" y="3028680"/>
+          <a:off x="17993520" y="3028680"/>
           <a:ext cx="400680" cy="505440"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -3367,7 +3463,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18586440" y="2705040"/>
+          <a:off x="18592560" y="2705040"/>
           <a:ext cx="400320" cy="505440"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -3393,9 +3489,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>36720</xdr:colOff>
+      <xdr:colOff>36360</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>8640</xdr:rowOff>
+      <xdr:rowOff>8280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3404,8 +3500,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16544160" y="4686480"/>
-          <a:ext cx="349920" cy="351360"/>
+          <a:off x="16549920" y="4686480"/>
+          <a:ext cx="349560" cy="351000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3451,9 +3547,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>270720</xdr:colOff>
+      <xdr:colOff>270360</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>149760</xdr:rowOff>
+      <xdr:rowOff>149400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3466,8 +3562,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3841200" y="331920"/>
-          <a:ext cx="1477800" cy="2865960"/>
+          <a:off x="3843720" y="331920"/>
+          <a:ext cx="1478160" cy="2865600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3489,9 +3585,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>551160</xdr:colOff>
+      <xdr:colOff>550800</xdr:colOff>
       <xdr:row>96</xdr:row>
-      <xdr:rowOff>34560</xdr:rowOff>
+      <xdr:rowOff>34200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3504,8 +3600,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2841120" y="14668200"/>
-          <a:ext cx="3309480" cy="3540240"/>
+          <a:off x="2842920" y="14668200"/>
+          <a:ext cx="3310560" cy="3539880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3527,9 +3623,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>220680</xdr:colOff>
+      <xdr:colOff>220320</xdr:colOff>
       <xdr:row>90</xdr:row>
-      <xdr:rowOff>2880</xdr:rowOff>
+      <xdr:rowOff>2520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3542,8 +3638,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6639120" y="14528160"/>
-          <a:ext cx="3678120" cy="2505600"/>
+          <a:off x="6642360" y="14528160"/>
+          <a:ext cx="3680280" cy="2505240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3565,9 +3661,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>61</xdr:col>
-      <xdr:colOff>365040</xdr:colOff>
+      <xdr:colOff>364680</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>94680</xdr:rowOff>
+      <xdr:rowOff>94320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3580,8 +3676,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="29343960" y="3476880"/>
-          <a:ext cx="6041160" cy="3856680"/>
+          <a:off x="29358360" y="3476880"/>
+          <a:ext cx="6046200" cy="3856320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3608,9 +3704,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>270720</xdr:colOff>
+      <xdr:colOff>270360</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>55440</xdr:rowOff>
+      <xdr:rowOff>110880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3623,8 +3719,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3841200" y="293760"/>
-          <a:ext cx="1477800" cy="2332080"/>
+          <a:off x="3843720" y="293760"/>
+          <a:ext cx="1478160" cy="2331720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3642,13 +3738,13 @@
       <xdr:col>28</xdr:col>
       <xdr:colOff>454320</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>60480</xdr:rowOff>
+      <xdr:rowOff>15120</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
       <xdr:colOff>47520</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>98280</xdr:rowOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>67680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp>
       <xdr:nvCxnSpPr>
@@ -3657,8 +3753,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="16761240" y="3507120"/>
-          <a:ext cx="2909520" cy="1953360"/>
+          <a:off x="16768080" y="3337560"/>
+          <a:ext cx="2910240" cy="1759680"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3677,14 +3773,14 @@
     <xdr:from>
       <xdr:col>28</xdr:col>
       <xdr:colOff>493200</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>153000</xdr:rowOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>99000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>318600</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>50400</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>149760</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp>
       <xdr:nvCxnSpPr>
@@ -3693,8 +3789,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="16800120" y="4989240"/>
-          <a:ext cx="385560" cy="248040"/>
+          <a:off x="16806960" y="4648320"/>
+          <a:ext cx="386640" cy="226080"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3714,14 +3810,14 @@
     <xdr:from>
       <xdr:col>29</xdr:col>
       <xdr:colOff>421560</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>108720</xdr:rowOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>78480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
       <xdr:colOff>266400</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>54360</xdr:rowOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>1080</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp>
       <xdr:nvCxnSpPr>
@@ -3730,8 +3826,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="17288280" y="4594320"/>
-          <a:ext cx="396360" cy="296640"/>
+          <a:off x="17296200" y="4277160"/>
+          <a:ext cx="396360" cy="273600"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3751,14 +3847,14 @@
     <xdr:from>
       <xdr:col>30</xdr:col>
       <xdr:colOff>352080</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>121320</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
       <xdr:colOff>190080</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>97920</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>151200</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp>
       <xdr:nvCxnSpPr>
@@ -3767,8 +3863,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="17769960" y="4310280"/>
-          <a:ext cx="389880" cy="273600"/>
+          <a:off x="17777880" y="3969360"/>
+          <a:ext cx="389520" cy="205560"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3788,14 +3884,14 @@
     <xdr:from>
       <xdr:col>31</xdr:col>
       <xdr:colOff>313920</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>21600</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>105120</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>95040</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>87120</xdr:rowOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>79200</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp>
       <xdr:nvCxnSpPr>
@@ -3804,8 +3900,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="18283320" y="3981600"/>
-          <a:ext cx="332640" cy="240840"/>
+          <a:off x="18290880" y="3777840"/>
+          <a:ext cx="332640" cy="149760"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3826,13 +3922,13 @@
       <xdr:col>32</xdr:col>
       <xdr:colOff>218880</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>86760</xdr:rowOff>
+      <xdr:rowOff>18720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
       <xdr:colOff>29520</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>153000</xdr:rowOff>
+      <xdr:rowOff>83160</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp>
       <xdr:nvCxnSpPr>
@@ -3841,8 +3937,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="18739440" y="3708720"/>
-          <a:ext cx="362160" cy="241920"/>
+          <a:off x="18747000" y="3516480"/>
+          <a:ext cx="362160" cy="239760"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3868,8 +3964,8 @@
     <xdr:to>
       <xdr:col>33</xdr:col>
       <xdr:colOff>485640</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>43560</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>150840</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp>
       <xdr:nvCxnSpPr>
@@ -3878,8 +3974,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="19166760" y="3413880"/>
-          <a:ext cx="390960" cy="252000"/>
+          <a:off x="19174320" y="3289320"/>
+          <a:ext cx="390960" cy="184320"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3915,8 +4011,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="19660680" y="2986200"/>
-          <a:ext cx="419760" cy="307440"/>
+          <a:off x="19668240" y="2884680"/>
+          <a:ext cx="419760" cy="284400"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3935,15 +4031,15 @@
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>414720</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>154080</xdr:rowOff>
+      <xdr:colOff>415800</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>119520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
-      <xdr:colOff>56160</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>160920</xdr:rowOff>
+      <xdr:colOff>54720</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>87840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3951,17 +4047,17 @@
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
-        <a:xfrm rot="1259400">
-          <a:off x="16710840" y="5511960"/>
-          <a:ext cx="201240" cy="344880"/>
+        <a:xfrm rot="1157400">
+          <a:off x="16738560" y="5151600"/>
+          <a:ext cx="199800" cy="318960"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
           <a:gdLst>
-            <a:gd name="textAreaLeft" fmla="*/ 0 w 201240"/>
-            <a:gd name="textAreaRight" fmla="*/ 202320 w 201240"/>
-            <a:gd name="textAreaTop" fmla="*/ 0 h 344880"/>
-            <a:gd name="textAreaBottom" fmla="*/ 345960 h 344880"/>
+            <a:gd name="textAreaLeft" fmla="*/ 0 w 199800"/>
+            <a:gd name="textAreaRight" fmla="*/ 200880 w 199800"/>
+            <a:gd name="textAreaTop" fmla="*/ 0 h 318960"/>
+            <a:gd name="textAreaBottom" fmla="*/ 320040 h 318960"/>
             <a:gd name="GluePoint1X" fmla="*/ 0 w 257175"/>
             <a:gd name="GluePoint1Y" fmla="*/ 0 h 314325"/>
             <a:gd name="GluePoint2X" fmla="*/ 47625 w 257175"/>
@@ -4035,15 +4131,15 @@
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>48240</xdr:colOff>
+      <xdr:colOff>48960</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>125280</xdr:rowOff>
+      <xdr:rowOff>56880</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>247680</xdr:colOff>
+      <xdr:colOff>247320</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>138600</xdr:rowOff>
+      <xdr:rowOff>64080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4051,17 +4147,17 @@
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
-        <a:xfrm rot="906000">
-          <a:off x="19658520" y="3568320"/>
-          <a:ext cx="199440" cy="363960"/>
+        <a:xfrm rot="896400">
+          <a:off x="19680120" y="3379320"/>
+          <a:ext cx="198360" cy="357480"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
           <a:gdLst>
-            <a:gd name="textAreaLeft" fmla="*/ 0 w 199440"/>
-            <a:gd name="textAreaRight" fmla="*/ 200520 w 199440"/>
-            <a:gd name="textAreaTop" fmla="*/ 0 h 363960"/>
-            <a:gd name="textAreaBottom" fmla="*/ 365040 h 363960"/>
+            <a:gd name="textAreaLeft" fmla="*/ 0 w 198360"/>
+            <a:gd name="textAreaRight" fmla="*/ 199440 w 198360"/>
+            <a:gd name="textAreaTop" fmla="*/ 0 h 357480"/>
+            <a:gd name="textAreaBottom" fmla="*/ 358560 h 357480"/>
             <a:gd name="GluePoint1X" fmla="*/ 0 w 257175"/>
             <a:gd name="GluePoint1Y" fmla="*/ 0 h 314325"/>
             <a:gd name="GluePoint2X" fmla="*/ 47625 w 257175"/>
@@ -4136,14 +4232,14 @@
     <xdr:from>
       <xdr:col>33</xdr:col>
       <xdr:colOff>344520</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>65520</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>172800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
       <xdr:colOff>502920</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>163800</xdr:rowOff>
+      <xdr:rowOff>95760</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp>
       <xdr:nvCxnSpPr>
@@ -4152,7 +4248,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="19416240" y="3687480"/>
+          <a:off x="19423800" y="3495240"/>
           <a:ext cx="158760" cy="98640"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -4352,39 +4448,39 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9.57"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="9.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="9.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="21" min="20" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="22" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="22" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="9.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="26" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="26" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="35" min="30" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="11.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="10.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="9.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="41" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="9.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="45" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="45" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="49" min="49" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="50" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="50" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="1" width="12.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="56" min="56" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="57" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="57" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="63" style="1" width="9.14"/>
   </cols>
   <sheetData>
@@ -8303,7 +8399,7 @@
       </c>
       <c r="BC44" s="37"/>
       <c r="BD44" s="20" t="n">
-        <v>23333.3333333307</v>
+        <v>23333.3333333319</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8394,7 +8490,7 @@
       </c>
       <c r="BB45" s="36" t="n">
         <f aca="false" t="array" ref="BB45:BB48">AV71:AV74</f>
-        <v>-0.0363737839934569</v>
+        <v>-0.0363737839934568</v>
       </c>
       <c r="BC45" s="37"/>
       <c r="BD45" s="20" t="n">
@@ -8522,11 +8618,11 @@
         <v>20000</v>
       </c>
       <c r="BB46" s="36" t="n">
-        <v>81.9356733185918</v>
+        <v>81.9356733185917</v>
       </c>
       <c r="BC46" s="37"/>
       <c r="BD46" s="20" t="n">
-        <v>4.80940798297524E-009</v>
+        <v>4.8275978770107E-009</v>
       </c>
       <c r="CE46" s="2"/>
     </row>
@@ -8649,11 +8745,11 @@
         <v>-30000</v>
       </c>
       <c r="BB47" s="36" t="n">
-        <v>-0.0444444444444445</v>
+        <v>-0.0444444444444467</v>
       </c>
       <c r="BC47" s="34"/>
       <c r="BD47" s="34" t="n">
-        <v>2.63025867752731E-009</v>
+        <v>1.44427758641541E-009</v>
       </c>
       <c r="BS47" s="13"/>
       <c r="CE47" s="2"/>
@@ -8775,7 +8871,7 @@
         <v>-16666666.6666667</v>
       </c>
       <c r="BB48" s="40" t="n">
-        <v>-0.00394228224012533</v>
+        <v>-0.00394228224012535</v>
       </c>
       <c r="BC48" s="37"/>
       <c r="BD48" s="20" t="n">
@@ -8913,7 +9009,7 @@
       </c>
       <c r="BC49" s="37"/>
       <c r="BD49" s="20" t="n">
-        <v>427.724341874609</v>
+        <v>427.724341874613</v>
       </c>
       <c r="CW49" s="2"/>
     </row>
@@ -9235,11 +9331,11 @@
         <v>-10000</v>
       </c>
       <c r="BB52" s="36" t="n">
-        <v>81.9077129247945</v>
+        <v>81.9077129247944</v>
       </c>
       <c r="BC52" s="41"/>
       <c r="BD52" s="7" t="n">
-        <v>-3.98904376197606E-009</v>
+        <v>-3.97085386794061E-009</v>
       </c>
       <c r="BE52" s="17"/>
       <c r="BK52" s="42"/>
@@ -9431,7 +9527,7 @@
         <v>23333333.3333333</v>
       </c>
       <c r="BB54" s="44" t="n">
-        <v>0.00107667377451686</v>
+        <v>0.00107667377451688</v>
       </c>
       <c r="BC54" s="41"/>
       <c r="BD54" s="7" t="n">
@@ -10490,7 +10586,7 @@
         <v>-3.17460317460169E-010</v>
       </c>
       <c r="AN71" s="1" t="n">
-        <v>-5.98492922837861E-012</v>
+        <v>-5.98492922837857E-012</v>
       </c>
       <c r="AO71" s="1" t="n">
         <v>8.72013899222411E-010</v>
@@ -10499,10 +10595,10 @@
         <v>-2.42887058575122E-006</v>
       </c>
       <c r="AQ71" s="1" t="n">
-        <v>3.17460317460467E-010</v>
+        <v>3.17460317460466E-010</v>
       </c>
       <c r="AR71" s="1" t="n">
-        <v>7.76251408685903E-011</v>
+        <v>7.76251408685902E-011</v>
       </c>
       <c r="AT71" s="13" t="n">
         <f aca="false" t="array" ref="AT71:AT74">AV60:AV63</f>
@@ -10510,14 +10606,14 @@
       </c>
       <c r="AV71" s="36" t="n">
         <f aca="false" t="array" ref="AV71:AV78">MMULT(AK71:AR78,AT71:AT78)</f>
-        <v>-0.0363737839934569</v>
+        <v>-0.0363737839934568</v>
       </c>
       <c r="AW71" s="1" t="s">
         <v>78</v>
       </c>
       <c r="AX71" s="1" t="n">
         <f aca="false">1000*AV71</f>
-        <v>-36.3737839934569</v>
+        <v>-36.3737839934568</v>
       </c>
       <c r="AY71" s="1" t="s">
         <v>79</v>
@@ -10543,7 +10639,7 @@
         <v>1.26984126984086E-006</v>
       </c>
       <c r="AN72" s="1" t="n">
-        <v>-1.4330002168729E-007</v>
+        <v>-1.43300021687291E-007</v>
       </c>
       <c r="AO72" s="1" t="n">
         <v>-2.42887058575122E-006</v>
@@ -10555,13 +10651,13 @@
         <v>-1.26984126984168E-006</v>
       </c>
       <c r="AR72" s="1" t="n">
-        <v>-1.43260824873557E-007</v>
+        <v>-1.43260824873556E-007</v>
       </c>
       <c r="AT72" s="1" t="n">
         <v>20000</v>
       </c>
       <c r="AV72" s="36" t="n">
-        <v>81.9356733185918</v>
+        <v>81.9356733185917</v>
       </c>
       <c r="AW72" s="1" t="s">
         <v>12</v>
@@ -10578,34 +10674,34 @@
         <v>5</v>
       </c>
       <c r="AK73" s="1" t="n">
-        <v>-3.17460317460492E-010</v>
+        <v>-3.17460317460142E-010</v>
       </c>
       <c r="AL73" s="13" t="n">
-        <v>1.26984126984115E-006</v>
+        <v>1.26984126984081E-006</v>
       </c>
       <c r="AM73" s="13" t="n">
         <v>1.9047619047619E-006</v>
       </c>
       <c r="AN73" s="1" t="n">
-        <v>-3.17460317460311E-010</v>
+        <v>-3.17460317460371E-010</v>
       </c>
       <c r="AO73" s="1" t="n">
-        <v>-3.17460317460172E-010</v>
+        <v>-3.17460317460218E-010</v>
       </c>
       <c r="AP73" s="1" t="n">
-        <v>1.26984126984118E-006</v>
+        <v>1.26984126984079E-006</v>
       </c>
       <c r="AQ73" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AR73" s="1" t="n">
-        <v>-3.17460317460388E-010</v>
+        <v>-3.1746031746019E-010</v>
       </c>
       <c r="AT73" s="1" t="n">
         <v>-30000</v>
       </c>
       <c r="AV73" s="36" t="n">
-        <v>-0.0444444444444445</v>
+        <v>-0.0444444444444467</v>
       </c>
       <c r="AW73" s="1" t="s">
         <v>12</v>
@@ -10621,7 +10717,7 @@
         <v>6</v>
       </c>
       <c r="AK74" s="1" t="n">
-        <v>-5.98492922837839E-012</v>
+        <v>-5.98492922837866E-012</v>
       </c>
       <c r="AL74" s="1" t="n">
         <v>-1.43300021687291E-007</v>
@@ -10633,7 +10729,7 @@
         <v>1.19444874722225E-010</v>
       </c>
       <c r="AO74" s="1" t="n">
-        <v>7.76251408685901E-011</v>
+        <v>7.76251408685904E-011</v>
       </c>
       <c r="AP74" s="1" t="n">
         <v>-1.43260824873556E-007</v>
@@ -10642,20 +10738,20 @@
         <v>3.17460317460326E-010</v>
       </c>
       <c r="AR74" s="1" t="n">
-        <v>-4.78046630820132E-011</v>
+        <v>-4.78046630820137E-011</v>
       </c>
       <c r="AT74" s="1" t="n">
         <v>-16666666.6666667</v>
       </c>
       <c r="AV74" s="36" t="n">
-        <v>-0.00394228224012533</v>
+        <v>-0.00394228224012535</v>
       </c>
       <c r="AW74" s="1" t="s">
         <v>78</v>
       </c>
       <c r="AX74" s="1" t="n">
         <f aca="false">1000*AV74</f>
-        <v>-3.94228224012533</v>
+        <v>-3.94228224012535</v>
       </c>
       <c r="AY74" s="1" t="s">
         <v>79</v>
@@ -10689,7 +10785,7 @@
         <v>-3.17460317460169E-010</v>
       </c>
       <c r="AN75" s="1" t="n">
-        <v>7.762514086859E-011</v>
+        <v>7.76251408685905E-011</v>
       </c>
       <c r="AO75" s="1" t="n">
         <v>1.48534059813209E-009</v>
@@ -10698,10 +10794,10 @@
         <v>-2.4291188322382E-006</v>
       </c>
       <c r="AQ75" s="1" t="n">
-        <v>3.17460317460467E-010</v>
+        <v>3.17460317460466E-010</v>
       </c>
       <c r="AR75" s="1" t="n">
-        <v>-5.98492922837822E-012</v>
+        <v>-5.98492922837884E-012</v>
       </c>
       <c r="AT75" s="13" t="n">
         <f aca="false">AV64</f>
@@ -10751,7 +10847,7 @@
         <v>1.26984126984086E-006</v>
       </c>
       <c r="AN76" s="1" t="n">
-        <v>-1.43260824873556E-007</v>
+        <v>-1.43260824873557E-007</v>
       </c>
       <c r="AO76" s="13" t="n">
         <v>-2.4291188322382E-006</v>
@@ -10763,14 +10859,14 @@
         <v>-1.26984126984168E-006</v>
       </c>
       <c r="AR76" s="1" t="n">
-        <v>-1.43300021687291E-007</v>
+        <v>-1.4330002168729E-007</v>
       </c>
       <c r="AT76" s="13" t="n">
         <f aca="false">AV65</f>
         <v>-10000</v>
       </c>
       <c r="AV76" s="36" t="n">
-        <v>81.9077129247945</v>
+        <v>81.9077129247944</v>
       </c>
       <c r="AW76" s="1" t="s">
         <v>12</v>
@@ -10809,7 +10905,7 @@
         <v>3.17460317460326E-010</v>
       </c>
       <c r="AO77" s="13" t="n">
-        <v>3.17460317460466E-010</v>
+        <v>3.17460317460467E-010</v>
       </c>
       <c r="AP77" s="1" t="n">
         <v>-1.26984126984168E-006</v>
@@ -10848,7 +10944,7 @@
         <v>12</v>
       </c>
       <c r="AK78" s="1" t="n">
-        <v>7.76251408685901E-011</v>
+        <v>7.76251408685904E-011</v>
       </c>
       <c r="AL78" s="1" t="n">
         <v>-1.43260824873556E-007</v>
@@ -10857,10 +10953,10 @@
         <v>-3.17460317460309E-010</v>
       </c>
       <c r="AN78" s="1" t="n">
-        <v>-4.78046630820132E-011</v>
+        <v>-4.78046630820136E-011</v>
       </c>
       <c r="AO78" s="1" t="n">
-        <v>-5.98492922837845E-012</v>
+        <v>-5.98492922837864E-012</v>
       </c>
       <c r="AP78" s="1" t="n">
         <v>-1.43300021687291E-007</v>
@@ -10876,14 +10972,14 @@
         <v>23333333.3333333</v>
       </c>
       <c r="AV78" s="36" t="n">
-        <v>0.00107667377451686</v>
+        <v>0.00107667377451688</v>
       </c>
       <c r="AW78" s="1" t="s">
         <v>78</v>
       </c>
       <c r="AX78" s="1" t="n">
         <f aca="false">1000*AV78</f>
-        <v>1.07667377451686</v>
+        <v>1.07667377451688</v>
       </c>
       <c r="AY78" s="1" t="s">
         <v>79</v>
@@ -11195,7 +11291,7 @@
         <v>875000000</v>
       </c>
       <c r="AR88" s="1" t="n">
-        <v>-0.0363737839934569</v>
+        <v>-0.0363737839934568</v>
       </c>
       <c r="AT88" s="13" t="n">
         <f aca="false">I30</f>
@@ -11234,7 +11330,7 @@
         <v>0</v>
       </c>
       <c r="AR89" s="1" t="n">
-        <v>-0.0444444444444394</v>
+        <v>-0.0444444444444417</v>
       </c>
       <c r="AT89" s="13" t="n">
         <f aca="false">I31</f>
@@ -11273,7 +11369,7 @@
         <v>-656250</v>
       </c>
       <c r="AR90" s="1" t="n">
-        <v>-81.9356733185918</v>
+        <v>-81.9356733185917</v>
       </c>
       <c r="AT90" s="13" t="n">
         <f aca="false">I32</f>
@@ -11312,7 +11408,7 @@
         <v>1750000000</v>
       </c>
       <c r="AR91" s="1" t="n">
-        <v>-0.00394228224012533</v>
+        <v>-0.00394228224012535</v>
       </c>
       <c r="AT91" s="13" t="n">
         <f aca="false">I33</f>
@@ -12937,9 +13033,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="34" width="9.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="34" width="12.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="34" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="34" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="34" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="34" width="13.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="42" style="34" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="42" style="34" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="34" width="12.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="34" width="10.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="34" width="12.42"/>
@@ -17646,7 +17742,7 @@
       </c>
       <c r="BE47" s="37"/>
       <c r="BF47" s="37" t="n">
-        <v>29999.9999999996</v>
+        <v>29999.9999999989</v>
       </c>
       <c r="BG47" s="41"/>
       <c r="BH47" s="41"/>
@@ -17963,11 +18059,11 @@
       <c r="BC49" s="1"/>
       <c r="BD49" s="36" t="n">
         <f aca="false" t="array" ref="BD49:BD51">AV77:AV79</f>
-        <v>45.7223209577564</v>
+        <v>45.7223209577565</v>
       </c>
       <c r="BE49" s="37"/>
       <c r="BF49" s="37" t="n">
-        <v>-1.05173967313021E-008</v>
+        <v>-3.09591996483505E-009</v>
       </c>
       <c r="BG49" s="41"/>
       <c r="BH49" s="37"/>
@@ -18122,10 +18218,10 @@
       </c>
       <c r="BC50" s="1"/>
       <c r="BD50" s="36" t="n">
-        <v>-0.0571428571428592</v>
+        <v>-0.0571428571428578</v>
       </c>
       <c r="BF50" s="34" t="n">
-        <v>3.74711817130446E-010</v>
+        <v>1.13141140900552E-009</v>
       </c>
       <c r="BG50" s="41"/>
       <c r="BH50" s="37"/>
@@ -18264,7 +18360,7 @@
       </c>
       <c r="BC51" s="1"/>
       <c r="BD51" s="40" t="n">
-        <v>-0.00642857142857143</v>
+        <v>-0.00642857142857144</v>
       </c>
       <c r="BE51" s="37"/>
       <c r="BF51" s="37" t="n">
@@ -18650,7 +18746,7 @@
       </c>
       <c r="BE54" s="37"/>
       <c r="BF54" s="37" t="n">
-        <v>4997363.43573621</v>
+        <v>4997363.43573622</v>
       </c>
       <c r="BG54" s="41"/>
       <c r="BH54" s="37"/>
@@ -18813,7 +18909,7 @@
       </c>
       <c r="BE55" s="41"/>
       <c r="BF55" s="41" t="n">
-        <v>6.7830114858225E-009</v>
+        <v>-6.85759005136788E-010</v>
       </c>
       <c r="BG55" s="41"/>
       <c r="BH55" s="41"/>
@@ -19128,7 +19224,7 @@
       </c>
       <c r="BC57" s="1"/>
       <c r="BD57" s="40" t="n">
-        <v>0.00642857142857143</v>
+        <v>0.00642857142857144</v>
       </c>
       <c r="BE57" s="41"/>
       <c r="BF57" s="41" t="n">
@@ -19285,7 +19381,7 @@
       </c>
       <c r="BC58" s="41"/>
       <c r="BD58" s="40" t="n">
-        <v>-0.00952682274011103</v>
+        <v>-0.00952682274011107</v>
       </c>
       <c r="BE58" s="41"/>
       <c r="BF58" s="41" t="n">
@@ -19642,7 +19738,7 @@
       </c>
       <c r="BC64" s="34" t="n">
         <f aca="false" t="array" ref="BC64:BC69">MMULT(B45:G50,BB64:BB69)</f>
-        <v>29999.9999999996</v>
+        <v>29999.9999999989</v>
       </c>
       <c r="BE64" s="132"/>
       <c r="BK64" s="95"/>
@@ -19691,7 +19787,7 @@
       <c r="AW65" s="1"/>
       <c r="AX65" s="1"/>
       <c r="BB65" s="132" t="n">
-        <v>29999.9999999996</v>
+        <v>29999.9999999989</v>
       </c>
       <c r="BC65" s="34" t="n">
         <v>28750.659141066</v>
@@ -19786,10 +19882,10 @@
       <c r="AW67" s="1"/>
       <c r="AX67" s="1"/>
       <c r="BB67" s="34" t="n">
-        <v>-1.05173967313021E-008</v>
+        <v>-3.09591996483505E-009</v>
       </c>
       <c r="BC67" s="34" t="n">
-        <v>3.74711817130446E-010</v>
+        <v>1.13141140900552E-009</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19831,10 +19927,10 @@
       <c r="AW68" s="1"/>
       <c r="AX68" s="1"/>
       <c r="BB68" s="34" t="n">
-        <v>3.74711817130446E-010</v>
+        <v>1.13141140900552E-009</v>
       </c>
       <c r="BC68" s="34" t="n">
-        <v>1.05173967313021E-008</v>
+        <v>3.09591996483505E-009</v>
       </c>
       <c r="BO68" s="100"/>
       <c r="BR68" s="133"/>
@@ -20151,16 +20247,16 @@
         <v>-3.73189238649237E-019</v>
       </c>
       <c r="AM77" s="1" t="n">
-        <v>7.28799829072712E-027</v>
+        <v>7.2879982636969E-027</v>
       </c>
       <c r="AN77" s="1" t="n">
-        <v>0.00609488097330607</v>
+        <v>0.00609488097330606</v>
       </c>
       <c r="AO77" s="1" t="n">
-        <v>-3.73145510659707E-019</v>
+        <v>-3.73145510659706E-019</v>
       </c>
       <c r="AP77" s="1" t="n">
-        <v>7.28799820624129E-027</v>
+        <v>7.28799822359393E-027</v>
       </c>
       <c r="AQ77" s="1" t="n">
         <v>-2.2858482064388E-006</v>
@@ -20176,7 +20272,7 @@
       <c r="AU77" s="1"/>
       <c r="AV77" s="36" t="n">
         <f aca="false" t="array" ref="AV77:AV84">MMULT(AK77:AR84,AT77:AT84)</f>
-        <v>45.7223209577564</v>
+        <v>45.7223209577565</v>
       </c>
       <c r="AW77" s="1" t="s">
         <v>12</v>
@@ -20195,16 +20291,16 @@
         <v>1.9047619047619E-006</v>
       </c>
       <c r="AM78" s="13" t="n">
-        <v>-3.17460317460314E-010</v>
+        <v>-3.1746031746041E-010</v>
       </c>
       <c r="AN78" s="1" t="n">
-        <v>-3.73145510659707E-019</v>
+        <v>-3.73145510659706E-019</v>
       </c>
       <c r="AO78" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AP78" s="1" t="n">
-        <v>-3.1746031746029E-010</v>
+        <v>-3.17460317460339E-010</v>
       </c>
       <c r="AQ78" s="1" t="n">
         <v>1.39989701879148E-022</v>
@@ -20218,7 +20314,7 @@
       </c>
       <c r="AU78" s="1"/>
       <c r="AV78" s="36" t="n">
-        <v>-0.0571428571428592</v>
+        <v>-0.0571428571428578</v>
       </c>
       <c r="AW78" s="1" t="s">
         <v>12</v>
@@ -20231,28 +20327,28 @@
         <v>5</v>
       </c>
       <c r="AK79" s="1" t="n">
-        <v>7.28799825507056E-027</v>
+        <v>7.28799825507051E-027</v>
       </c>
       <c r="AL79" s="13" t="n">
-        <v>-3.17460317460318E-010</v>
+        <v>-3.17460317460317E-010</v>
       </c>
       <c r="AM79" s="13" t="n">
         <v>1.42962962962963E-010</v>
       </c>
       <c r="AN79" s="1" t="n">
-        <v>-7.28799825507424E-027</v>
+        <v>-7.28799825507425E-027</v>
       </c>
       <c r="AO79" s="1" t="n">
-        <v>3.17460317460318E-010</v>
+        <v>3.17460317460317E-010</v>
       </c>
       <c r="AP79" s="1" t="n">
-        <v>-7.13227513227513E-011</v>
+        <v>-7.13227513227515E-011</v>
       </c>
       <c r="AQ79" s="1" t="n">
-        <v>-1.00225636262905E-029</v>
+        <v>-1.00225636262904E-029</v>
       </c>
       <c r="AR79" s="1" t="n">
-        <v>1.00225636262911E-029</v>
+        <v>1.00225636262931E-029</v>
       </c>
       <c r="AS79" s="1"/>
       <c r="AT79" s="1" t="n">
@@ -20260,14 +20356,14 @@
       </c>
       <c r="AU79" s="1"/>
       <c r="AV79" s="36" t="n">
-        <v>-0.00642857142857143</v>
+        <v>-0.00642857142857144</v>
       </c>
       <c r="AW79" s="1" t="s">
         <v>78</v>
       </c>
       <c r="AX79" s="1" t="n">
         <f aca="false">1000*AV79</f>
-        <v>-6.42857142857143</v>
+        <v>-6.42857142857144</v>
       </c>
       <c r="AY79" s="7"/>
       <c r="BK79" s="100"/>
@@ -20277,13 +20373,13 @@
         <v>6</v>
       </c>
       <c r="AK80" s="1" t="n">
-        <v>0.00609488097330607</v>
+        <v>0.00609488097330606</v>
       </c>
       <c r="AL80" s="1" t="n">
-        <v>-3.73145510659707E-019</v>
+        <v>-3.73145510659706E-019</v>
       </c>
       <c r="AM80" s="1" t="n">
-        <v>-7.28799821941333E-027</v>
+        <v>-7.28799824645115E-027</v>
       </c>
       <c r="AN80" s="1" t="n">
         <v>0.00609559521717012</v>
@@ -20292,7 +20388,7 @@
         <v>-3.73189238649237E-019</v>
       </c>
       <c r="AP80" s="1" t="n">
-        <v>-7.28799830390796E-027</v>
+        <v>-7.28799828655552E-027</v>
       </c>
       <c r="AQ80" s="1" t="n">
         <v>-2.28558036498977E-006</v>
@@ -20330,10 +20426,10 @@
         <v>9</v>
       </c>
       <c r="AK81" s="1" t="n">
-        <v>-3.73145510659707E-019</v>
+        <v>-3.73145510659706E-019</v>
       </c>
       <c r="AL81" s="1" t="n">
-        <v>-3.23939099426459E-025</v>
+        <v>9.19987042438306E-024</v>
       </c>
       <c r="AM81" s="1" t="n">
         <v>3.17460317460317E-010</v>
@@ -20383,28 +20479,28 @@
         <v>10</v>
       </c>
       <c r="AK82" s="1" t="n">
-        <v>7.28799825507056E-027</v>
+        <v>7.28799825507051E-027</v>
       </c>
       <c r="AL82" s="1" t="n">
-        <v>-3.17460317460318E-010</v>
+        <v>-3.17460317460317E-010</v>
       </c>
       <c r="AM82" s="1" t="n">
-        <v>-7.13227513227513E-011</v>
+        <v>-7.13227513227515E-011</v>
       </c>
       <c r="AN82" s="1" t="n">
-        <v>-7.28799825507424E-027</v>
+        <v>-7.28799825507425E-027</v>
       </c>
       <c r="AO82" s="13" t="n">
-        <v>3.17460317460318E-010</v>
+        <v>3.17460317460317E-010</v>
       </c>
       <c r="AP82" s="1" t="n">
         <v>1.42962962962963E-010</v>
       </c>
       <c r="AQ82" s="1" t="n">
-        <v>-1.00225636262905E-029</v>
+        <v>-1.00225636262904E-029</v>
       </c>
       <c r="AR82" s="1" t="n">
-        <v>1.00225636262911E-029</v>
+        <v>1.00225636262931E-029</v>
       </c>
       <c r="AS82" s="1"/>
       <c r="AT82" s="1" t="n">
@@ -20412,14 +20508,14 @@
       </c>
       <c r="AU82" s="1"/>
       <c r="AV82" s="36" t="n">
-        <v>0.00642857142857143</v>
+        <v>0.00642857142857144</v>
       </c>
       <c r="AW82" s="1" t="s">
         <v>78</v>
       </c>
       <c r="AX82" s="1" t="n">
         <f aca="false">1000*AV82</f>
-        <v>6.42857142857143</v>
+        <v>6.42857142857144</v>
       </c>
       <c r="AY82" s="7"/>
       <c r="AZ82" s="132"/>
@@ -20474,13 +20570,13 @@
         <v>11</v>
       </c>
       <c r="AK83" s="1" t="n">
-        <v>-2.2858482064388E-006</v>
+        <v>-2.28584820643879E-006</v>
       </c>
       <c r="AL83" s="1" t="n">
         <v>1.39989701879148E-022</v>
       </c>
       <c r="AM83" s="1" t="n">
-        <v>-1.00225636396655E-029</v>
+        <v>-1.00225636295276E-029</v>
       </c>
       <c r="AN83" s="1" t="n">
         <v>-2.28558036498977E-006</v>
@@ -20489,7 +20585,7 @@
         <v>1.3992956649739E-022</v>
       </c>
       <c r="AP83" s="1" t="n">
-        <v>-1.00225636079732E-029</v>
+        <v>-1.00225636144795E-029</v>
       </c>
       <c r="AQ83" s="1" t="n">
         <v>1.42862164884312E-009</v>
@@ -20503,14 +20599,14 @@
       </c>
       <c r="AU83" s="1"/>
       <c r="AV83" s="36" t="n">
-        <v>-0.00952682274011103</v>
+        <v>-0.00952682274011107</v>
       </c>
       <c r="AW83" s="1" t="s">
         <v>78</v>
       </c>
       <c r="AX83" s="1" t="n">
         <f aca="false">1000*AV83</f>
-        <v>-9.52682274011103</v>
+        <v>-9.52682274011107</v>
       </c>
       <c r="AY83" s="7"/>
       <c r="AZ83" s="137"/>
@@ -20569,7 +20665,7 @@
         <v>1.3992956649739E-022</v>
       </c>
       <c r="AM84" s="1" t="n">
-        <v>1.0022563612919E-029</v>
+        <v>1.00225636230582E-029</v>
       </c>
       <c r="AN84" s="1" t="n">
         <v>-2.2858482064388E-006</v>
@@ -20578,7 +20674,7 @@
         <v>1.39989701879148E-022</v>
       </c>
       <c r="AP84" s="1" t="n">
-        <v>1.00225636446045E-029</v>
+        <v>1.00225636380973E-029</v>
       </c>
       <c r="AQ84" s="1" t="n">
         <v>8.57092636871165E-010</v>
@@ -29416,7 +29512,7 @@
       </c>
       <c r="AK79" s="34" t="n">
         <f aca="false" t="array" ref="AK79:AT88">MINVERSE(AK66:AT75)</f>
-        <v>7.16223406501651E-010</v>
+        <v>7.16223406501652E-010</v>
       </c>
       <c r="AL79" s="1" t="n">
         <v>-2.00005067439259E-006</v>
@@ -29425,10 +29521,10 @@
         <v>1.22476057257248E-022</v>
       </c>
       <c r="AN79" s="1" t="n">
-        <v>-3.79244748708235E-030</v>
+        <v>-3.79244747819568E-030</v>
       </c>
       <c r="AO79" s="34" t="n">
-        <v>2.83776593498602E-010</v>
+        <v>2.83776593498603E-010</v>
       </c>
       <c r="AP79" s="1" t="n">
         <v>-1.9999493256092E-006</v>
@@ -29437,13 +29533,13 @@
         <v>1.22453302572332E-022</v>
       </c>
       <c r="AR79" s="1" t="n">
-        <v>-3.79244748713591E-030</v>
+        <v>-3.79244748666768E-030</v>
       </c>
       <c r="AS79" s="1" t="n">
-        <v>3.91907299646395E-010</v>
+        <v>3.91907299646397E-010</v>
       </c>
       <c r="AT79" s="1" t="n">
-        <v>6.08092700354147E-010</v>
+        <v>6.08092700354148E-010</v>
       </c>
       <c r="AU79" s="1"/>
       <c r="AV79" s="13" t="n">
@@ -29472,31 +29568,31 @@
         <v>-2.00005067439259E-006</v>
       </c>
       <c r="AL80" s="1" t="n">
-        <v>0.0140955952290525</v>
+        <v>0.0140955952290526</v>
       </c>
       <c r="AM80" s="13" t="n">
         <v>-8.63047960974973E-019</v>
       </c>
       <c r="AN80" s="13" t="n">
-        <v>7.2888870653519E-027</v>
+        <v>7.28888700270918E-027</v>
       </c>
       <c r="AO80" s="34" t="n">
         <v>-1.9999493256092E-006</v>
       </c>
       <c r="AP80" s="1" t="n">
-        <v>0.0140948809614362</v>
+        <v>0.0140948809614363</v>
       </c>
       <c r="AQ80" s="1" t="n">
-        <v>-8.63004227652625E-019</v>
+        <v>-8.63004227652626E-019</v>
       </c>
       <c r="AR80" s="1" t="n">
-        <v>7.28888706573259E-027</v>
+        <v>7.28888706242603E-027</v>
       </c>
       <c r="AS80" s="1" t="n">
         <v>-4.28582287369841E-006</v>
       </c>
       <c r="AT80" s="1" t="n">
-        <v>-4.28560569773399E-006</v>
+        <v>-4.285605697734E-006</v>
       </c>
       <c r="AU80" s="1"/>
       <c r="AV80" s="34" t="n">
@@ -29529,28 +29625,28 @@
         <v>1.22476057257248E-022</v>
       </c>
       <c r="AL81" s="1" t="n">
-        <v>-8.63047960974972E-019</v>
+        <v>-8.63047960974973E-019</v>
       </c>
       <c r="AM81" s="13" t="n">
         <v>1.9047619047619E-006</v>
       </c>
       <c r="AN81" s="13" t="n">
-        <v>-3.17460317460314E-010</v>
+        <v>-3.1746031746041E-010</v>
       </c>
       <c r="AO81" s="34" t="n">
         <v>1.22453302572332E-022</v>
       </c>
       <c r="AP81" s="1" t="n">
-        <v>-8.63004227652625E-019</v>
+        <v>-8.63004227652626E-019</v>
       </c>
       <c r="AQ81" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AR81" s="1" t="n">
-        <v>-3.1746031746029E-010</v>
+        <v>-3.17460317460339E-010</v>
       </c>
       <c r="AS81" s="1" t="n">
-        <v>2.62448694122674E-022</v>
+        <v>2.62448694122675E-022</v>
       </c>
       <c r="AT81" s="1" t="n">
         <v>2.62399934083568E-022</v>
@@ -29583,34 +29679,34 @@
         <v>6</v>
       </c>
       <c r="AK82" s="34" t="n">
-        <v>-3.79244748601887E-030</v>
+        <v>-3.7924474860163E-030</v>
       </c>
       <c r="AL82" s="1" t="n">
-        <v>7.28888705785753E-027</v>
+        <v>7.28888705783948E-027</v>
       </c>
       <c r="AM82" s="1" t="n">
-        <v>-3.17460317460318E-010</v>
+        <v>-3.17460317460317E-010</v>
       </c>
       <c r="AN82" s="1" t="n">
         <v>1.42962962962963E-010</v>
       </c>
       <c r="AO82" s="34" t="n">
-        <v>3.7924474860221E-030</v>
+        <v>3.79244748602375E-030</v>
       </c>
       <c r="AP82" s="1" t="n">
-        <v>-7.28888705788977E-027</v>
+        <v>-7.28888705790779E-027</v>
       </c>
       <c r="AQ82" s="1" t="n">
-        <v>3.17460317460318E-010</v>
+        <v>3.17460317460317E-010</v>
       </c>
       <c r="AR82" s="1" t="n">
-        <v>-7.13227513227513E-011</v>
+        <v>-7.13227513227515E-011</v>
       </c>
       <c r="AS82" s="1" t="n">
-        <v>-8.12667318432615E-030</v>
+        <v>-8.12667318432064E-030</v>
       </c>
       <c r="AT82" s="1" t="n">
-        <v>8.12667318433881E-030</v>
+        <v>8.12667318434713E-030</v>
       </c>
       <c r="AU82" s="1"/>
       <c r="AV82" s="1" t="n">
@@ -29678,7 +29774,7 @@
         <v>9</v>
       </c>
       <c r="AK83" s="34" t="n">
-        <v>2.83776593498602E-010</v>
+        <v>2.83776593498603E-010</v>
       </c>
       <c r="AL83" s="1" t="n">
         <v>-1.9999493256092E-006</v>
@@ -29687,10 +29783,10 @@
         <v>1.22453302572332E-022</v>
       </c>
       <c r="AN83" s="1" t="n">
-        <v>3.79244748495997E-030</v>
+        <v>3.79244749384954E-030</v>
       </c>
       <c r="AO83" s="34" t="n">
-        <v>7.16223406501651E-010</v>
+        <v>7.16223406501652E-010</v>
       </c>
       <c r="AP83" s="1" t="n">
         <v>-2.00005067439259E-006</v>
@@ -29699,13 +29795,13 @@
         <v>1.22476057257248E-022</v>
       </c>
       <c r="AR83" s="1" t="n">
-        <v>3.7924474849058E-030</v>
+        <v>3.79244748537531E-030</v>
       </c>
       <c r="AS83" s="1" t="n">
-        <v>6.08092700354148E-010</v>
+        <v>6.08092700354149E-010</v>
       </c>
       <c r="AT83" s="1" t="n">
-        <v>3.91907299646395E-010</v>
+        <v>3.91907299646396E-010</v>
       </c>
       <c r="AU83" s="1"/>
       <c r="AV83" s="13" t="n">
@@ -29774,31 +29870,31 @@
         <v>-1.9999493256092E-006</v>
       </c>
       <c r="AL84" s="1" t="n">
-        <v>0.0140948809614362</v>
+        <v>0.0140948809614363</v>
       </c>
       <c r="AM84" s="1" t="n">
-        <v>-8.63004227652625E-019</v>
+        <v>-8.63004227652626E-019</v>
       </c>
       <c r="AN84" s="1" t="n">
-        <v>-7.28888705039484E-027</v>
+        <v>-7.28888711304516E-027</v>
       </c>
       <c r="AO84" s="34" t="n">
         <v>-2.00005067439259E-006</v>
       </c>
       <c r="AP84" s="1" t="n">
-        <v>0.0140955952290525</v>
+        <v>0.0140955952290526</v>
       </c>
       <c r="AQ84" s="13" t="n">
-        <v>-8.63047960974972E-019</v>
+        <v>-8.63047960974973E-019</v>
       </c>
       <c r="AR84" s="1" t="n">
-        <v>-7.28888705001304E-027</v>
+        <v>-7.28888705332201E-027</v>
       </c>
       <c r="AS84" s="1" t="n">
         <v>-4.285605697734E-006</v>
       </c>
       <c r="AT84" s="1" t="n">
-        <v>-4.2858228736984E-006</v>
+        <v>-4.28582287369841E-006</v>
       </c>
       <c r="AU84" s="1"/>
       <c r="AV84" s="1" t="n">
@@ -29842,10 +29938,10 @@
         <v>1.22453302572332E-022</v>
       </c>
       <c r="AL85" s="1" t="n">
-        <v>-8.63004227652625E-019</v>
+        <v>-8.63004227652626E-019</v>
       </c>
       <c r="AM85" s="1" t="n">
-        <v>-6.47878198845767E-025</v>
+        <v>8.68156786529417E-024</v>
       </c>
       <c r="AN85" s="1" t="n">
         <v>3.17460317460317E-010</v>
@@ -29854,7 +29950,7 @@
         <v>1.22476057257248E-022</v>
       </c>
       <c r="AP85" s="1" t="n">
-        <v>-8.63047960974972E-019</v>
+        <v>-8.63047960974973E-019</v>
       </c>
       <c r="AQ85" s="13" t="n">
         <v>1.9047619047619E-006</v>
@@ -29863,10 +29959,10 @@
         <v>3.17460317460317E-010</v>
       </c>
       <c r="AS85" s="1" t="n">
-        <v>2.62399934083568E-022</v>
+        <v>2.62399934083569E-022</v>
       </c>
       <c r="AT85" s="1" t="n">
-        <v>2.62448694122674E-022</v>
+        <v>2.62448694122675E-022</v>
       </c>
       <c r="AU85" s="1"/>
       <c r="AV85" s="1" t="n">
@@ -29900,34 +29996,34 @@
         <v>12</v>
       </c>
       <c r="AK86" s="34" t="n">
-        <v>-3.79244748601887E-030</v>
+        <v>-3.7924474860163E-030</v>
       </c>
       <c r="AL86" s="1" t="n">
-        <v>7.28888705785753E-027</v>
+        <v>7.28888705783948E-027</v>
       </c>
       <c r="AM86" s="1" t="n">
-        <v>-3.17460317460318E-010</v>
+        <v>-3.17460317460317E-010</v>
       </c>
       <c r="AN86" s="1" t="n">
-        <v>-7.13227513227513E-011</v>
+        <v>-7.13227513227515E-011</v>
       </c>
       <c r="AO86" s="34" t="n">
-        <v>3.7924474860221E-030</v>
+        <v>3.79244748602375E-030</v>
       </c>
       <c r="AP86" s="1" t="n">
-        <v>-7.28888705788977E-027</v>
+        <v>-7.28888705790779E-027</v>
       </c>
       <c r="AQ86" s="1" t="n">
-        <v>3.17460317460318E-010</v>
+        <v>3.17460317460317E-010</v>
       </c>
       <c r="AR86" s="1" t="n">
         <v>1.42962962962963E-010</v>
       </c>
       <c r="AS86" s="1" t="n">
-        <v>-8.12667318432615E-030</v>
+        <v>-8.12667318432064E-030</v>
       </c>
       <c r="AT86" s="1" t="n">
-        <v>8.12667318433881E-030</v>
+        <v>8.12667318434713E-030</v>
       </c>
       <c r="AU86" s="1"/>
       <c r="AV86" s="1" t="n">
@@ -29962,25 +30058,25 @@
         <v>2.62448694122675E-022</v>
       </c>
       <c r="AN87" s="34" t="n">
-        <v>-8.12667318660437E-030</v>
+        <v>-8.12667316755631E-030</v>
       </c>
       <c r="AO87" s="34" t="n">
-        <v>6.08092700354148E-010</v>
+        <v>6.08092700354149E-010</v>
       </c>
       <c r="AP87" s="34" t="n">
         <v>-4.285605697734E-006</v>
       </c>
       <c r="AQ87" s="34" t="n">
-        <v>2.62399934083568E-022</v>
+        <v>2.62399934083569E-022</v>
       </c>
       <c r="AR87" s="34" t="n">
-        <v>-8.12667318672046E-030</v>
+        <v>-8.12667318571436E-030</v>
       </c>
       <c r="AS87" s="34" t="n">
         <v>1.98265849924228E-009</v>
       </c>
       <c r="AT87" s="34" t="n">
-        <v>1.30305578647317E-009</v>
+        <v>1.30305578647318E-009</v>
       </c>
       <c r="AU87" s="1"/>
       <c r="AV87" s="1" t="n">
@@ -30006,13 +30102,13 @@
         <v>6.08092700354148E-010</v>
       </c>
       <c r="AL88" s="34" t="n">
-        <v>-4.28560569773399E-006</v>
+        <v>-4.285605697734E-006</v>
       </c>
       <c r="AM88" s="34" t="n">
-        <v>2.62399934083568E-022</v>
+        <v>2.62399934083569E-022</v>
       </c>
       <c r="AN88" s="34" t="n">
-        <v>8.12667318205708E-030</v>
+        <v>8.12667320110615E-030</v>
       </c>
       <c r="AO88" s="34" t="n">
         <v>3.91907299646396E-010</v>
@@ -30021,16 +30117,16 @@
         <v>-4.28582287369841E-006</v>
       </c>
       <c r="AQ88" s="34" t="n">
-        <v>2.62448694122674E-022</v>
+        <v>2.62448694122675E-022</v>
       </c>
       <c r="AR88" s="34" t="n">
-        <v>8.126673181941E-030</v>
+        <v>8.12667318294709E-030</v>
       </c>
       <c r="AS88" s="34" t="n">
-        <v>1.30305578647317E-009</v>
+        <v>1.30305578647318E-009</v>
       </c>
       <c r="AT88" s="34" t="n">
-        <v>1.98265849924227E-009</v>
+        <v>1.98265849924228E-009</v>
       </c>
       <c r="AV88" s="34" t="n">
         <v>-6666666.66666667</v>
@@ -32335,72 +32431,72 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L14" s="0" t="s">
+      <c r="L14" s="157" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L15" s="157" t="n">
+      <c r="L15" s="158" t="n">
         <v>10000000</v>
       </c>
-      <c r="M15" s="0" t="n">
+      <c r="M15" s="157" t="n">
         <f aca="false">6*N31*O31/M31^3*L15</f>
         <v>3750</v>
       </c>
-      <c r="N15" s="0" t="n">
+      <c r="N15" s="157" t="n">
         <f aca="false">O31*(2*N31-O31)/M31^2*L15</f>
         <v>2500000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M30" s="0" t="s">
+      <c r="M30" s="157" t="s">
         <v>105</v>
       </c>
-      <c r="N30" s="0" t="s">
+      <c r="N30" s="157" t="s">
         <v>106</v>
       </c>
-      <c r="O30" s="0" t="s">
+      <c r="O30" s="157" t="s">
         <v>75</v>
       </c>
-      <c r="P30" s="0" t="s">
+      <c r="P30" s="157" t="s">
         <v>107</v>
       </c>
-      <c r="Q30" s="0" t="s">
+      <c r="Q30" s="157" t="s">
         <v>108</v>
       </c>
-      <c r="R30" s="0" t="s">
+      <c r="R30" s="157" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M31" s="0" t="n">
+      <c r="M31" s="157" t="n">
         <v>4000</v>
       </c>
-      <c r="N31" s="0" t="n">
+      <c r="N31" s="157" t="n">
         <v>2000</v>
       </c>
-      <c r="O31" s="0" t="n">
+      <c r="O31" s="157" t="n">
         <f aca="false">M31-N31</f>
         <v>2000</v>
       </c>
-      <c r="P31" s="0" t="n">
+      <c r="P31" s="157" t="n">
         <v>2500</v>
       </c>
-      <c r="Q31" s="0" t="n">
+      <c r="Q31" s="157" t="n">
         <v>1250</v>
       </c>
-      <c r="R31" s="0" t="n">
+      <c r="R31" s="157" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M33" s="0" t="n">
+      <c r="M33" s="157" t="n">
         <f aca="false">P31/M31^3*((2*N31+M31)*O31^2+1/4*(N31-O31)*P31^2)*R31</f>
         <v>12500</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M34" s="0" t="n">
+      <c r="M34" s="157" t="n">
         <f aca="false">P31/M31^2*(N31*O31^2+1/12*(N31-2*O31)*P31^2)*R31</f>
         <v>10872395.8333333</v>
       </c>
@@ -32426,44 +32522,44 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9.57"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="9.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="12.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="9.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="10.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="9.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="10.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="12.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="9.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="26" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="26" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="35" min="30" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="11.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="10.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="9.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="41" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="9.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="45" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="45" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="49" min="49" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="50" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="50" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="1" width="12.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="56" min="56" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="57" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="57" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="63" style="1" width="9.14"/>
   </cols>
   <sheetData>
@@ -32963,13 +33059,13 @@
       <c r="N12" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="O12" s="158" t="n">
+      <c r="O12" s="159" t="n">
         <v>0</v>
       </c>
       <c r="P12" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="Q12" s="158" t="n">
+      <c r="Q12" s="159" t="n">
         <v>45</v>
       </c>
       <c r="R12" s="7"/>
@@ -33616,7 +33712,7 @@
       <c r="Y22" s="7"/>
       <c r="Z22" s="7" t="n">
         <f aca="false" t="array" ref="Z22:Z27">MMULT(M22:R27,X22:X27)-V22:V27</f>
-        <v>28284.2712474619</v>
+        <v>28284.271247462</v>
       </c>
       <c r="AJ22" s="7"/>
       <c r="AK22" s="7"/>
@@ -33704,7 +33800,7 @@
       </c>
       <c r="Y23" s="37"/>
       <c r="Z23" s="20" t="n">
-        <v>28284.2712474619</v>
+        <v>28284.271247462</v>
       </c>
       <c r="AJ23" s="7"/>
       <c r="AK23" s="7"/>
@@ -34003,7 +34099,7 @@
       </c>
       <c r="X27" s="40" t="n">
         <f aca="false">U61</f>
-        <v>-6.22042818614529E-019</v>
+        <v>-6.2204281861453E-019</v>
       </c>
       <c r="Y27" s="37"/>
       <c r="Z27" s="20" t="n">
@@ -34236,7 +34332,7 @@
         <v>-464038.825153672</v>
       </c>
       <c r="P31" s="12" t="n">
-        <v>-371231.060122938</v>
+        <v>-371231.060122937</v>
       </c>
       <c r="Q31" s="12" t="n">
         <v>232.019412576832</v>
@@ -34309,7 +34405,7 @@
         <v>464038.825153672</v>
       </c>
       <c r="P32" s="12" t="n">
-        <v>-371231.060122938</v>
+        <v>-371231.060122937</v>
       </c>
       <c r="Q32" s="12" t="n">
         <v>-232.019412576832</v>
@@ -34419,7 +34515,7 @@
         <v>464038.825153672</v>
       </c>
       <c r="P34" s="12" t="n">
-        <v>371231.060122938</v>
+        <v>371231.060122937</v>
       </c>
       <c r="Q34" s="12" t="n">
         <v>-232.019412576832</v>
@@ -34428,7 +34524,7 @@
         <v>464038.825153672</v>
       </c>
       <c r="V34" s="13" t="n">
-        <v>-20000</v>
+        <v>-20000.0000000001</v>
       </c>
       <c r="AB34" s="20"/>
       <c r="AD34" s="36"/>
@@ -34470,7 +34566,7 @@
         <v>-464038.825153672</v>
       </c>
       <c r="P35" s="12" t="n">
-        <v>371231.060122938</v>
+        <v>371231.060122937</v>
       </c>
       <c r="Q35" s="12" t="n">
         <v>232.019412576832</v>
@@ -34710,7 +34806,7 @@
         <v>-464038.825153672</v>
       </c>
       <c r="P39" s="12" t="n">
-        <v>-371231.060122938</v>
+        <v>-371231.060122937</v>
       </c>
       <c r="Q39" s="12" t="n">
         <v>232.019412576832</v>
@@ -34723,7 +34819,7 @@
       </c>
       <c r="V39" s="69" t="n">
         <f aca="false" t="array" ref="V39:V44">MMULT(M39:R44,T39:T44)-V31:V36</f>
-        <v>28284.2712474619</v>
+        <v>28284.271247462</v>
       </c>
       <c r="Y39" s="1" t="n">
         <v>262664.0625</v>
@@ -34774,7 +34870,7 @@
         <v>464038.825153672</v>
       </c>
       <c r="P40" s="12" t="n">
-        <v>-371231.060122938</v>
+        <v>-371231.060122937</v>
       </c>
       <c r="Q40" s="12" t="n">
         <v>-232.019412576832</v>
@@ -34786,7 +34882,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="69" t="n">
-        <v>28284.2712474619</v>
+        <v>28284.271247462</v>
       </c>
       <c r="Y40" s="1" t="n">
         <v>262335.9375</v>
@@ -34871,10 +34967,10 @@
         <v>4</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>-371231.060122938</v>
+        <v>-371231.060122937</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>-371231.060122938</v>
+        <v>-371231.060122937</v>
       </c>
       <c r="O42" s="12" t="n">
         <v>0</v>
@@ -34890,7 +34986,7 @@
       </c>
       <c r="T42" s="36" t="n">
         <f aca="false">U60</f>
-        <v>-0.0380952380952381</v>
+        <v>-0.0380952380952382</v>
       </c>
       <c r="V42" s="69" t="n">
         <v>0</v>
@@ -34937,7 +35033,7 @@
         <v>464038.825153672</v>
       </c>
       <c r="AB43" s="1" t="n">
-        <v>371231.060122938</v>
+        <v>371231.060122937</v>
       </c>
       <c r="AC43" s="1" t="n">
         <v>-232.019412576832</v>
@@ -34973,7 +35069,7 @@
       </c>
       <c r="T44" s="36" t="n">
         <f aca="false">U61</f>
-        <v>-6.22042818614529E-019</v>
+        <v>-6.2204281861453E-019</v>
       </c>
       <c r="V44" s="69" t="n">
         <v>1.63286239886314E-009</v>
@@ -34988,7 +35084,7 @@
         <v>-464038.825153672</v>
       </c>
       <c r="AB44" s="1" t="n">
-        <v>371231.060122938</v>
+        <v>371231.060122937</v>
       </c>
       <c r="AC44" s="1" t="n">
         <v>232.019412576832</v>
@@ -35197,7 +35293,7 @@
         <v>r14</v>
       </c>
       <c r="U49" s="51" t="n">
-        <v>-20000</v>
+        <v>-20000.0000000001</v>
       </c>
       <c r="AH49" s="2"/>
       <c r="AI49" s="2"/>
@@ -35494,7 +35590,6 @@
       <c r="O58" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="P58" s="159"/>
       <c r="R58" s="7" t="s">
         <v>37</v>
       </c>
@@ -35599,10 +35694,10 @@
       </c>
       <c r="P60" s="13"/>
       <c r="S60" s="1" t="n">
-        <v>-20000</v>
+        <v>-20000.0000000001</v>
       </c>
       <c r="U60" s="36" t="n">
-        <v>-0.0380952380952381</v>
+        <v>-0.0380952380952382</v>
       </c>
       <c r="V60" s="1" t="s">
         <v>12</v>
@@ -35643,7 +35738,7 @@
         <v>0</v>
       </c>
       <c r="U61" s="36" t="n">
-        <v>-6.22042818614529E-019</v>
+        <v>-6.2204281861453E-019</v>
       </c>
       <c r="V61" s="1" t="s">
         <v>78</v>
@@ -35679,7 +35774,6 @@
       <c r="CE61" s="52"/>
     </row>
     <row r="62" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L62" s="159"/>
       <c r="U62" s="36"/>
       <c r="AB62" s="20"/>
       <c r="AD62" s="20"/>
@@ -35745,7 +35839,7 @@
       </c>
       <c r="X66" s="36" t="n">
         <f aca="false">U60</f>
-        <v>-0.0380952380952381</v>
+        <v>-0.0380952380952382</v>
       </c>
       <c r="Y66" s="1" t="n">
         <f aca="false" t="array" ref="Y66:Y67">MMULT(W16:X17,X66:X67)</f>
@@ -36058,7 +36152,7 @@
         <v>0</v>
       </c>
       <c r="T80" s="1" t="n">
-        <v>-0.0380952380952381</v>
+        <v>-0.0380952380952383</v>
       </c>
       <c r="V80" s="13" t="n">
         <f aca="false">I31</f>
@@ -36139,7 +36233,7 @@
         <v>1750000000</v>
       </c>
       <c r="T82" s="1" t="n">
-        <v>-6.22042818614529E-019</v>
+        <v>-6.2204281861453E-019</v>
       </c>
       <c r="V82" s="13" t="n">
         <f aca="false">I33</f>
@@ -37846,18 +37940,18 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9.57"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="9.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="12.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="9.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="10.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="9.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="12.42"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="9.14"/>
@@ -37866,24 +37960,24 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="10.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="12.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="9.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="26" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="26" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="35" min="30" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="11.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="10.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="9.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="41" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="9.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="45" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="45" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="49" min="49" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="50" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="50" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="1" width="12.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="56" min="56" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="57" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="57" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="63" style="1" width="9.14"/>
   </cols>
   <sheetData>
@@ -38383,13 +38477,13 @@
       <c r="N12" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="O12" s="158" t="n">
+      <c r="O12" s="159" t="n">
         <v>0</v>
       </c>
       <c r="P12" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="Q12" s="158" t="n">
+      <c r="Q12" s="159" t="n">
         <v>45</v>
       </c>
       <c r="R12" s="7"/>
@@ -39302,7 +39396,7 @@
       </c>
       <c r="X25" s="36" t="n">
         <f aca="false">U66</f>
-        <v>129.299525702692</v>
+        <v>129.299525702693</v>
       </c>
       <c r="Y25" s="37"/>
       <c r="Z25" s="20"/>
@@ -39362,7 +39456,7 @@
       </c>
       <c r="X26" s="36" t="n">
         <f aca="false">U67</f>
-        <v>-129.299525702692</v>
+        <v>-129.299525702693</v>
       </c>
       <c r="Y26" s="34"/>
       <c r="Z26" s="34"/>
@@ -39425,7 +39519,7 @@
       </c>
       <c r="X27" s="40" t="n">
         <f aca="false">U60</f>
-        <v>-0.0609523809523856</v>
+        <v>-0.0609523809523862</v>
       </c>
       <c r="Y27" s="37"/>
       <c r="Z27" s="20"/>
@@ -39800,7 +39894,7 @@
         <v>0</v>
       </c>
       <c r="Q33" s="12" t="n">
-        <v>-656250</v>
+        <v>-656250.000000001</v>
       </c>
       <c r="R33" s="12" t="n">
         <v>875000000</v>
@@ -39899,7 +39993,7 @@
         <v>-464038.825153672</v>
       </c>
       <c r="V35" s="13" t="n">
-        <v>-20000</v>
+        <v>-20000.0000000001</v>
       </c>
       <c r="AB35" s="20"/>
       <c r="AD35" s="36"/>
@@ -39961,7 +40055,7 @@
         <v>0</v>
       </c>
       <c r="Q36" s="12" t="n">
-        <v>-656250</v>
+        <v>-656250.000000001</v>
       </c>
       <c r="R36" s="12" t="n">
         <v>1750000000</v>
@@ -40115,7 +40209,7 @@
       </c>
       <c r="V39" s="69" t="n">
         <f aca="false" t="array" ref="V39:V44">MMULT(M39:R44,T39:T44)-V31:V36</f>
-        <v>-28284.2712474619</v>
+        <v>-28284.271247462</v>
       </c>
       <c r="AD39" s="20"/>
     </row>
@@ -40169,7 +40263,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="69" t="n">
-        <v>28284.2712474619</v>
+        <v>28284.271247462</v>
       </c>
       <c r="AC40" s="7"/>
       <c r="AD40" s="20"/>
@@ -40217,7 +40311,7 @@
         <v>0</v>
       </c>
       <c r="Q41" s="12" t="n">
-        <v>-656250</v>
+        <v>-656250.000000001</v>
       </c>
       <c r="R41" s="12" t="n">
         <v>875000000</v>
@@ -40226,7 +40320,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="69" t="n">
-        <v>80000000.000004</v>
+        <v>80000000.0000045</v>
       </c>
       <c r="AD41" s="20"/>
     </row>
@@ -40244,7 +40338,7 @@
         <v>0</v>
       </c>
       <c r="P42" s="12" t="n">
-        <v>525000</v>
+        <v>525000.000000001</v>
       </c>
       <c r="Q42" s="12" t="n">
         <v>0</v>
@@ -40272,7 +40366,7 @@
         <v>-232.019412576832</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>-656250</v>
+        <v>-656250.000000001</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>0</v>
@@ -40281,11 +40375,11 @@
         <v>328.124999999995</v>
       </c>
       <c r="R43" s="12" t="n">
-        <v>-656250</v>
+        <v>-656250.000000001</v>
       </c>
       <c r="T43" s="36" t="n">
         <f aca="false">U59</f>
-        <v>-182.857142857155</v>
+        <v>-182.857142857157</v>
       </c>
       <c r="V43" s="69" t="n">
         <v>0</v>
@@ -40311,14 +40405,14 @@
         <v>0</v>
       </c>
       <c r="Q44" s="12" t="n">
-        <v>-656250</v>
+        <v>-656250.000000001</v>
       </c>
       <c r="R44" s="12" t="n">
         <v>1750000000</v>
       </c>
       <c r="T44" s="36" t="n">
         <f aca="false">U60</f>
-        <v>-0.0609523809523856</v>
+        <v>-0.0609523809523862</v>
       </c>
       <c r="V44" s="69" t="n">
         <v>0</v>
@@ -40443,7 +40537,7 @@
         <v>328.124999999995</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>-656250</v>
+        <v>-656250.000000001</v>
       </c>
       <c r="O48" s="13"/>
       <c r="P48" s="13"/>
@@ -40455,7 +40549,7 @@
       </c>
       <c r="U48" s="50" t="n">
         <f aca="false" t="array" ref="U48:U49">V35:V36</f>
-        <v>-20000</v>
+        <v>-20000.0000000001</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40483,7 +40577,7 @@
         <v>5</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>-656250</v>
+        <v>-656250.000000001</v>
       </c>
       <c r="N49" s="13" t="n">
         <v>1750000000</v>
@@ -40821,15 +40915,15 @@
         <v>0.012190476190477</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>4.57142857142888E-006</v>
+        <v>4.57142857142889E-006</v>
       </c>
       <c r="S59" s="13" t="n">
         <f aca="false" t="array" ref="S59:S60">U48:U49</f>
-        <v>-20000</v>
+        <v>-20000.0000000001</v>
       </c>
       <c r="U59" s="36" t="n">
         <f aca="false" t="array" ref="U59:U60">MMULT(M59:N60,S59:S60)</f>
-        <v>-182.857142857155</v>
+        <v>-182.857142857157</v>
       </c>
       <c r="V59" s="1" t="s">
         <v>12</v>
@@ -40860,24 +40954,24 @@
         <v>6</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>4.57142857142888E-006</v>
+        <v>4.57142857142889E-006</v>
       </c>
       <c r="N60" s="13" t="n">
-        <v>2.2857142857144E-009</v>
+        <v>2.28571428571441E-009</v>
       </c>
       <c r="P60" s="13"/>
       <c r="S60" s="1" t="n">
         <v>13333333.3333333</v>
       </c>
       <c r="U60" s="36" t="n">
-        <v>-0.0609523809523856</v>
+        <v>-0.0609523809523862</v>
       </c>
       <c r="V60" s="1" t="s">
         <v>78</v>
       </c>
       <c r="W60" s="1" t="n">
         <f aca="false">1000*U60</f>
-        <v>-60.9523809523856</v>
+        <v>-60.9523809523862</v>
       </c>
       <c r="X60" s="1" t="s">
         <v>79</v>
@@ -40985,7 +41079,7 @@
       </c>
       <c r="U66" s="1" t="n">
         <f aca="false">-SIN(RADIANS(Q12))*U59</f>
-        <v>129.299525702692</v>
+        <v>129.299525702693</v>
       </c>
       <c r="V66" s="1" t="s">
         <v>12</v>
@@ -40995,7 +41089,7 @@
       </c>
       <c r="X66" s="1" t="n">
         <f aca="false" t="array" ref="X66:X67">MMULT(W16:X17,W66:W67)</f>
-        <v>129.299525702692</v>
+        <v>129.299525702693</v>
       </c>
       <c r="AB66" s="7"/>
       <c r="AD66" s="7"/>
@@ -41008,17 +41102,17 @@
       </c>
       <c r="U67" s="1" t="n">
         <f aca="false">COS(RADIANS(Q12))*U59</f>
-        <v>-129.299525702692</v>
+        <v>-129.299525702693</v>
       </c>
       <c r="V67" s="1" t="s">
         <v>12</v>
       </c>
       <c r="W67" s="36" t="n">
         <f aca="false">U59</f>
-        <v>-182.857142857155</v>
+        <v>-182.857142857157</v>
       </c>
       <c r="X67" s="1" t="n">
-        <v>-129.299525702692</v>
+        <v>-129.299525702693</v>
       </c>
       <c r="BR67" s="54"/>
     </row>
@@ -41345,7 +41439,7 @@
         <v>-656250</v>
       </c>
       <c r="T81" s="1" t="n">
-        <v>-182.857142857155</v>
+        <v>-182.857142857157</v>
       </c>
       <c r="V81" s="13" t="n">
         <f aca="false">I32</f>
@@ -41386,7 +41480,7 @@
         <v>1750000000</v>
       </c>
       <c r="T82" s="1" t="n">
-        <v>-0.0609523809523856</v>
+        <v>-0.0609523809523862</v>
       </c>
       <c r="V82" s="13" t="n">
         <f aca="false">I33</f>
@@ -43093,39 +43187,39 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9.57"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="9.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="9.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="21" min="20" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="22" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="22" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="9.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="26" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="26" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="35" min="30" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="11.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="10.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="9.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="41" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="9.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="45" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="45" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="49" min="49" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="50" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="50" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="1" width="12.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="56" min="56" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="57" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="57" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="101" min="63" style="1" width="9.14"/>
   </cols>
   <sheetData>
@@ -47043,7 +47137,7 @@
       </c>
       <c r="BC44" s="37"/>
       <c r="BD44" s="62" t="n">
-        <v>8.74631353182469E-013</v>
+        <v>8.74631353182468E-013</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47134,7 +47228,7 @@
       </c>
       <c r="BB45" s="36" t="n">
         <f aca="false">AT116</f>
-        <v>-0.00653690088492458</v>
+        <v>-0.00653690088492456</v>
       </c>
       <c r="BC45" s="37"/>
       <c r="BD45" s="62" t="n">
@@ -47518,7 +47612,7 @@
       </c>
       <c r="BB48" s="40" t="n">
         <f aca="false">AT118</f>
-        <v>-0.00219184652470182</v>
+        <v>-0.00219184652470184</v>
       </c>
       <c r="BC48" s="37"/>
       <c r="BD48" s="62" t="n">
@@ -47788,7 +47882,7 @@
       </c>
       <c r="BC50" s="41"/>
       <c r="BD50" s="69" t="n">
-        <v>28474.4115483278</v>
+        <v>28474.41154833</v>
       </c>
       <c r="BK50" s="2"/>
       <c r="CW50" s="2"/>
@@ -47896,7 +47990,7 @@
       </c>
       <c r="BB51" s="36" t="n">
         <f aca="false">AT119</f>
-        <v>0.00239572823183017</v>
+        <v>0.00239572823183016</v>
       </c>
       <c r="BC51" s="37"/>
       <c r="BD51" s="62" t="n">
@@ -47978,7 +48072,7 @@
       </c>
       <c r="BB52" s="36" t="n">
         <f aca="false">AZ120</f>
-        <v>-3.32105685335849E-018</v>
+        <v>-3.32105685335874E-018</v>
       </c>
       <c r="BC52" s="41"/>
       <c r="BD52" s="69" t="n">
@@ -48063,11 +48157,11 @@
       </c>
       <c r="BB53" s="36" t="n">
         <f aca="false">AZ121</f>
-        <v>-0.0542369743777673</v>
+        <v>-0.0542369743777714</v>
       </c>
       <c r="BC53" s="41"/>
       <c r="BD53" s="69" t="n">
-        <v>1.16415321826935E-009</v>
+        <v>-9.78616299107671E-010</v>
       </c>
       <c r="BE53" s="17"/>
       <c r="BK53" s="42"/>
@@ -48176,7 +48270,7 @@
       </c>
       <c r="BB54" s="44" t="n">
         <f aca="false">AT121</f>
-        <v>0.00282759115538728</v>
+        <v>0.00282759115538729</v>
       </c>
       <c r="BC54" s="41"/>
       <c r="BD54" s="69" t="n">
@@ -50084,7 +50178,7 @@
         <v>-525000</v>
       </c>
       <c r="AO76" s="12" t="n">
-        <v>-2.00918615485109E-014</v>
+        <v>-2.00918615485432E-014</v>
       </c>
       <c r="AP76" s="12" t="n">
         <v>4.01837230970225E-011</v>
@@ -50247,7 +50341,7 @@
         <v>525777.777777778</v>
       </c>
       <c r="AO79" s="39" t="n">
-        <v>6.77170148486868E-014</v>
+        <v>6.7717014848732E-014</v>
       </c>
       <c r="AP79" s="39" t="n">
         <v>2333333.33333333</v>
@@ -50321,7 +50415,7 @@
         <v>-2333333.33333333</v>
       </c>
       <c r="AU80" s="24" t="n">
-        <v>-1.42875459900525E-010</v>
+        <v>-1.42875459900524E-010</v>
       </c>
       <c r="AV80" s="24" t="n">
         <v>4666666666.66667</v>
@@ -50413,7 +50507,7 @@
         <v>-525000</v>
       </c>
       <c r="AU82" s="31" t="n">
-        <v>-2.00918615485109E-014</v>
+        <v>-2.00918615485432E-014</v>
       </c>
       <c r="AV82" s="31" t="n">
         <v>4.01837230970225E-011</v>
@@ -50585,7 +50679,7 @@
         <v>525777.777777778</v>
       </c>
       <c r="AU85" s="43" t="n">
-        <v>6.77170148486868E-014</v>
+        <v>6.7717014848732E-014</v>
       </c>
       <c r="AV85" s="43" t="n">
         <v>-2333333.33333333</v>
@@ -50622,7 +50716,7 @@
         <v>2333333.33333333</v>
       </c>
       <c r="AO86" s="16" t="n">
-        <v>1.42875459900525E-010</v>
+        <v>1.42875459900524E-010</v>
       </c>
       <c r="AP86" s="24" t="n">
         <v>4666666666.66667</v>
@@ -50799,7 +50893,7 @@
         <v>-525000</v>
       </c>
       <c r="AO91" s="12" t="n">
-        <v>-2.00918615485109E-014</v>
+        <v>-2.00918615485432E-014</v>
       </c>
       <c r="AP91" s="12" t="n">
         <v>4.01837230970225E-011</v>
@@ -50829,7 +50923,7 @@
         <v>-1.22464679914735E-012</v>
       </c>
       <c r="BB91" s="63" t="n">
-        <v>8.7463135318247E-013</v>
+        <v>8.74631353182468E-013</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50874,7 +50968,7 @@
       </c>
       <c r="AX92" s="162" t="n">
         <f aca="false">AT116</f>
-        <v>-0.00653690088492458</v>
+        <v>-0.00653690088492456</v>
       </c>
       <c r="AZ92" s="13" t="n">
         <v>-13333333.3333333</v>
@@ -50941,7 +51035,7 @@
         <v>328.125</v>
       </c>
       <c r="AL94" s="12" t="n">
-        <v>-2.00918615485109E-014</v>
+        <v>-2.00918615485432E-014</v>
       </c>
       <c r="AM94" s="12" t="n">
         <v>-656250</v>
@@ -50971,7 +51065,7 @@
         <v>-700000</v>
       </c>
       <c r="AV94" s="16" t="n">
-        <v>1.42875459900525E-010</v>
+        <v>1.42875459900524E-010</v>
       </c>
       <c r="AX94" s="162" t="n">
         <f aca="false">AT117</f>
@@ -51021,14 +51115,14 @@
         <v>-2333333.33333333</v>
       </c>
       <c r="AU95" s="24" t="n">
-        <v>-1.42875459900525E-010</v>
+        <v>-1.42875459900524E-010</v>
       </c>
       <c r="AV95" s="24" t="n">
         <v>4666666666.66667</v>
       </c>
       <c r="AX95" s="162" t="n">
         <f aca="false">AT118</f>
-        <v>-0.00219184652470182</v>
+        <v>-0.00219184652470184</v>
       </c>
       <c r="AZ95" s="13" t="n">
         <v>-16666666.6666667</v>
@@ -51122,7 +51216,7 @@
         <v>-525000</v>
       </c>
       <c r="AU97" s="31" t="n">
-        <v>-2.00918615485109E-014</v>
+        <v>-2.00918615485432E-014</v>
       </c>
       <c r="AV97" s="31" t="n">
         <v>4.01837230970225E-011</v>
@@ -51134,7 +51228,7 @@
         <v>6.12323399573677E-013</v>
       </c>
       <c r="BB97" s="63" t="n">
-        <v>28474.4115483278</v>
+        <v>28474.41154833</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51179,7 +51273,7 @@
       </c>
       <c r="AX98" s="162" t="n">
         <f aca="false">AT119</f>
-        <v>0.00239572823183017</v>
+        <v>0.00239572823183016</v>
       </c>
       <c r="AZ98" s="13" t="n">
         <v>6666666.66666667</v>
@@ -51230,13 +51324,13 @@
       </c>
       <c r="AX99" s="162" t="n">
         <f aca="false">AT120</f>
-        <v>-0.0542369743777673</v>
+        <v>-0.0542369743777714</v>
       </c>
       <c r="AZ99" s="13" t="n">
         <v>-30000</v>
       </c>
       <c r="BB99" s="63" t="n">
-        <v>1.16415321826935E-009</v>
+        <v>-9.78616299107671E-010</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51259,13 +51353,13 @@
         <v>-700000</v>
       </c>
       <c r="AP100" s="24" t="n">
-        <v>-1.42875459900525E-010</v>
+        <v>-1.42875459900524E-010</v>
       </c>
       <c r="AQ100" s="31" t="n">
         <v>328.125</v>
       </c>
       <c r="AR100" s="31" t="n">
-        <v>-2.00918615485109E-014</v>
+        <v>-2.00918615485432E-014</v>
       </c>
       <c r="AS100" s="31" t="n">
         <v>-656250</v>
@@ -51306,7 +51400,7 @@
         <v>2333333.33333333</v>
       </c>
       <c r="AO101" s="16" t="n">
-        <v>1.42875459900525E-010</v>
+        <v>1.42875459900524E-010</v>
       </c>
       <c r="AP101" s="24" t="n">
         <v>4666666666.66667</v>
@@ -51331,7 +51425,7 @@
       </c>
       <c r="AX101" s="162" t="n">
         <f aca="false">AT121</f>
-        <v>0.00282759115538728</v>
+        <v>0.00282759115538729</v>
       </c>
       <c r="AZ101" s="13" t="n">
         <v>23333333.3333333</v>
@@ -51520,7 +51614,7 @@
       </c>
       <c r="AP106" s="13" t="n">
         <f aca="false">AV94</f>
-        <v>1.42875459900525E-010</v>
+        <v>1.42875459900524E-010</v>
       </c>
       <c r="AQ106" s="13"/>
       <c r="AR106" s="13" t="s">
@@ -51730,7 +51824,7 @@
       </c>
       <c r="AL110" s="13" t="n">
         <f aca="false">AO101</f>
-        <v>1.42875459900525E-010</v>
+        <v>1.42875459900524E-010</v>
       </c>
       <c r="AM110" s="13" t="n">
         <f aca="false">AP101</f>
@@ -51950,16 +52044,16 @@
         <v>5.08401074255991E-010</v>
       </c>
       <c r="AM116" s="1" t="n">
-        <v>-5.81410841757986E-011</v>
+        <v>-5.81410841757989E-011</v>
       </c>
       <c r="AN116" s="1" t="n">
-        <v>-1.27273545725196E-011</v>
+        <v>-1.27273545725198E-011</v>
       </c>
       <c r="AO116" s="1" t="n">
         <v>-1.45057877355441E-010</v>
       </c>
       <c r="AP116" s="1" t="n">
-        <v>2.54547091450393E-011</v>
+        <v>2.54547091450395E-011</v>
       </c>
       <c r="AR116" s="13" t="n">
         <f aca="false">AZ92</f>
@@ -51967,14 +52061,14 @@
       </c>
       <c r="AT116" s="36" t="n">
         <f aca="false" t="array" ref="AT116:AT121">MMULT(AK116:AP121,AR116:AR121)</f>
-        <v>-0.00653690088492458</v>
+        <v>-0.00653690088492456</v>
       </c>
       <c r="AU116" s="1" t="s">
         <v>78</v>
       </c>
       <c r="AV116" s="1" t="n">
         <f aca="false">1000*AT116</f>
-        <v>-6.53690088492458</v>
+        <v>-6.53690088492456</v>
       </c>
       <c r="AW116" s="1" t="s">
         <v>79</v>
@@ -52005,16 +52099,16 @@
         <v>1.42842959074965E-006</v>
       </c>
       <c r="AM117" s="13" t="n">
-        <v>5.45200445502526E-011</v>
+        <v>5.45200445502529E-011</v>
       </c>
       <c r="AN117" s="1" t="n">
-        <v>1.19346921051993E-011</v>
+        <v>1.19346921051994E-011</v>
       </c>
       <c r="AO117" s="1" t="n">
         <v>1.36023640561366E-010</v>
       </c>
       <c r="AP117" s="1" t="n">
-        <v>-2.38693842103987E-011</v>
+        <v>-2.38693842103989E-011</v>
       </c>
       <c r="AR117" s="13" t="n">
         <f aca="false">AZ94</f>
@@ -52044,36 +52138,36 @@
         <v>6</v>
       </c>
       <c r="AK118" s="1" t="n">
-        <v>-5.81410841757986E-011</v>
+        <v>-5.81410841757989E-011</v>
       </c>
       <c r="AL118" s="13" t="n">
-        <v>5.45200445502526E-011</v>
+        <v>5.45200445502529E-011</v>
       </c>
       <c r="AM118" s="13" t="n">
         <v>1.1632305838501E-010</v>
       </c>
       <c r="AN118" s="1" t="n">
-        <v>2.54636601641182E-011</v>
+        <v>2.54636601641184E-011</v>
       </c>
       <c r="AO118" s="1" t="n">
-        <v>2.90217772441302E-010</v>
+        <v>2.90217772441303E-010</v>
       </c>
       <c r="AP118" s="1" t="n">
-        <v>-5.09273203282363E-011</v>
+        <v>-5.09273203282368E-011</v>
       </c>
       <c r="AR118" s="13" t="n">
         <f aca="false">AZ95</f>
         <v>-16666666.6666667</v>
       </c>
       <c r="AT118" s="36" t="n">
-        <v>-0.00219184652470182</v>
+        <v>-0.00219184652470184</v>
       </c>
       <c r="AU118" s="1" t="s">
         <v>78</v>
       </c>
       <c r="AV118" s="1" t="n">
         <f aca="false">1000*AT118</f>
-        <v>-2.19184652470182</v>
+        <v>-2.19184652470184</v>
       </c>
       <c r="AW118" s="1" t="s">
         <v>79</v>
@@ -52097,13 +52191,13 @@
         <v>9</v>
       </c>
       <c r="AK119" s="1" t="n">
-        <v>-1.27273545725196E-011</v>
+        <v>-1.27273545725198E-011</v>
       </c>
       <c r="AL119" s="1" t="n">
-        <v>1.19346921051993E-011</v>
+        <v>1.19346921051994E-011</v>
       </c>
       <c r="AM119" s="1" t="n">
-        <v>2.54636601641182E-011</v>
+        <v>2.54636601641184E-011</v>
       </c>
       <c r="AN119" s="1" t="n">
         <v>6.00508915512716E-010</v>
@@ -52112,21 +52206,21 @@
         <v>-1.4510515386466E-010</v>
       </c>
       <c r="AP119" s="1" t="n">
-        <v>-5.81606881682883E-011</v>
+        <v>-5.81606881682886E-011</v>
       </c>
       <c r="AR119" s="13" t="n">
         <f aca="false">AZ98</f>
         <v>6666666.66666667</v>
       </c>
       <c r="AT119" s="36" t="n">
-        <v>0.00239572823183017</v>
+        <v>0.00239572823183016</v>
       </c>
       <c r="AU119" s="1" t="s">
         <v>78</v>
       </c>
       <c r="AV119" s="1" t="n">
         <f aca="false">1000*AT119</f>
-        <v>2.39572823183017</v>
+        <v>2.39572823183016</v>
       </c>
       <c r="AW119" s="1" t="s">
         <v>79</v>
@@ -52140,29 +52234,29 @@
         <v>10</v>
       </c>
       <c r="AK120" s="1" t="n">
-        <v>-1.45057877355455E-010</v>
+        <v>-1.45057877355456E-010</v>
       </c>
       <c r="AL120" s="1" t="n">
-        <v>1.36023640561383E-010</v>
+        <v>1.36023640561362E-010</v>
       </c>
       <c r="AM120" s="1" t="n">
-        <v>2.90217772441284E-010</v>
+        <v>2.90217772441327E-010</v>
       </c>
       <c r="AN120" s="1" t="n">
-        <v>-1.45105153864703E-010</v>
+        <v>-1.45105153864619E-010</v>
       </c>
       <c r="AO120" s="1" t="n">
         <v>1.90452007389763E-006</v>
       </c>
       <c r="AP120" s="1" t="n">
-        <v>2.90210307729406E-010</v>
+        <v>2.90210307729238E-010</v>
       </c>
       <c r="AR120" s="13" t="n">
         <f aca="false">AZ99</f>
         <v>-30000</v>
       </c>
       <c r="AT120" s="36" t="n">
-        <v>-0.0542369743777673</v>
+        <v>-0.0542369743777714</v>
       </c>
       <c r="AU120" s="1" t="s">
         <v>12</v>
@@ -52172,11 +52266,11 @@
       </c>
       <c r="AY120" s="36" t="n">
         <f aca="false">AT120</f>
-        <v>-0.0542369743777673</v>
+        <v>-0.0542369743777714</v>
       </c>
       <c r="AZ120" s="164" t="n">
         <f aca="false" t="array" ref="AZ120:AZ121">MMULT(BH69:BI70,AY120:AY121)</f>
-        <v>-3.32105685335849E-018</v>
+        <v>-3.32105685335874E-018</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52187,16 +52281,16 @@
         <v>12</v>
       </c>
       <c r="AK121" s="1" t="n">
-        <v>2.54547091450393E-011</v>
+        <v>2.54547091450395E-011</v>
       </c>
       <c r="AL121" s="1" t="n">
-        <v>-2.38693842103987E-011</v>
+        <v>-2.38693842103989E-011</v>
       </c>
       <c r="AM121" s="1" t="n">
-        <v>-5.09273203282364E-011</v>
+        <v>-5.09273203282368E-011</v>
       </c>
       <c r="AN121" s="1" t="n">
-        <v>-5.81606881682883E-011</v>
+        <v>-5.81606881682886E-011</v>
       </c>
       <c r="AO121" s="13" t="n">
         <v>2.90210307729321E-010</v>
@@ -52209,14 +52303,14 @@
         <v>23333333.3333333</v>
       </c>
       <c r="AT121" s="36" t="n">
-        <v>0.00282759115538728</v>
+        <v>0.00282759115538729</v>
       </c>
       <c r="AU121" s="1" t="s">
         <v>78</v>
       </c>
       <c r="AV121" s="1" t="n">
         <f aca="false">1000*AT121</f>
-        <v>2.82759115538728</v>
+        <v>2.82759115538729</v>
       </c>
       <c r="AW121" s="1" t="s">
         <v>79</v>
@@ -52228,7 +52322,7 @@
         <v>0</v>
       </c>
       <c r="AZ121" s="164" t="n">
-        <v>-0.0542369743777673</v>
+        <v>-0.0542369743777714</v>
       </c>
       <c r="BB121" s="20"/>
       <c r="BE121" s="62"/>
@@ -52473,7 +52567,7 @@
         <v>875000000</v>
       </c>
       <c r="AR133" s="1" t="n">
-        <v>-0.00653690088492458</v>
+        <v>-0.00653690088492456</v>
       </c>
       <c r="AT133" s="13" t="n">
         <f aca="false">I30</f>
@@ -52599,7 +52693,7 @@
         <v>1750000000</v>
       </c>
       <c r="AR136" s="1" t="n">
-        <v>-0.00219184652470182</v>
+        <v>-0.00219184652470184</v>
       </c>
       <c r="AT136" s="13" t="n">
         <f aca="false">I33</f>
@@ -53712,44 +53806,44 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9.57"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="9.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="12.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="9.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="10.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="9.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="10.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="12.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="9.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="26" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="26" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="35" min="30" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="11.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="10.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="9.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="41" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="9.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="45" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="45" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="49" min="49" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="50" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="50" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="1" width="12.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="56" min="56" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="57" style="1" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="57" style="1" width="9.3"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="101" min="63" style="1" width="9.14"/>
   </cols>
   <sheetData>
@@ -53767,10 +53861,28 @@
       <c r="L3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="S3" s="0"/>
+      <c r="S3" s="157"/>
       <c r="Z3" s="4"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AC3" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
@@ -53809,6 +53921,24 @@
       <c r="X4" s="7"/>
       <c r="Y4" s="7"/>
       <c r="Z4" s="9"/>
+      <c r="AC4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF4" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG4" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH4" s="1" t="n">
+        <v>7</v>
+      </c>
       <c r="AZ4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53841,7 +53971,9 @@
         <f aca="false">D20</f>
         <v>-464038.825153672</v>
       </c>
-      <c r="P5" s="0"/>
+      <c r="P5" s="157" t="n">
+        <v>0</v>
+      </c>
       <c r="Q5" s="12" t="n">
         <f aca="false">F20</f>
         <v>-262335.9375</v>
@@ -53850,7 +53982,7 @@
         <f aca="false">G20</f>
         <v>-464038.825153672</v>
       </c>
-      <c r="S5" s="12" t="n">
+      <c r="S5" s="165" t="n">
         <f aca="false">E20</f>
         <v>-262664.0625</v>
       </c>
@@ -53861,9 +53993,43 @@
       <c r="U5" s="7"/>
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="9"/>
+      <c r="X5" s="0"/>
+      <c r="Y5" s="0"/>
+      <c r="Z5" s="0"/>
+      <c r="AA5" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="AB5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="0" t="n">
+        <v>-262335.9375</v>
+      </c>
+      <c r="AG5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="0" t="n">
+        <v>-262664.0625</v>
+      </c>
+      <c r="AI5" s="0"/>
+      <c r="AK5" s="1" t="n">
+        <f aca="false" t="array" ref="AK5:AK7">AA14:AA16</f>
+        <v>0</v>
+      </c>
+      <c r="AL5" s="0"/>
+      <c r="AM5" s="1" t="n">
+        <f aca="false" t="array" ref="AM5:AM10">MMULT(AC5:AH10,AK5:AK10)</f>
+        <v>-371231.060122938</v>
+      </c>
       <c r="AW5" s="7"/>
       <c r="BA5" s="7"/>
       <c r="BB5" s="7"/>
@@ -53904,7 +54070,9 @@
         <f aca="false">D21</f>
         <v>464038.825153672</v>
       </c>
-      <c r="P6" s="0"/>
+      <c r="P6" s="157" t="n">
+        <v>0</v>
+      </c>
       <c r="Q6" s="12" t="n">
         <f aca="false">F21</f>
         <v>-262664.0625</v>
@@ -53913,7 +54081,7 @@
         <f aca="false">G21</f>
         <v>464038.825153672</v>
       </c>
-      <c r="S6" s="12" t="n">
+      <c r="S6" s="165" t="n">
         <f aca="false">E21</f>
         <v>-262335.9375</v>
       </c>
@@ -53924,9 +54092,41 @@
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
       <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
-      <c r="Z6" s="9"/>
+      <c r="X6" s="0"/>
+      <c r="Y6" s="0"/>
+      <c r="Z6" s="0"/>
+      <c r="AA6" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB6" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="0" t="n">
+        <v>-262664.0625</v>
+      </c>
+      <c r="AG6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="0" t="n">
+        <v>-262335.9375</v>
+      </c>
+      <c r="AI6" s="0"/>
+      <c r="AK6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="0"/>
+      <c r="AM6" s="1" t="n">
+        <v>-371231.060122938</v>
+      </c>
       <c r="AW6" s="7"/>
       <c r="AX6" s="13"/>
       <c r="AZ6" s="7"/>
@@ -53970,7 +54170,9 @@
         <f aca="false">D22</f>
         <v>1750000000</v>
       </c>
-      <c r="P7" s="0"/>
+      <c r="P7" s="157" t="n">
+        <v>0</v>
+      </c>
       <c r="Q7" s="12" t="n">
         <f aca="false">F22</f>
         <v>-464038.825153672</v>
@@ -53979,7 +54181,7 @@
         <f aca="false">G22</f>
         <v>875000000</v>
       </c>
-      <c r="S7" s="12" t="n">
+      <c r="S7" s="165" t="n">
         <f aca="false">E22</f>
         <v>464038.825153672</v>
       </c>
@@ -53990,9 +54192,41 @@
       <c r="U7" s="7"/>
       <c r="V7" s="7"/>
       <c r="W7" s="41"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
-      <c r="Z7" s="35"/>
+      <c r="X7" s="0"/>
+      <c r="Y7" s="0"/>
+      <c r="Z7" s="0"/>
+      <c r="AA7" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="AB7" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="0" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="AG7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="0" t="n">
+        <v>464038.825153672</v>
+      </c>
+      <c r="AI7" s="0"/>
+      <c r="AK7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="0"/>
+      <c r="AM7" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="AW7" s="7"/>
       <c r="AX7" s="13"/>
       <c r="AZ7" s="7"/>
@@ -54024,20 +54258,70 @@
       <c r="L8" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="M8" s="0"/>
-      <c r="N8" s="0"/>
-      <c r="O8" s="0"/>
-      <c r="P8" s="0"/>
-      <c r="Q8" s="0"/>
-      <c r="R8" s="0"/>
-      <c r="S8" s="0"/>
-      <c r="T8" s="0"/>
+      <c r="M8" s="157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="157" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="157"/>
       <c r="U8" s="7"/>
       <c r="V8" s="7"/>
       <c r="W8" s="7"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
-      <c r="Z8" s="35"/>
+      <c r="X8" s="0"/>
+      <c r="Y8" s="0"/>
+      <c r="Z8" s="0"/>
+      <c r="AA8" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB8" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="0" t="n">
+        <v>262664.0625</v>
+      </c>
+      <c r="AG8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="0" t="n">
+        <v>262335.9375</v>
+      </c>
+      <c r="AI8" s="0"/>
+      <c r="AJ8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK8" s="1" t="n">
+        <f aca="false" t="array" ref="AK8:AK10">AA18:AA20</f>
+        <v>0.707106781186548</v>
+      </c>
+      <c r="AL8" s="0"/>
+      <c r="AM8" s="1" t="n">
+        <v>371231.060122938</v>
+      </c>
       <c r="AW8" s="7"/>
       <c r="AX8" s="13"/>
       <c r="AZ8" s="7"/>
@@ -54081,7 +54365,9 @@
         <f aca="false">D24</f>
         <v>-464038.825153672</v>
       </c>
-      <c r="P9" s="0"/>
+      <c r="P9" s="157" t="n">
+        <v>0</v>
+      </c>
       <c r="Q9" s="12" t="n">
         <f aca="false">F24</f>
         <v>262664.0625</v>
@@ -54090,20 +54376,52 @@
         <f aca="false">G24</f>
         <v>-464038.825153672</v>
       </c>
-      <c r="S9" s="12" t="n">
+      <c r="S9" s="165" t="n">
         <f aca="false">E24</f>
         <v>262335.9375</v>
       </c>
       <c r="T9" s="21" t="n">
-        <f aca="false">I23</f>
+        <f aca="false">I24</f>
         <v>-14142.135623731</v>
       </c>
       <c r="U9" s="7"/>
       <c r="V9" s="7"/>
       <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-      <c r="Z9" s="35"/>
+      <c r="X9" s="0"/>
+      <c r="Y9" s="0"/>
+      <c r="Z9" s="0"/>
+      <c r="AA9" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="AB9" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="0" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="AG9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="0" t="n">
+        <v>464038.825153672</v>
+      </c>
+      <c r="AI9" s="0"/>
+      <c r="AK9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="0"/>
+      <c r="AM9" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="AW9" s="7"/>
       <c r="AX9" s="13"/>
       <c r="AZ9" s="7"/>
@@ -54148,7 +54466,9 @@
         <f aca="false">D25</f>
         <v>875000000</v>
       </c>
-      <c r="P10" s="0"/>
+      <c r="P10" s="157" t="n">
+        <v>0</v>
+      </c>
       <c r="Q10" s="12" t="n">
         <f aca="false">F25</f>
         <v>-464038.825153672</v>
@@ -54157,20 +54477,55 @@
         <f aca="false">G25</f>
         <v>1750000000</v>
       </c>
-      <c r="S10" s="12" t="n">
+      <c r="S10" s="165" t="n">
         <f aca="false">E25</f>
         <v>464038.825153672</v>
       </c>
       <c r="T10" s="21" t="n">
-        <f aca="false">I24</f>
-        <v>-14142.135623731</v>
+        <f aca="false">I25</f>
+        <v>-1.63286239886314E-009</v>
       </c>
       <c r="U10" s="7"/>
       <c r="V10" s="7"/>
       <c r="W10" s="7"/>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="7"/>
-      <c r="Z10" s="13"/>
+      <c r="X10" s="0"/>
+      <c r="Y10" s="0"/>
+      <c r="Z10" s="0"/>
+      <c r="AA10" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="AB10" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="0" t="n">
+        <v>262335.9375</v>
+      </c>
+      <c r="AG10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="0" t="n">
+        <v>262664.0625</v>
+      </c>
+      <c r="AI10" s="166"/>
+      <c r="AJ10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK10" s="1" t="n">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="AL10" s="0"/>
+      <c r="AM10" s="1" t="n">
+        <v>371231.060122938</v>
+      </c>
       <c r="AW10" s="7"/>
       <c r="AX10" s="13"/>
       <c r="AZ10" s="7"/>
@@ -54202,34 +54557,36 @@
       <c r="L11" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="M11" s="165" t="n">
         <f aca="false">B23</f>
         <v>-262664.0625</v>
       </c>
-      <c r="N11" s="12" t="n">
+      <c r="N11" s="165" t="n">
         <f aca="false">C23</f>
         <v>-262335.9375</v>
       </c>
-      <c r="O11" s="12" t="n">
+      <c r="O11" s="165" t="n">
         <f aca="false">D23</f>
         <v>464038.825153672</v>
       </c>
-      <c r="P11" s="0"/>
-      <c r="Q11" s="12" t="n">
+      <c r="P11" s="157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="165" t="n">
         <f aca="false">F23</f>
         <v>262335.9375</v>
       </c>
-      <c r="R11" s="12" t="n">
+      <c r="R11" s="165" t="n">
         <f aca="false">G23</f>
         <v>464038.825153672</v>
       </c>
-      <c r="S11" s="12" t="n">
+      <c r="S11" s="165" t="n">
         <f aca="false">E23</f>
         <v>262664.0625</v>
       </c>
       <c r="T11" s="21" t="n">
-        <f aca="false">I25</f>
-        <v>-1.63286239886314E-009</v>
+        <f aca="false">I23</f>
+        <v>-14142.135623731</v>
       </c>
       <c r="U11" s="7"/>
       <c r="V11" s="7"/>
@@ -54255,31 +54612,31 @@
       <c r="BM11" s="17"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L12" s="0"/>
-      <c r="M12" s="0"/>
-      <c r="N12" s="0"/>
-      <c r="O12" s="0"/>
-      <c r="P12" s="0"/>
-      <c r="Q12" s="0"/>
-      <c r="R12" s="0"/>
-      <c r="S12" s="0"/>
-      <c r="T12" s="0"/>
-      <c r="U12" s="0"/>
-      <c r="V12" s="0"/>
-      <c r="W12" s="0"/>
-      <c r="X12" s="0"/>
-      <c r="Y12" s="0"/>
-      <c r="Z12" s="0"/>
-      <c r="AA12" s="0"/>
-      <c r="AB12" s="0"/>
-      <c r="AC12" s="0"/>
-      <c r="AD12" s="0"/>
-      <c r="AE12" s="0"/>
-      <c r="AF12" s="0"/>
-      <c r="AG12" s="0"/>
-      <c r="AH12" s="0"/>
-      <c r="AI12" s="0"/>
-      <c r="AJ12" s="0"/>
+      <c r="L12" s="157"/>
+      <c r="M12" s="157"/>
+      <c r="N12" s="157"/>
+      <c r="O12" s="157"/>
+      <c r="P12" s="157"/>
+      <c r="Q12" s="157"/>
+      <c r="R12" s="157"/>
+      <c r="S12" s="157"/>
+      <c r="T12" s="157"/>
+      <c r="U12" s="157"/>
+      <c r="V12" s="157"/>
+      <c r="W12" s="157"/>
+      <c r="X12" s="157"/>
+      <c r="Y12" s="157"/>
+      <c r="Z12" s="157"/>
+      <c r="AA12" s="157"/>
+      <c r="AB12" s="157"/>
+      <c r="AC12" s="157"/>
+      <c r="AD12" s="157"/>
+      <c r="AE12" s="157"/>
+      <c r="AF12" s="157"/>
+      <c r="AG12" s="157"/>
+      <c r="AH12" s="157"/>
+      <c r="AI12" s="157"/>
+      <c r="AJ12" s="157"/>
       <c r="AW12" s="7"/>
       <c r="AZ12" s="7"/>
       <c r="BA12" s="7"/>
@@ -54301,26 +54658,26 @@
         <v>26</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="M13" s="7"/>
       <c r="N13" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="O13" s="158" t="n">
+      <c r="O13" s="159" t="n">
         <v>0</v>
       </c>
       <c r="P13" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="Q13" s="158" t="n">
-        <v>45</v>
+      <c r="Q13" s="159" t="n">
+        <v>0</v>
       </c>
       <c r="R13" s="7"/>
-      <c r="S13" s="0"/>
+      <c r="S13" s="157"/>
       <c r="T13" s="7"/>
       <c r="U13" s="2" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="V13" s="7"/>
       <c r="W13" s="7"/>
@@ -54342,7 +54699,7 @@
       <c r="BL13" s="7"/>
       <c r="BM13" s="7"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
         <v>27</v>
       </c>
@@ -54355,45 +54712,50 @@
       <c r="L14" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="M14" s="167" t="n">
         <f aca="false">COS(RADIANS(O13))</f>
         <v>1</v>
       </c>
-      <c r="N14" s="12" t="n">
+      <c r="N14" s="167" t="n">
         <f aca="false">SIN(RADIANS(O13))</f>
         <v>0</v>
       </c>
-      <c r="O14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="0"/>
+      <c r="O14" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="167" t="n">
+        <v>0</v>
+      </c>
       <c r="T14" s="7"/>
-      <c r="U14" s="12" t="n">
-        <f aca="false" t="array" ref="U14:Z19">TRANSPOSE(M14:R19)</f>
+      <c r="U14" s="167" t="n">
+        <f aca="false" t="array" ref="U14:AA20">TRANSPOSE(M14:S20)</f>
         <v>1</v>
       </c>
-      <c r="V14" s="12" t="n">
+      <c r="V14" s="167" t="n">
         <v>-0</v>
       </c>
-      <c r="W14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="12" t="n">
+      <c r="W14" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="167" t="n">
         <v>0</v>
       </c>
       <c r="AW14" s="7"/>
@@ -54412,7 +54774,7 @@
       <c r="BL14" s="7"/>
       <c r="BM14" s="7"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
@@ -54425,44 +54787,49 @@
       <c r="L15" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="M15" s="167" t="n">
         <f aca="false">-SIN(RADIANS(O13))</f>
         <v>-0</v>
       </c>
-      <c r="N15" s="12" t="n">
+      <c r="N15" s="167" t="n">
         <f aca="false">COS(RADIANS(O13))</f>
         <v>1</v>
       </c>
-      <c r="O15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="0"/>
+      <c r="O15" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="167" t="n">
+        <v>0</v>
+      </c>
       <c r="T15" s="7"/>
-      <c r="U15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="12" t="n">
+      <c r="U15" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="167" t="n">
         <v>1</v>
       </c>
-      <c r="W15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="12" t="n">
+      <c r="W15" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="167" t="n">
         <v>0</v>
       </c>
       <c r="AW15" s="7"/>
@@ -54483,47 +54850,52 @@
       <c r="BM15" s="17"/>
       <c r="BN15" s="17"/>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E16" s="13"/>
       <c r="L16" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="M16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="12" t="n">
+      <c r="M16" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="167" t="n">
         <v>1</v>
       </c>
-      <c r="P16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="0"/>
+      <c r="P16" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="167" t="n">
+        <v>0</v>
+      </c>
       <c r="T16" s="7"/>
-      <c r="U16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" s="12" t="n">
+      <c r="U16" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="167" t="n">
         <v>1</v>
       </c>
-      <c r="X16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="12" t="n">
+      <c r="X16" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="167" t="n">
         <v>0</v>
       </c>
       <c r="AW16" s="7"/>
@@ -54544,47 +54916,52 @@
       <c r="BM16" s="17"/>
       <c r="BN16" s="20"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L17" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="M17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="12" t="n">
+      <c r="M17" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="167" t="n">
         <f aca="false">COS(RADIANS(Q13))</f>
-        <v>0.707106781186548</v>
-      </c>
-      <c r="Q17" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="167" t="n">
         <f aca="false">SIN(RADIANS(Q13))</f>
-        <v>0.707106781186548</v>
-      </c>
-      <c r="R17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="0"/>
-      <c r="U17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" s="12" t="n">
-        <v>0.707106781186548</v>
-      </c>
-      <c r="Y17" s="12" t="n">
-        <v>-0.707106781186548</v>
-      </c>
-      <c r="Z17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="167" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="167" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z17" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="167" t="n">
         <v>0</v>
       </c>
       <c r="AW17" s="7"/>
@@ -54605,58 +54982,85 @@
       <c r="BM17" s="17"/>
       <c r="BN17" s="20"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L18" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="M18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="12" t="n">
+      <c r="M18" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="167" t="n">
         <f aca="false">-SIN(RADIANS(Q13))</f>
-        <v>-0.707106781186548</v>
-      </c>
-      <c r="Q18" s="12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q18" s="167" t="n">
         <f aca="false">COS(RADIANS(Q13))</f>
+        <v>1</v>
+      </c>
+      <c r="R18" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="167" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="167" t="n">
         <v>0.707106781186548</v>
       </c>
-      <c r="R18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="0"/>
-      <c r="U18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" s="12" t="n">
-        <v>0.707106781186548</v>
-      </c>
-      <c r="Y18" s="12" t="n">
-        <v>0.707106781186548</v>
-      </c>
-      <c r="Z18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" s="7"/>
-      <c r="AN18" s="7"/>
-      <c r="AO18" s="7"/>
-      <c r="AP18" s="7"/>
-      <c r="AQ18" s="7"/>
-      <c r="AR18" s="7"/>
-      <c r="AS18" s="7"/>
-      <c r="AT18" s="7"/>
-      <c r="AU18" s="7"/>
+      <c r="AK18" s="7"/>
+      <c r="AL18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM18" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN18" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO18" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP18" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ18" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR18" s="7" t="n">
+        <v>111</v>
+      </c>
+      <c r="AS18" s="7" t="n">
+        <v>112</v>
+      </c>
+      <c r="AT18" s="7" t="n">
+        <v>113</v>
+      </c>
+      <c r="AU18" s="7" t="n">
+        <v>114</v>
+      </c>
       <c r="AV18" s="7"/>
       <c r="AW18" s="7"/>
       <c r="AX18" s="7"/>
@@ -54686,52 +55090,61 @@
       <c r="L19" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="M19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="12" t="n">
+      <c r="M19" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="167" t="n">
         <v>1</v>
       </c>
-      <c r="S19" s="0"/>
-      <c r="U19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="12" t="n">
+      <c r="S19" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="167" t="n">
         <v>1</v>
       </c>
-      <c r="AM19" s="7"/>
-      <c r="AN19" s="21"/>
-      <c r="AO19" s="7"/>
-      <c r="AP19" s="7"/>
-      <c r="AQ19" s="7"/>
-      <c r="AR19" s="7"/>
-      <c r="AS19" s="7"/>
-      <c r="AT19" s="7"/>
-      <c r="AU19" s="21"/>
+      <c r="AA19" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL19" s="0"/>
+      <c r="AM19" s="0"/>
+      <c r="AN19" s="0"/>
+      <c r="AO19" s="0"/>
+      <c r="AP19" s="0"/>
+      <c r="AQ19" s="0"/>
+      <c r="AR19" s="0"/>
+      <c r="AS19" s="0"/>
+      <c r="AT19" s="0"/>
+      <c r="AU19" s="0"/>
       <c r="AV19" s="7"/>
       <c r="AW19" s="7"/>
       <c r="AX19" s="7"/>
@@ -54783,8 +55196,76 @@
       <c r="L20" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="S20" s="0"/>
+      <c r="M20" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="167" t="n">
+        <f aca="false">E5</f>
+        <v>0.707106781186548</v>
+      </c>
+      <c r="R20" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="167" t="n">
+        <f aca="false">C5</f>
+        <v>0.707106781186548</v>
+      </c>
+      <c r="U20" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="167" t="n">
+        <v>0.707106781186548</v>
+      </c>
       <c r="AD20" s="2"/>
+      <c r="AK20" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL20" s="0"/>
+      <c r="AM20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="0"/>
+      <c r="AP20" s="0"/>
+      <c r="AQ20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="AS20" s="0"/>
+      <c r="AT20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="22" t="n">
@@ -54815,34 +55296,48 @@
         <f aca="false">B55*I28+C55*I29+D55*I30+E55*I31+F55*I32+G55*I33</f>
         <v>-14142.135623731</v>
       </c>
-      <c r="L21" s="0"/>
-      <c r="M21" s="0"/>
-      <c r="N21" s="0"/>
-      <c r="O21" s="0"/>
-      <c r="P21" s="0"/>
-      <c r="Q21" s="0"/>
-      <c r="R21" s="0"/>
-      <c r="S21" s="0"/>
-      <c r="T21" s="0"/>
-      <c r="U21" s="0"/>
-      <c r="V21" s="0"/>
-      <c r="W21" s="0"/>
-      <c r="X21" s="0"/>
-      <c r="Y21" s="0"/>
-      <c r="Z21" s="0"/>
-      <c r="AA21" s="0"/>
-      <c r="AB21" s="0"/>
-      <c r="AK21" s="7"/>
-      <c r="AL21" s="7"/>
-      <c r="AM21" s="7"/>
-      <c r="AN21" s="7"/>
-      <c r="AO21" s="7"/>
-      <c r="AP21" s="7"/>
-      <c r="AQ21" s="7"/>
-      <c r="AR21" s="7"/>
-      <c r="AS21" s="7"/>
-      <c r="AT21" s="7"/>
-      <c r="AU21" s="7"/>
+      <c r="L21" s="157"/>
+      <c r="M21" s="157"/>
+      <c r="N21" s="157"/>
+      <c r="O21" s="157"/>
+      <c r="P21" s="157"/>
+      <c r="Q21" s="157"/>
+      <c r="R21" s="157"/>
+      <c r="S21" s="157"/>
+      <c r="T21" s="157"/>
+      <c r="U21" s="157"/>
+      <c r="V21" s="157"/>
+      <c r="W21" s="157"/>
+      <c r="X21" s="157"/>
+      <c r="Y21" s="157"/>
+      <c r="Z21" s="157"/>
+      <c r="AA21" s="157"/>
+      <c r="AB21" s="157"/>
+      <c r="AK21" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL21" s="0"/>
+      <c r="AM21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO21" s="0"/>
+      <c r="AP21" s="0"/>
+      <c r="AQ21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" s="0"/>
+      <c r="AT21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="AV21" s="7"/>
       <c r="AW21" s="7"/>
     </row>
@@ -54878,7 +55373,7 @@
       <c r="L22" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="S22" s="0"/>
+      <c r="S22" s="157"/>
       <c r="T22" s="7"/>
       <c r="U22" s="7"/>
       <c r="V22" s="7"/>
@@ -54886,21 +55381,23 @@
       <c r="X22" s="7"/>
       <c r="Y22" s="7"/>
       <c r="Z22" s="13"/>
-      <c r="AK22" s="7"/>
-      <c r="AL22" s="7"/>
-      <c r="AM22" s="7"/>
-      <c r="AN22" s="7"/>
-      <c r="AO22" s="7"/>
-      <c r="AP22" s="7"/>
-      <c r="AQ22" s="7"/>
-      <c r="AR22" s="7"/>
-      <c r="AS22" s="7"/>
-      <c r="AT22" s="7"/>
-      <c r="AU22" s="7"/>
+      <c r="AK22" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL22" s="0"/>
+      <c r="AM22" s="0"/>
+      <c r="AN22" s="0"/>
+      <c r="AO22" s="0"/>
+      <c r="AP22" s="0"/>
+      <c r="AQ22" s="0"/>
+      <c r="AR22" s="0"/>
+      <c r="AS22" s="0"/>
+      <c r="AT22" s="0"/>
+      <c r="AU22" s="0"/>
       <c r="AV22" s="7"/>
       <c r="AW22" s="7"/>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="22" t="n">
         <f aca="false">$B39*B$45+$C39*B$46+$D39*B$47+$E39*B$48+$F39*B$49+$G39*B$50</f>
         <v>-262664.0625</v>
@@ -54970,17 +55467,19 @@
       <c r="AA23" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="AK23" s="7"/>
-      <c r="AL23" s="7"/>
-      <c r="AM23" s="7"/>
-      <c r="AN23" s="7"/>
-      <c r="AO23" s="7"/>
-      <c r="AP23" s="7"/>
-      <c r="AQ23" s="7"/>
-      <c r="AR23" s="7"/>
-      <c r="AS23" s="7"/>
-      <c r="AT23" s="7"/>
-      <c r="AU23" s="7"/>
+      <c r="AK23" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL23" s="0"/>
+      <c r="AM23" s="0"/>
+      <c r="AN23" s="0"/>
+      <c r="AO23" s="0"/>
+      <c r="AP23" s="0"/>
+      <c r="AQ23" s="0"/>
+      <c r="AR23" s="0"/>
+      <c r="AS23" s="0"/>
+      <c r="AT23" s="0"/>
+      <c r="AU23" s="0"/>
       <c r="AV23" s="7"/>
       <c r="AW23" s="7"/>
     </row>
@@ -55016,13 +55515,28 @@
       <c r="L24" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
-      <c r="O24" s="17"/>
-      <c r="P24" s="17"/>
-      <c r="Q24" s="17"/>
-      <c r="R24" s="17"/>
-      <c r="S24" s="165"/>
+      <c r="M24" s="167" t="n">
+        <f aca="false" t="array" ref="M24:S30">M5:S11</f>
+        <v>262664.0625</v>
+      </c>
+      <c r="N24" s="167" t="n">
+        <v>262335.9375</v>
+      </c>
+      <c r="O24" s="167" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="P24" s="168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="167" t="n">
+        <v>-262335.9375</v>
+      </c>
+      <c r="R24" s="167" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="S24" s="169" t="n">
+        <v>-262664.0625</v>
+      </c>
       <c r="U24" s="7" t="n">
         <v>0</v>
       </c>
@@ -55038,21 +55552,35 @@
         <v>0</v>
       </c>
       <c r="Z24" s="7"/>
-      <c r="AA24" s="7" t="e">
+      <c r="AA24" s="7" t="n">
         <f aca="false" t="array" ref="AA24:AA29">MMULT(M24:R29,Y24:Y29)-W24:W29</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AK24" s="7"/>
-      <c r="AL24" s="7"/>
-      <c r="AM24" s="7"/>
-      <c r="AN24" s="7"/>
-      <c r="AO24" s="7"/>
-      <c r="AP24" s="7"/>
-      <c r="AQ24" s="7"/>
-      <c r="AR24" s="7"/>
-      <c r="AS24" s="7"/>
-      <c r="AT24" s="7"/>
-      <c r="AU24" s="7"/>
+        <v>14142.135623731</v>
+      </c>
+      <c r="AK24" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL24" s="0"/>
+      <c r="AM24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="0"/>
+      <c r="AP24" s="0"/>
+      <c r="AQ24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" s="0"/>
+      <c r="AT24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="AV24" s="7"/>
       <c r="AW24" s="7"/>
     </row>
@@ -55089,13 +55617,27 @@
       <c r="L25" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
-      <c r="P25" s="17"/>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="17"/>
-      <c r="S25" s="165"/>
+      <c r="M25" s="167" t="n">
+        <v>262335.9375</v>
+      </c>
+      <c r="N25" s="167" t="n">
+        <v>262664.0625</v>
+      </c>
+      <c r="O25" s="167" t="n">
+        <v>464038.825153672</v>
+      </c>
+      <c r="P25" s="168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="167" t="n">
+        <v>-262664.0625</v>
+      </c>
+      <c r="R25" s="167" t="n">
+        <v>464038.825153672</v>
+      </c>
+      <c r="S25" s="169" t="n">
+        <v>-262335.9375</v>
+      </c>
       <c r="U25" s="7" t="n">
         <v>0</v>
       </c>
@@ -55110,20 +55652,34 @@
         <v>0</v>
       </c>
       <c r="Z25" s="37"/>
-      <c r="AA25" s="20" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="AK25" s="7"/>
-      <c r="AL25" s="7"/>
-      <c r="AM25" s="7"/>
-      <c r="AN25" s="7"/>
-      <c r="AO25" s="7"/>
-      <c r="AP25" s="7"/>
-      <c r="AQ25" s="7"/>
-      <c r="AR25" s="7"/>
-      <c r="AS25" s="7"/>
-      <c r="AT25" s="7"/>
-      <c r="AU25" s="7"/>
+      <c r="AA25" s="20" t="n">
+        <v>14142.135623731</v>
+      </c>
+      <c r="AK25" s="7" t="n">
+        <v>111</v>
+      </c>
+      <c r="AL25" s="170"/>
+      <c r="AM25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="0"/>
+      <c r="AP25" s="0"/>
+      <c r="AQ25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="AS25" s="0"/>
+      <c r="AT25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="AV25" s="7"/>
       <c r="AW25" s="7"/>
     </row>
@@ -55132,13 +55688,27 @@
       <c r="L26" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="17"/>
-      <c r="R26" s="17"/>
-      <c r="S26" s="165"/>
+      <c r="M26" s="167" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="N26" s="167" t="n">
+        <v>464038.825153672</v>
+      </c>
+      <c r="O26" s="167" t="n">
+        <v>1750000000</v>
+      </c>
+      <c r="P26" s="168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="167" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="R26" s="167" t="n">
+        <v>875000000</v>
+      </c>
+      <c r="S26" s="169" t="n">
+        <v>464038.825153672</v>
+      </c>
       <c r="U26" s="7" t="s">
         <v>44</v>
       </c>
@@ -55146,25 +55716,27 @@
         <f aca="false">T7</f>
         <v>1.63286239886314E-009</v>
       </c>
-      <c r="Y26" s="36" t="e">
+      <c r="Y26" s="36" t="n">
         <f aca="false">V58</f>
-        <v>#VALUE!</v>
+        <v>1.86612845584359E-018</v>
       </c>
       <c r="Z26" s="37"/>
-      <c r="AA26" s="20" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="AK26" s="7"/>
+      <c r="AA26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="7" t="n">
+        <v>112</v>
+      </c>
       <c r="AL26" s="7"/>
-      <c r="AM26" s="7"/>
-      <c r="AN26" s="7"/>
-      <c r="AO26" s="7"/>
-      <c r="AP26" s="7"/>
-      <c r="AQ26" s="7"/>
-      <c r="AR26" s="7"/>
-      <c r="AS26" s="7"/>
-      <c r="AT26" s="7"/>
-      <c r="AU26" s="7"/>
+      <c r="AM26" s="0"/>
+      <c r="AN26" s="0"/>
+      <c r="AO26" s="0"/>
+      <c r="AP26" s="0"/>
+      <c r="AQ26" s="0"/>
+      <c r="AR26" s="0"/>
+      <c r="AS26" s="0"/>
+      <c r="AT26" s="0"/>
+      <c r="AU26" s="0"/>
       <c r="AV26" s="7"/>
       <c r="AW26" s="7"/>
       <c r="AY26" s="2"/>
@@ -55179,42 +55751,68 @@
       <c r="L27" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
-      <c r="O27" s="17"/>
-      <c r="P27" s="17"/>
-      <c r="Q27" s="17"/>
-      <c r="R27" s="17"/>
-      <c r="S27" s="165"/>
-      <c r="U27" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="W27" s="13" t="n">
-        <f aca="false">T9</f>
-        <v>-14142.135623731</v>
+      <c r="M27" s="168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="168" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="168" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="171" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="X27" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Y27" s="36" t="e">
-        <f aca="false">V65</f>
-        <v>#VALUE!</v>
+      <c r="Y27" s="36" t="n">
+        <v>0</v>
       </c>
       <c r="Z27" s="37"/>
-      <c r="AA27" s="20" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="AK27" s="7"/>
+      <c r="AA27" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="7" t="n">
+        <v>113</v>
+      </c>
       <c r="AL27" s="7"/>
-      <c r="AM27" s="7"/>
-      <c r="AN27" s="7"/>
-      <c r="AO27" s="7"/>
-      <c r="AP27" s="7"/>
-      <c r="AQ27" s="7"/>
-      <c r="AR27" s="7"/>
-      <c r="AS27" s="7"/>
-      <c r="AT27" s="7"/>
-      <c r="AU27" s="7"/>
+      <c r="AM27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="0"/>
+      <c r="AP27" s="0"/>
+      <c r="AQ27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" s="0"/>
+      <c r="AT27" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="AU27" s="7" t="s">
+        <v>9</v>
+      </c>
       <c r="AV27" s="7"/>
       <c r="AW27" s="7"/>
       <c r="AY27" s="2"/>
@@ -55247,48 +55845,75 @@
       <c r="L28" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="M28" s="17"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="17"/>
-      <c r="P28" s="17"/>
-      <c r="Q28" s="17"/>
-      <c r="R28" s="17"/>
-      <c r="S28" s="165"/>
+      <c r="M28" s="167" t="n">
+        <v>-262335.9375</v>
+      </c>
+      <c r="N28" s="167" t="n">
+        <v>-262664.0625</v>
+      </c>
+      <c r="O28" s="167" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="P28" s="168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="167" t="n">
+        <v>262664.0625</v>
+      </c>
+      <c r="R28" s="167" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="S28" s="169" t="n">
+        <v>262335.9375</v>
+      </c>
       <c r="U28" s="7" t="n">
         <v>0</v>
       </c>
       <c r="W28" s="13" t="n">
-        <f aca="false">T10</f>
+        <f aca="false">T9</f>
         <v>-14142.135623731</v>
       </c>
       <c r="X28" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Y28" s="36" t="e">
-        <f aca="false">V66</f>
-        <v>#VALUE!</v>
+      <c r="Y28" s="36" t="n">
+        <v>0</v>
       </c>
       <c r="Z28" s="34"/>
-      <c r="AA28" s="34" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="AK28" s="7"/>
+      <c r="AA28" s="34" t="n">
+        <v>14142.135623731</v>
+      </c>
+      <c r="AK28" s="7" t="n">
+        <v>114</v>
+      </c>
       <c r="AL28" s="7"/>
-      <c r="AM28" s="7"/>
-      <c r="AN28" s="7"/>
-      <c r="AO28" s="7"/>
-      <c r="AP28" s="7"/>
-      <c r="AQ28" s="17"/>
-      <c r="AR28" s="17"/>
-      <c r="AS28" s="17"/>
-      <c r="AT28" s="17"/>
-      <c r="AU28" s="17"/>
+      <c r="AM28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="0"/>
+      <c r="AP28" s="0"/>
+      <c r="AQ28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" s="0"/>
+      <c r="AT28" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="AU28" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="AV28" s="17"/>
       <c r="AW28" s="7"/>
       <c r="AX28" s="13"/>
       <c r="AY28" s="32"/>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="29" t="n">
         <v>0</v>
       </c>
@@ -55318,27 +55943,41 @@
       <c r="L29" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="17"/>
-      <c r="P29" s="17"/>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="17"/>
-      <c r="S29" s="165"/>
+      <c r="M29" s="167" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="N29" s="167" t="n">
+        <v>464038.825153672</v>
+      </c>
+      <c r="O29" s="167" t="n">
+        <v>875000000</v>
+      </c>
+      <c r="P29" s="168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="167" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="R29" s="167" t="n">
+        <v>1750000000</v>
+      </c>
+      <c r="S29" s="169" t="n">
+        <v>464038.825153672</v>
+      </c>
       <c r="U29" s="7" t="s">
         <v>115</v>
       </c>
       <c r="W29" s="13" t="n">
-        <f aca="false">T11</f>
+        <f aca="false">T10</f>
         <v>-1.63286239886314E-009</v>
       </c>
-      <c r="Y29" s="40" t="e">
-        <f aca="false">V60</f>
-        <v>#VALUE!</v>
+      <c r="Y29" s="40" t="n">
+        <f aca="false">V59</f>
+        <v>-1.86612845584359E-018</v>
       </c>
       <c r="Z29" s="37"/>
-      <c r="AA29" s="20" t="e">
-        <v>#VALUE!</v>
+      <c r="AA29" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="AK29" s="7"/>
       <c r="AL29" s="7"/>
@@ -55356,7 +55995,7 @@
       <c r="AX29" s="13"/>
       <c r="AY29" s="33"/>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="29" t="n">
         <v>0</v>
       </c>
@@ -55386,18 +56025,42 @@
       <c r="L30" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="M30" s="159"/>
-      <c r="N30" s="159"/>
-      <c r="O30" s="159"/>
-      <c r="P30" s="159"/>
-      <c r="Q30" s="159"/>
-      <c r="R30" s="159"/>
-      <c r="S30" s="165"/>
-      <c r="U30" s="7"/>
-      <c r="W30" s="13"/>
-      <c r="Y30" s="36"/>
+      <c r="M30" s="169" t="n">
+        <v>-262664.0625</v>
+      </c>
+      <c r="N30" s="169" t="n">
+        <v>-262335.9375</v>
+      </c>
+      <c r="O30" s="169" t="n">
+        <v>464038.825153672</v>
+      </c>
+      <c r="P30" s="171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="169" t="n">
+        <v>262335.9375</v>
+      </c>
+      <c r="R30" s="169" t="n">
+        <v>464038.825153672</v>
+      </c>
+      <c r="S30" s="169" t="n">
+        <v>262664.0625</v>
+      </c>
+      <c r="U30" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="W30" s="13" t="n">
+        <f aca="false">T11</f>
+        <v>-14142.135623731</v>
+      </c>
+      <c r="Y30" s="36" t="n">
+        <f aca="false">V60</f>
+        <v>-0.0380952380952381</v>
+      </c>
       <c r="Z30" s="37"/>
-      <c r="AA30" s="20"/>
+      <c r="AA30" s="20" t="n">
+        <v>0</v>
+      </c>
       <c r="AK30" s="7"/>
       <c r="AL30" s="7"/>
       <c r="AM30" s="7"/>
@@ -55439,22 +56102,22 @@
         <f aca="false">-E6/2*E15*I38</f>
         <v>-20000</v>
       </c>
-      <c r="L31" s="0"/>
-      <c r="M31" s="0"/>
-      <c r="N31" s="0"/>
-      <c r="O31" s="0"/>
-      <c r="P31" s="0"/>
-      <c r="Q31" s="0"/>
-      <c r="R31" s="0"/>
-      <c r="S31" s="0"/>
-      <c r="T31" s="0"/>
-      <c r="U31" s="0"/>
-      <c r="V31" s="0"/>
-      <c r="W31" s="0"/>
-      <c r="X31" s="0"/>
-      <c r="Y31" s="0"/>
-      <c r="Z31" s="0"/>
-      <c r="AA31" s="0"/>
+      <c r="L31" s="157"/>
+      <c r="M31" s="157"/>
+      <c r="N31" s="157"/>
+      <c r="O31" s="157"/>
+      <c r="P31" s="157"/>
+      <c r="Q31" s="157"/>
+      <c r="R31" s="157"/>
+      <c r="S31" s="157"/>
+      <c r="T31" s="157"/>
+      <c r="U31" s="157"/>
+      <c r="V31" s="157"/>
+      <c r="W31" s="157"/>
+      <c r="X31" s="157"/>
+      <c r="Y31" s="157"/>
+      <c r="Z31" s="157"/>
+      <c r="AA31" s="157"/>
       <c r="AK31" s="7"/>
       <c r="AL31" s="7"/>
       <c r="AM31" s="7"/>
@@ -55501,7 +56164,7 @@
       <c r="L32" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="S32" s="0"/>
+      <c r="S32" s="157"/>
       <c r="U32" s="7"/>
       <c r="W32" s="10" t="s">
         <v>117</v>
@@ -55526,7 +56189,7 @@
       <c r="AX32" s="13"/>
       <c r="AY32" s="33"/>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="29" t="n">
         <v>0</v>
       </c>
@@ -55598,20 +56261,35 @@
       <c r="AX33" s="13"/>
       <c r="AY33" s="32"/>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L34" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="M34" s="17"/>
-      <c r="N34" s="17"/>
-      <c r="O34" s="17"/>
-      <c r="P34" s="17"/>
-      <c r="Q34" s="17"/>
-      <c r="R34" s="17"/>
-      <c r="S34" s="165"/>
+      <c r="M34" s="165" t="n">
+        <f aca="false" t="array" ref="M34:S40">MMULT(M24:S30,U14:AA20)</f>
+        <v>262664.0625</v>
+      </c>
+      <c r="N34" s="165" t="n">
+        <v>262335.9375</v>
+      </c>
+      <c r="O34" s="165" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="P34" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="165" t="n">
+        <v>-262335.9375</v>
+      </c>
+      <c r="R34" s="165" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="S34" s="172" t="n">
+        <v>-371231.060122938</v>
+      </c>
       <c r="U34" s="7"/>
       <c r="W34" s="13" t="n">
-        <f aca="false" t="array" ref="W34:W39">MMULT(M14:R19,W24:W29)</f>
+        <f aca="false" t="array" ref="W34:W40">MMULT(M14:S20,W24:W30)</f>
         <v>-14142.135623731</v>
       </c>
       <c r="Y34" s="36"/>
@@ -55633,7 +56311,7 @@
       <c r="BO34" s="7"/>
       <c r="BP34" s="7"/>
     </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="2" t="s">
         <v>35</v>
       </c>
@@ -55643,13 +56321,27 @@
       <c r="L35" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
-      <c r="O35" s="17"/>
-      <c r="P35" s="17"/>
-      <c r="Q35" s="17"/>
-      <c r="R35" s="17"/>
-      <c r="S35" s="165"/>
+      <c r="M35" s="165" t="n">
+        <v>262335.9375</v>
+      </c>
+      <c r="N35" s="165" t="n">
+        <v>262664.0625</v>
+      </c>
+      <c r="O35" s="165" t="n">
+        <v>464038.825153672</v>
+      </c>
+      <c r="P35" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="165" t="n">
+        <v>-262664.0625</v>
+      </c>
+      <c r="R35" s="165" t="n">
+        <v>464038.825153672</v>
+      </c>
+      <c r="S35" s="172" t="n">
+        <v>-371231.060122938</v>
+      </c>
       <c r="W35" s="13" t="n">
         <v>-14142.135623731</v>
       </c>
@@ -55669,7 +56361,7 @@
       <c r="BO35" s="7"/>
       <c r="BP35" s="7"/>
     </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="28" t="n">
         <f aca="false">$B54*B28+$C54*B29+$D54*B30+$E54*B31+$F54*B32+$G54*B33</f>
         <v>371231.060122938</v>
@@ -55700,13 +56392,27 @@
       <c r="L36" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="M36" s="17"/>
-      <c r="N36" s="17"/>
-      <c r="O36" s="17"/>
-      <c r="P36" s="17"/>
-      <c r="Q36" s="17"/>
-      <c r="R36" s="17"/>
-      <c r="S36" s="165"/>
+      <c r="M36" s="165" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="N36" s="165" t="n">
+        <v>464038.825153672</v>
+      </c>
+      <c r="O36" s="165" t="n">
+        <v>1750000000</v>
+      </c>
+      <c r="P36" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="165" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="R36" s="165" t="n">
+        <v>875000000</v>
+      </c>
+      <c r="S36" s="172" t="n">
+        <v>0</v>
+      </c>
       <c r="W36" s="13" t="n">
         <v>1.63286239886314E-009</v>
       </c>
@@ -55715,7 +56421,7 @@
       <c r="AF36" s="34"/>
       <c r="AG36" s="34"/>
     </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="28" t="n">
         <f aca="false">$B55*B28+$C55*B29+$D55*B30+$E55*B31+$F55*B32+$G55*B33</f>
         <v>371231.060122938</v>
@@ -55746,15 +56452,29 @@
       <c r="L37" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="M37" s="17"/>
-      <c r="N37" s="17"/>
-      <c r="O37" s="17"/>
-      <c r="P37" s="17"/>
-      <c r="Q37" s="17"/>
-      <c r="R37" s="17"/>
-      <c r="S37" s="165"/>
+      <c r="M37" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="172" t="n">
+        <v>0</v>
+      </c>
       <c r="W37" s="13" t="n">
-        <v>-20000</v>
+        <v>0</v>
       </c>
       <c r="AC37" s="20"/>
       <c r="AE37" s="7"/>
@@ -55791,21 +56511,70 @@
       <c r="L38" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="M38" s="17"/>
-      <c r="N38" s="17"/>
-      <c r="O38" s="17"/>
-      <c r="P38" s="17"/>
-      <c r="Q38" s="17"/>
-      <c r="R38" s="17"/>
-      <c r="S38" s="165"/>
+      <c r="M38" s="165" t="n">
+        <v>-262335.9375</v>
+      </c>
+      <c r="N38" s="165" t="n">
+        <v>-262664.0625</v>
+      </c>
+      <c r="O38" s="165" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="P38" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="165" t="n">
+        <v>262664.0625</v>
+      </c>
+      <c r="R38" s="165" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="S38" s="172" t="n">
+        <v>371231.060122938</v>
+      </c>
       <c r="W38" s="13" t="n">
-        <v>0</v>
+        <v>-14142.135623731</v>
       </c>
       <c r="AC38" s="20"/>
-      <c r="AD38" s="7"/>
-      <c r="AE38" s="20"/>
-      <c r="AF38" s="46"/>
-      <c r="AG38" s="46"/>
+      <c r="AD38" s="7" t="n">
+        <f aca="false" t="array" ref="AD38:AF38">M20:O20</f>
+        <v>0</v>
+      </c>
+      <c r="AE38" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" s="46" t="n">
+        <f aca="false" t="array" ref="AG38:AI38">Q20:S20</f>
+        <v>0.707106781186548</v>
+      </c>
+      <c r="AH38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" s="1" t="n">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="AK38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" s="0"/>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="28" t="n">
@@ -55839,17 +56608,50 @@
       <c r="L39" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="M39" s="17"/>
-      <c r="N39" s="17"/>
-      <c r="O39" s="17"/>
-      <c r="P39" s="17"/>
-      <c r="Q39" s="17"/>
-      <c r="R39" s="17"/>
-      <c r="S39" s="165"/>
+      <c r="M39" s="165" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="N39" s="165" t="n">
+        <v>464038.825153672</v>
+      </c>
+      <c r="O39" s="165" t="n">
+        <v>875000000</v>
+      </c>
+      <c r="P39" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="165" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="R39" s="165" t="n">
+        <v>1750000000</v>
+      </c>
+      <c r="S39" s="172" t="n">
+        <v>0</v>
+      </c>
       <c r="W39" s="13" t="n">
         <v>-1.63286239886314E-009</v>
       </c>
       <c r="AE39" s="20"/>
+      <c r="AK39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" s="0"/>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="28" t="n">
@@ -55879,22 +56681,75 @@
       <c r="L40" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="M40" s="165"/>
-      <c r="N40" s="165"/>
-      <c r="O40" s="165"/>
-      <c r="P40" s="165"/>
-      <c r="Q40" s="165"/>
-      <c r="R40" s="165"/>
-      <c r="S40" s="165"/>
-      <c r="T40" s="0"/>
-      <c r="U40" s="0"/>
-      <c r="V40" s="0"/>
-      <c r="W40" s="0"/>
-      <c r="X40" s="0"/>
-      <c r="Y40" s="0"/>
-      <c r="Z40" s="0"/>
-      <c r="AA40" s="0"/>
-      <c r="AE40" s="20"/>
+      <c r="M40" s="172" t="n">
+        <v>-262664.0625</v>
+      </c>
+      <c r="N40" s="172" t="n">
+        <v>-262335.9375</v>
+      </c>
+      <c r="O40" s="172" t="n">
+        <v>464038.825153672</v>
+      </c>
+      <c r="P40" s="172" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="172" t="n">
+        <v>262335.9375</v>
+      </c>
+      <c r="R40" s="172" t="n">
+        <v>464038.825153672</v>
+      </c>
+      <c r="S40" s="172" t="n">
+        <v>371231.060122938</v>
+      </c>
+      <c r="T40" s="157"/>
+      <c r="U40" s="157"/>
+      <c r="V40" s="157"/>
+      <c r="W40" s="158" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="X40" s="157"/>
+      <c r="Y40" s="157"/>
+      <c r="Z40" s="157"/>
+      <c r="AA40" s="157"/>
+      <c r="AD40" s="1" t="n">
+        <f aca="false" t="array" ref="AD40:AI40">MMULT(AD38:AI38,AK38:AP43)</f>
+        <v>-371231.060122938</v>
+      </c>
+      <c r="AE40" s="1" t="n">
+        <v>-633731.060122938</v>
+      </c>
+      <c r="AF40" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" s="56" t="n">
+        <v>371231.060122938</v>
+      </c>
+      <c r="AH40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" s="1" t="n">
+        <v>525000</v>
+      </c>
+      <c r="AK40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" s="0"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="28" t="n">
@@ -55924,13 +56779,32 @@
       <c r="L41" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="S41" s="0"/>
+      <c r="S41" s="157"/>
       <c r="AD41" s="7"/>
       <c r="AE41" s="20"/>
       <c r="AF41" s="7"/>
       <c r="AG41" s="7"/>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AK41" s="1" t="n">
+        <v>-262335.9375</v>
+      </c>
+      <c r="AL41" s="1" t="n">
+        <v>-448163.58285518</v>
+      </c>
+      <c r="AM41" s="1" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="AN41" s="1" t="n">
+        <v>262664.0625</v>
+      </c>
+      <c r="AO41" s="1" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="AP41" s="1" t="n">
+        <v>371231.060122938</v>
+      </c>
+      <c r="AQ41" s="0"/>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L42" s="10"/>
       <c r="M42" s="11" t="n">
         <v>1</v>
@@ -55954,48 +56828,110 @@
         <v>7</v>
       </c>
       <c r="AE42" s="20"/>
+      <c r="AK42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" s="0"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H43" s="35"/>
       <c r="L43" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="M43" s="17"/>
-      <c r="N43" s="17"/>
-      <c r="O43" s="17"/>
-      <c r="P43" s="17"/>
-      <c r="Q43" s="17"/>
-      <c r="R43" s="17"/>
-      <c r="S43" s="165"/>
+      <c r="M43" s="165" t="n">
+        <f aca="false" t="array" ref="M43:S49">MMULT(M14:S20,M34:S40)</f>
+        <v>262664.0625</v>
+      </c>
+      <c r="N43" s="165" t="n">
+        <v>262335.9375</v>
+      </c>
+      <c r="O43" s="165" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="P43" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="165" t="n">
+        <v>-262335.9375</v>
+      </c>
+      <c r="R43" s="165" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="S43" s="172" t="n">
+        <v>-371231.060122938</v>
+      </c>
       <c r="U43" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="W43" s="69" t="e">
-        <f aca="false" t="array" ref="W43:W48">MMULT(M43:R48,U43:U48)-W34:W39</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="W43" s="69"/>
       <c r="AE43" s="20"/>
-    </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AK43" s="1" t="n">
+        <v>-262664.0625</v>
+      </c>
+      <c r="AL43" s="1" t="n">
+        <v>-448067.477267757</v>
+      </c>
+      <c r="AM43" s="1" t="n">
+        <v>464038.825153672</v>
+      </c>
+      <c r="AN43" s="1" t="n">
+        <v>262335.9375</v>
+      </c>
+      <c r="AO43" s="1" t="n">
+        <v>464038.825153672</v>
+      </c>
+      <c r="AP43" s="1" t="n">
+        <v>371231.060122938</v>
+      </c>
+      <c r="AQ43" s="0"/>
+    </row>
+    <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="2" t="s">
         <v>42</v>
       </c>
       <c r="L44" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="M44" s="17"/>
-      <c r="N44" s="17"/>
-      <c r="O44" s="17"/>
-      <c r="P44" s="17"/>
-      <c r="Q44" s="17"/>
-      <c r="R44" s="17"/>
-      <c r="S44" s="165"/>
+      <c r="M44" s="165" t="n">
+        <v>262335.9375</v>
+      </c>
+      <c r="N44" s="165" t="n">
+        <v>262664.0625</v>
+      </c>
+      <c r="O44" s="165" t="n">
+        <v>464038.825153672</v>
+      </c>
+      <c r="P44" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="165" t="n">
+        <v>-262664.0625</v>
+      </c>
+      <c r="R44" s="165" t="n">
+        <v>464038.825153672</v>
+      </c>
+      <c r="S44" s="172" t="n">
+        <v>-371231.060122938</v>
+      </c>
       <c r="U44" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="W44" s="69" t="e">
-        <v>#VALUE!</v>
-      </c>
+      <c r="W44" s="69"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="38" t="n">
@@ -56021,20 +56957,38 @@
       <c r="L45" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="M45" s="17"/>
-      <c r="N45" s="17"/>
-      <c r="O45" s="17"/>
-      <c r="P45" s="17"/>
-      <c r="Q45" s="17"/>
-      <c r="R45" s="17"/>
-      <c r="S45" s="165"/>
-      <c r="U45" s="36" t="e">
+      <c r="M45" s="165" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="N45" s="165" t="n">
+        <v>464038.825153672</v>
+      </c>
+      <c r="O45" s="165" t="n">
+        <v>1750000000</v>
+      </c>
+      <c r="P45" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="165" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="R45" s="165" t="n">
+        <v>875000000</v>
+      </c>
+      <c r="S45" s="172" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="36" t="n">
         <f aca="false">V58</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W45" s="69" t="e">
-        <v>#VALUE!</v>
-      </c>
+        <v>1.86612845584359E-018</v>
+      </c>
+      <c r="W45" s="69"/>
+      <c r="AK45" s="0"/>
+      <c r="AL45" s="0"/>
+      <c r="AM45" s="0"/>
+      <c r="AN45" s="0"/>
+      <c r="AO45" s="0"/>
+      <c r="AP45" s="0"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="38" t="n">
@@ -56060,22 +57014,44 @@
       <c r="L46" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="M46" s="17"/>
-      <c r="N46" s="17"/>
-      <c r="O46" s="17"/>
-      <c r="P46" s="17"/>
-      <c r="Q46" s="17"/>
-      <c r="R46" s="17"/>
-      <c r="S46" s="165"/>
-      <c r="U46" s="36" t="e">
+      <c r="M46" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="172" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="36" t="n">
         <f aca="false">V59</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W46" s="69" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="AF46" s="56"/>
-      <c r="AG46" s="56"/>
+        <v>-1.86612845584359E-018</v>
+      </c>
+      <c r="W46" s="69"/>
+      <c r="AD46" s="0"/>
+      <c r="AE46" s="0"/>
+      <c r="AF46" s="0"/>
+      <c r="AG46" s="0"/>
+      <c r="AH46" s="0"/>
+      <c r="AI46" s="0"/>
+      <c r="AK46" s="0"/>
+      <c r="AL46" s="0"/>
+      <c r="AM46" s="0"/>
+      <c r="AN46" s="0"/>
+      <c r="AO46" s="0"/>
+      <c r="AP46" s="0"/>
       <c r="CE46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56100,19 +57076,37 @@
       <c r="L47" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="M47" s="17"/>
-      <c r="N47" s="17"/>
-      <c r="O47" s="17"/>
-      <c r="P47" s="17"/>
-      <c r="Q47" s="17"/>
-      <c r="R47" s="17"/>
-      <c r="S47" s="165"/>
+      <c r="M47" s="165" t="n">
+        <v>-262335.9375</v>
+      </c>
+      <c r="N47" s="165" t="n">
+        <v>-262664.0625</v>
+      </c>
+      <c r="O47" s="165" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="P47" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="165" t="n">
+        <v>262664.0625</v>
+      </c>
+      <c r="R47" s="165" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="S47" s="172" t="n">
+        <v>371231.060122938</v>
+      </c>
       <c r="U47" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="W47" s="69" t="e">
-        <v>#VALUE!</v>
-      </c>
+      <c r="W47" s="69"/>
+      <c r="AK47" s="0"/>
+      <c r="AL47" s="0"/>
+      <c r="AM47" s="0"/>
+      <c r="AN47" s="0"/>
+      <c r="AO47" s="0"/>
+      <c r="AP47" s="0"/>
       <c r="BS47" s="13"/>
       <c r="CE47" s="2"/>
     </row>
@@ -56140,20 +57134,37 @@
       <c r="L48" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="M48" s="17"/>
-      <c r="N48" s="17"/>
-      <c r="O48" s="17"/>
-      <c r="P48" s="17"/>
-      <c r="Q48" s="17"/>
-      <c r="R48" s="17"/>
-      <c r="S48" s="165"/>
-      <c r="U48" s="36" t="e">
-        <f aca="false">V60</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W48" s="69" t="e">
-        <v>#VALUE!</v>
-      </c>
+      <c r="M48" s="165" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="N48" s="165" t="n">
+        <v>464038.825153672</v>
+      </c>
+      <c r="O48" s="165" t="n">
+        <v>875000000</v>
+      </c>
+      <c r="P48" s="165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="165" t="n">
+        <v>-464038.825153672</v>
+      </c>
+      <c r="R48" s="165" t="n">
+        <v>1750000000</v>
+      </c>
+      <c r="S48" s="172" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="69"/>
+      <c r="AK48" s="0"/>
+      <c r="AL48" s="0"/>
+      <c r="AM48" s="0"/>
+      <c r="AN48" s="0"/>
+      <c r="AO48" s="0"/>
+      <c r="AP48" s="0"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="38" t="n">
@@ -56179,13 +57190,37 @@
       <c r="L49" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="M49" s="159"/>
-      <c r="N49" s="159"/>
-      <c r="O49" s="159"/>
-      <c r="P49" s="159"/>
-      <c r="Q49" s="159"/>
-      <c r="R49" s="159"/>
-      <c r="S49" s="165"/>
+      <c r="M49" s="172" t="n">
+        <v>-371231.060122938</v>
+      </c>
+      <c r="N49" s="172" t="n">
+        <v>-371231.060122938</v>
+      </c>
+      <c r="O49" s="172" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="172" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="172" t="n">
+        <v>371231.060122938</v>
+      </c>
+      <c r="R49" s="172" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="172" t="n">
+        <v>525000</v>
+      </c>
+      <c r="U49" s="36" t="n">
+        <f aca="false">V60</f>
+        <v>-0.0380952380952381</v>
+      </c>
+      <c r="AK49" s="0"/>
+      <c r="AL49" s="0"/>
+      <c r="AM49" s="0"/>
+      <c r="AN49" s="0"/>
+      <c r="AO49" s="0"/>
+      <c r="AP49" s="0"/>
       <c r="CW49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56211,9 +57246,15 @@
       <c r="L50" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="S50" s="0"/>
+      <c r="S50" s="157"/>
       <c r="AI50" s="2"/>
       <c r="AJ50" s="2"/>
+      <c r="AK50" s="0"/>
+      <c r="AL50" s="0"/>
+      <c r="AM50" s="0"/>
+      <c r="AN50" s="0"/>
+      <c r="AO50" s="0"/>
+      <c r="AP50" s="0"/>
       <c r="BK50" s="2"/>
       <c r="CW50" s="2"/>
     </row>
@@ -56225,15 +57266,15 @@
         <v>3</v>
       </c>
       <c r="N51" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O51" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R51" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="S51" s="0"/>
+      <c r="S51" s="157"/>
       <c r="T51" s="10" t="s">
         <v>38</v>
       </c>
@@ -56260,19 +57301,27 @@
       <c r="L52" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="M52" s="13"/>
-      <c r="N52" s="13"/>
-      <c r="O52" s="13"/>
+      <c r="M52" s="173" t="n">
+        <f aca="false">O45</f>
+        <v>1750000000</v>
+      </c>
+      <c r="N52" s="173" t="n">
+        <f aca="false">R45</f>
+        <v>875000000</v>
+      </c>
+      <c r="O52" s="174" t="n">
+        <f aca="false">S45</f>
+        <v>0</v>
+      </c>
       <c r="P52" s="13"/>
       <c r="Q52" s="13"/>
       <c r="R52" s="13"/>
-      <c r="S52" s="0"/>
-      <c r="T52" s="21" t="str">
-        <f aca="false">U26</f>
-        <v>r13</v>
+      <c r="S52" s="157"/>
+      <c r="T52" s="21" t="s">
+        <v>44</v>
       </c>
       <c r="V52" s="50" t="n">
-        <f aca="false" t="array" ref="V52:V53">W36:W37</f>
+        <f aca="false">W36</f>
         <v>1.63286239886314E-009</v>
       </c>
       <c r="AI52" s="32"/>
@@ -56295,20 +57344,30 @@
       </c>
       <c r="I53" s="13"/>
       <c r="L53" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="M53" s="13"/>
-      <c r="N53" s="13"/>
+        <v>6</v>
+      </c>
+      <c r="M53" s="173" t="n">
+        <f aca="false">O48</f>
+        <v>875000000</v>
+      </c>
+      <c r="N53" s="173" t="n">
+        <f aca="false">R48</f>
+        <v>1750000000</v>
+      </c>
+      <c r="O53" s="174" t="n">
+        <f aca="false">S48</f>
+        <v>0</v>
+      </c>
       <c r="P53" s="13"/>
       <c r="Q53" s="13"/>
       <c r="R53" s="13"/>
-      <c r="S53" s="0"/>
-      <c r="T53" s="21" t="str">
-        <f aca="false">U27</f>
-        <v>r14</v>
-      </c>
-      <c r="V53" s="51" t="n">
-        <v>-20000</v>
+      <c r="S53" s="157"/>
+      <c r="T53" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="V53" s="50" t="n">
+        <f aca="false">W39</f>
+        <v>-1.63286239886314E-009</v>
       </c>
       <c r="AB53" s="7"/>
       <c r="AE53" s="7"/>
@@ -56333,11 +57392,10 @@
     </row>
     <row r="54" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="38" t="n">
-        <f aca="false">$C$5</f>
+        <f aca="false" t="array" ref="B54:G59">TRANSPOSE(B45:G50)</f>
         <v>0.707106781186548</v>
       </c>
       <c r="C54" s="38" t="n">
-        <f aca="false">-$E$5</f>
         <v>-0.707106781186548</v>
       </c>
       <c r="D54" s="38" t="n">
@@ -56353,20 +57411,28 @@
         <v>0</v>
       </c>
       <c r="L54" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="M54" s="13"/>
-      <c r="N54" s="13"/>
-      <c r="O54" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="M54" s="174" t="n">
+        <f aca="false">O49</f>
+        <v>0</v>
+      </c>
+      <c r="N54" s="174" t="n">
+        <f aca="false">P49</f>
+        <v>0</v>
+      </c>
+      <c r="O54" s="174" t="n">
+        <f aca="false">S49</f>
+        <v>525000</v>
+      </c>
       <c r="P54" s="13"/>
-      <c r="S54" s="0"/>
-      <c r="T54" s="21" t="str">
-        <f aca="false">U29</f>
-        <v>r16</v>
+      <c r="S54" s="157"/>
+      <c r="T54" s="21" t="s">
+        <v>153</v>
       </c>
       <c r="V54" s="13" t="n">
-        <f aca="false">W38</f>
-        <v>0</v>
+        <f aca="false">W40</f>
+        <v>-20000</v>
       </c>
       <c r="AB54" s="7"/>
       <c r="AC54" s="20"/>
@@ -56387,11 +57453,9 @@
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="38" t="n">
-        <f aca="false">$E$5</f>
         <v>0.707106781186548</v>
       </c>
       <c r="C55" s="38" t="n">
-        <f aca="false">$C$5</f>
         <v>0.707106781186548</v>
       </c>
       <c r="D55" s="38" t="n">
@@ -56408,7 +57472,7 @@
       </c>
       <c r="Q55" s="13"/>
       <c r="R55" s="13"/>
-      <c r="S55" s="0"/>
+      <c r="S55" s="157"/>
       <c r="V55" s="50"/>
       <c r="AC55" s="20"/>
       <c r="AE55" s="20"/>
@@ -56434,7 +57498,6 @@
         <v>0</v>
       </c>
       <c r="D56" s="38" t="n">
-        <f aca="false">D47</f>
         <v>1</v>
       </c>
       <c r="E56" s="38" t="n">
@@ -56446,7 +57509,7 @@
       <c r="G56" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="S56" s="0"/>
+      <c r="S56" s="157"/>
       <c r="V56" s="10" t="s">
         <v>117</v>
       </c>
@@ -56477,11 +57540,9 @@
         <v>0</v>
       </c>
       <c r="E57" s="38" t="n">
-        <f aca="false">$C$5</f>
         <v>0.707106781186548</v>
       </c>
       <c r="F57" s="38" t="n">
-        <f aca="false">-$E$5</f>
         <v>-0.707106781186548</v>
       </c>
       <c r="G57" s="38" t="n">
@@ -56492,16 +57553,15 @@
         <v>3</v>
       </c>
       <c r="N57" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O57" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="P57" s="159"/>
+        <v>7</v>
+      </c>
       <c r="R57" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="S57" s="0"/>
+      <c r="S57" s="157"/>
       <c r="T57" s="47" t="s">
         <v>10</v>
       </c>
@@ -56528,11 +57588,9 @@
         <v>0</v>
       </c>
       <c r="E58" s="38" t="n">
-        <f aca="false">$E$5</f>
         <v>0.707106781186548</v>
       </c>
       <c r="F58" s="38" t="n">
-        <f aca="false">$C$5</f>
         <v>0.707106781186548</v>
       </c>
       <c r="G58" s="38" t="n">
@@ -56541,21 +57599,31 @@
       <c r="L58" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="S58" s="0"/>
+      <c r="M58" s="175" t="n">
+        <f aca="false" t="array" ref="M58:O60">MINVERSE(M52:O54)</f>
+        <v>7.61904761904762E-010</v>
+      </c>
+      <c r="N58" s="175" t="n">
+        <v>-3.80952380952381E-010</v>
+      </c>
+      <c r="O58" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="157"/>
       <c r="T58" s="13" t="n">
-        <f aca="false" t="array" ref="T58:T60">V52:V54</f>
+        <f aca="false">W36</f>
         <v>1.63286239886314E-009</v>
       </c>
-      <c r="V58" s="36" t="e">
+      <c r="V58" s="36" t="n">
         <f aca="false" t="array" ref="V58:V60">MMULT(M58:O60,T58:T60)</f>
-        <v>#VALUE!</v>
+        <v>1.86612845584359E-018</v>
       </c>
       <c r="W58" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="X58" s="1" t="e">
+      <c r="X58" s="1" t="n">
         <f aca="false">1000*V58</f>
-        <v>#VALUE!</v>
+        <v>1.86612845584359E-015</v>
       </c>
       <c r="Y58" s="1" t="s">
         <v>79</v>
@@ -56582,26 +57650,38 @@
         <v>0</v>
       </c>
       <c r="G59" s="38" t="n">
-        <f aca="false">D47</f>
         <v>1</v>
       </c>
       <c r="L59" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="N59" s="13"/>
+        <v>6</v>
+      </c>
+      <c r="M59" s="175" t="n">
+        <v>-3.80952380952381E-010</v>
+      </c>
+      <c r="N59" s="176" t="n">
+        <v>7.61904761904762E-010</v>
+      </c>
+      <c r="O59" s="175" t="n">
+        <v>0</v>
+      </c>
       <c r="P59" s="13"/>
-      <c r="S59" s="0"/>
-      <c r="T59" s="1" t="n">
-        <v>-20000</v>
-      </c>
-      <c r="V59" s="36" t="e">
-        <v>#VALUE!</v>
+      <c r="S59" s="157"/>
+      <c r="T59" s="13" t="n">
+        <f aca="false">W39</f>
+        <v>-1.63286239886314E-009</v>
+      </c>
+      <c r="V59" s="36" t="n">
+        <v>-1.86612845584359E-018</v>
       </c>
       <c r="W59" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="X59" s="1" t="s">
-        <v>121</v>
+        <v>78</v>
+      </c>
+      <c r="X59" s="1" t="n">
+        <f aca="false">1000*V59</f>
+        <v>-1.86612845584359E-015</v>
+      </c>
+      <c r="Y59" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="AC59" s="60"/>
       <c r="AD59" s="7"/>
@@ -56623,27 +57703,33 @@
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L60" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="N60" s="13"/>
+        <v>7</v>
+      </c>
+      <c r="M60" s="175" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="176" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="175" t="n">
+        <v>1.9047619047619E-006</v>
+      </c>
       <c r="P60" s="13"/>
-      <c r="S60" s="0"/>
-      <c r="T60" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" s="36" t="e">
-        <v>#VALUE!</v>
+      <c r="S60" s="157"/>
+      <c r="T60" s="13" t="n">
+        <f aca="false">W40</f>
+        <v>-20000</v>
+      </c>
+      <c r="V60" s="36" t="n">
+        <v>-0.0380952380952381</v>
       </c>
       <c r="W60" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="X60" s="1" t="e">
-        <f aca="false">1000*V60</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Y60" s="1" t="s">
-        <v>79</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="X60" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y60" s="0"/>
       <c r="AC60" s="60"/>
       <c r="AD60" s="7"/>
       <c r="AE60" s="7"/>
@@ -56663,8 +57749,7 @@
       <c r="CA60" s="49"/>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L61" s="159"/>
-      <c r="S61" s="0"/>
+      <c r="S61" s="157"/>
       <c r="V61" s="36"/>
       <c r="AC61" s="7"/>
       <c r="AE61" s="20"/>
@@ -56690,7 +57775,7 @@
       <c r="CE61" s="52"/>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="S62" s="0"/>
+      <c r="S62" s="157"/>
       <c r="W62" s="13"/>
       <c r="Y62" s="36"/>
       <c r="AC62" s="7"/>
@@ -56709,8 +57794,12 @@
       <c r="CA62" s="49"/>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L63" s="13" t="n">
+        <f aca="false">M49</f>
+        <v>-371231.060122938</v>
+      </c>
       <c r="Q63" s="13"/>
-      <c r="S63" s="0"/>
+      <c r="S63" s="157"/>
       <c r="V63" s="10" t="s">
         <v>122</v>
       </c>
@@ -56731,7 +57820,7 @@
       <c r="CA63" s="49"/>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="S64" s="0"/>
+      <c r="S64" s="157"/>
       <c r="V64" s="10" t="s">
         <v>38</v>
       </c>
@@ -56740,37 +57829,37 @@
       <c r="BR64" s="54"/>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="S65" s="0"/>
+      <c r="S65" s="157"/>
       <c r="U65" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="V65" s="1" t="e">
+      <c r="V65" s="1" t="n">
         <f aca="false">COS(RADIANS(Q13))*V59</f>
-        <v>#VALUE!</v>
+        <v>-1.86612845584359E-018</v>
       </c>
       <c r="W65" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="Y65" s="36" t="e">
+      <c r="Y65" s="36" t="n">
         <f aca="false">V59</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Z65" s="1" t="e">
+        <v>-1.86612845584359E-018</v>
+      </c>
+      <c r="Z65" s="1" t="n">
         <f aca="false" t="array" ref="Z65:Z66">MMULT(X17:Y18,Y65:Y66)</f>
-        <v>#VALUE!</v>
+        <v>-1.86612845584359E-018</v>
       </c>
       <c r="AC65" s="7"/>
       <c r="AE65" s="7"/>
       <c r="BR65" s="54"/>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="S66" s="0"/>
+      <c r="S66" s="157"/>
       <c r="U66" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="V66" s="1" t="e">
+      <c r="V66" s="1" t="n">
         <f aca="false">SIN(RADIANS(Q13))*V59</f>
-        <v>#VALUE!</v>
+        <v>-0</v>
       </c>
       <c r="W66" s="1" t="s">
         <v>12</v>
@@ -56778,8 +57867,8 @@
       <c r="Y66" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="1" t="e">
-        <v>#VALUE!</v>
+      <c r="Z66" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="AC66" s="7"/>
       <c r="AE66" s="7"/>
@@ -56787,91 +57876,91 @@
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I67" s="9"/>
-      <c r="L67" s="0"/>
-      <c r="M67" s="0"/>
-      <c r="N67" s="0"/>
-      <c r="O67" s="0"/>
-      <c r="P67" s="0"/>
-      <c r="Q67" s="0"/>
-      <c r="R67" s="0"/>
-      <c r="S67" s="0"/>
-      <c r="T67" s="0"/>
-      <c r="U67" s="0"/>
-      <c r="V67" s="0"/>
-      <c r="W67" s="0"/>
-      <c r="X67" s="0"/>
-      <c r="Y67" s="0"/>
-      <c r="Z67" s="0"/>
+      <c r="L67" s="157"/>
+      <c r="M67" s="157"/>
+      <c r="N67" s="157"/>
+      <c r="O67" s="157"/>
+      <c r="P67" s="157"/>
+      <c r="Q67" s="157"/>
+      <c r="R67" s="157"/>
+      <c r="S67" s="157"/>
+      <c r="T67" s="157"/>
+      <c r="U67" s="157"/>
+      <c r="V67" s="157"/>
+      <c r="W67" s="157"/>
+      <c r="X67" s="157"/>
+      <c r="Y67" s="157"/>
+      <c r="Z67" s="157"/>
       <c r="AC67" s="7"/>
       <c r="AE67" s="7"/>
       <c r="BR67" s="54"/>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L68" s="0"/>
-      <c r="M68" s="0"/>
-      <c r="N68" s="0"/>
-      <c r="O68" s="0"/>
-      <c r="P68" s="0"/>
-      <c r="Q68" s="0"/>
-      <c r="R68" s="0"/>
-      <c r="S68" s="0"/>
-      <c r="T68" s="0"/>
-      <c r="U68" s="0"/>
-      <c r="V68" s="0"/>
-      <c r="W68" s="0"/>
-      <c r="X68" s="0"/>
-      <c r="Y68" s="0"/>
+      <c r="L68" s="157"/>
+      <c r="M68" s="157"/>
+      <c r="N68" s="157"/>
+      <c r="O68" s="157"/>
+      <c r="P68" s="157"/>
+      <c r="Q68" s="157"/>
+      <c r="R68" s="157"/>
+      <c r="S68" s="157"/>
+      <c r="T68" s="157"/>
+      <c r="U68" s="157"/>
+      <c r="V68" s="157"/>
+      <c r="W68" s="157"/>
+      <c r="X68" s="157"/>
+      <c r="Y68" s="157"/>
       <c r="BR68" s="54"/>
     </row>
     <row r="69" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="L69" s="0"/>
-      <c r="M69" s="0"/>
-      <c r="N69" s="0"/>
-      <c r="O69" s="0"/>
-      <c r="P69" s="0"/>
-      <c r="Q69" s="0"/>
-      <c r="R69" s="0"/>
-      <c r="S69" s="0"/>
-      <c r="T69" s="0"/>
-      <c r="U69" s="0"/>
-      <c r="V69" s="0"/>
-      <c r="W69" s="0"/>
-      <c r="X69" s="0"/>
-      <c r="Y69" s="0"/>
+      <c r="L69" s="157"/>
+      <c r="M69" s="157"/>
+      <c r="N69" s="157"/>
+      <c r="O69" s="157"/>
+      <c r="P69" s="157"/>
+      <c r="Q69" s="157"/>
+      <c r="R69" s="157"/>
+      <c r="S69" s="157"/>
+      <c r="T69" s="157"/>
+      <c r="U69" s="157"/>
+      <c r="V69" s="157"/>
+      <c r="W69" s="157"/>
+      <c r="X69" s="157"/>
+      <c r="Y69" s="157"/>
       <c r="BR69" s="54"/>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E70" s="15"/>
-      <c r="L70" s="0"/>
-      <c r="M70" s="0"/>
-      <c r="N70" s="0"/>
-      <c r="O70" s="0"/>
-      <c r="P70" s="0"/>
-      <c r="Q70" s="0"/>
-      <c r="R70" s="0"/>
-      <c r="S70" s="0"/>
-      <c r="T70" s="0"/>
-      <c r="U70" s="0"/>
-      <c r="V70" s="0"/>
-      <c r="W70" s="0"/>
-      <c r="X70" s="0"/>
-      <c r="Y70" s="0"/>
+      <c r="L70" s="157"/>
+      <c r="M70" s="157"/>
+      <c r="N70" s="157"/>
+      <c r="O70" s="157"/>
+      <c r="P70" s="157"/>
+      <c r="Q70" s="157"/>
+      <c r="R70" s="157"/>
+      <c r="S70" s="157"/>
+      <c r="T70" s="157"/>
+      <c r="U70" s="157"/>
+      <c r="V70" s="157"/>
+      <c r="W70" s="157"/>
+      <c r="X70" s="157"/>
+      <c r="Y70" s="157"/>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L71" s="0"/>
-      <c r="M71" s="0"/>
-      <c r="N71" s="0"/>
-      <c r="O71" s="0"/>
-      <c r="P71" s="0"/>
-      <c r="Q71" s="0"/>
-      <c r="R71" s="0"/>
-      <c r="S71" s="0"/>
-      <c r="T71" s="0"/>
-      <c r="U71" s="0"/>
-      <c r="V71" s="0"/>
-      <c r="W71" s="0"/>
-      <c r="X71" s="0"/>
-      <c r="Y71" s="0"/>
+      <c r="L71" s="157"/>
+      <c r="M71" s="157"/>
+      <c r="N71" s="157"/>
+      <c r="O71" s="157"/>
+      <c r="P71" s="157"/>
+      <c r="Q71" s="157"/>
+      <c r="R71" s="157"/>
+      <c r="S71" s="157"/>
+      <c r="T71" s="157"/>
+      <c r="U71" s="157"/>
+      <c r="V71" s="157"/>
+      <c r="W71" s="157"/>
+      <c r="X71" s="157"/>
+      <c r="Y71" s="157"/>
       <c r="AG71" s="2"/>
       <c r="AH71" s="2"/>
     </row>
@@ -56996,9 +58085,9 @@
         <f aca="false">G28</f>
         <v>0</v>
       </c>
-      <c r="T77" s="1" t="e">
+      <c r="T77" s="1" t="n">
         <f aca="false" t="array" ref="T77:T82">MMULT(B45:G50,Y24:Y29)</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="V77" s="13" t="n">
         <f aca="false">I28</f>
@@ -57047,8 +58136,8 @@
         <f aca="false">G29</f>
         <v>656250</v>
       </c>
-      <c r="T78" s="1" t="e">
-        <v>#VALUE!</v>
+      <c r="T78" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="V78" s="13" t="n">
         <f aca="false">I29</f>
@@ -57096,8 +58185,8 @@
         <f aca="false">G30</f>
         <v>875000000</v>
       </c>
-      <c r="T79" s="1" t="e">
-        <v>#VALUE!</v>
+      <c r="T79" s="1" t="n">
+        <v>1.86612845584359E-018</v>
       </c>
       <c r="V79" s="13" t="n">
         <f aca="false">I30</f>
@@ -57145,8 +58234,8 @@
         <f aca="false">G31</f>
         <v>0</v>
       </c>
-      <c r="T80" s="1" t="e">
-        <v>#VALUE!</v>
+      <c r="T80" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="V80" s="13" t="n">
         <f aca="false">I31</f>
@@ -57185,8 +58274,8 @@
         <f aca="false">G32</f>
         <v>-656250</v>
       </c>
-      <c r="T81" s="1" t="e">
-        <v>#VALUE!</v>
+      <c r="T81" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="V81" s="13" t="n">
         <f aca="false">I32</f>
@@ -57226,8 +58315,8 @@
         <f aca="false">G33</f>
         <v>1750000000</v>
       </c>
-      <c r="T82" s="1" t="e">
-        <v>#VALUE!</v>
+      <c r="T82" s="1" t="n">
+        <v>-1.86612845584359E-018</v>
       </c>
       <c r="V82" s="13" t="n">
         <f aca="false">I33</f>
@@ -58904,14 +59993,39 @@
       <formula>"OK!"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M15:R20 M26:R30 M33:R33 M37:R39 M42:R44 M47:R52 V15:AA20">
+  <conditionalFormatting sqref="M33:R33 M37:R39 M42:R44 M47:R51 M15:O20 U15:W20 X20:AA20 P52:R52 S18:S19 P20:S20">
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>ABS(M16)&lt;0.1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X26:X30 X33:X34 X37:X39 X42:X44">
+  <conditionalFormatting sqref="X33:X34 X37:X39 X42:X44">
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>ABS(Y35)&lt;0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P15:P19 X15:X19">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>ABS(P16)&lt;0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q15:Q19 Y15:Y19">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>ABS(Q16)&lt;0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X26:X30">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>ABS(Y28)&lt;0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M26:R30">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>ABS(M27)&lt;0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O52">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>ABS(O53)&lt;0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
